--- a/artfynd/A 9000-2025 artfynd.xlsx
+++ b/artfynd/A 9000-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122840378</v>
+        <v>122840992</v>
       </c>
       <c r="B2" t="n">
-        <v>57848</v>
+        <v>90944</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>676985</v>
+        <v>676900</v>
       </c>
       <c r="R2" t="n">
-        <v>6615696</v>
+        <v>6615757</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122840623</v>
+        <v>122840972</v>
       </c>
       <c r="B3" t="n">
-        <v>57494</v>
+        <v>90944</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,39 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>676932</v>
+        <v>676898</v>
       </c>
       <c r="R3" t="n">
-        <v>6615725</v>
+        <v>6615759</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122842144</v>
+        <v>122840378</v>
       </c>
       <c r="B4" t="n">
-        <v>100613</v>
+        <v>57848</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,34 +895,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>676841</v>
+        <v>676985</v>
       </c>
       <c r="R4" t="n">
-        <v>6615983</v>
+        <v>6615696</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122842273</v>
+        <v>122844921</v>
       </c>
       <c r="B5" t="n">
-        <v>100613</v>
+        <v>79807</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,34 +1002,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>229497</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>676787</v>
+        <v>676904</v>
       </c>
       <c r="R5" t="n">
-        <v>6615980</v>
+        <v>6615766</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122841097</v>
+        <v>122840623</v>
       </c>
       <c r="B6" t="n">
-        <v>5173</v>
+        <v>57494</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,31 +1100,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1138,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>676861</v>
+        <v>676932</v>
       </c>
       <c r="R6" t="n">
-        <v>6615758</v>
+        <v>6615725</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122842748</v>
+        <v>122843607</v>
       </c>
       <c r="B7" t="n">
-        <v>5193</v>
+        <v>100621</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,39 +1211,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>676684</v>
+        <v>676666</v>
       </c>
       <c r="R7" t="n">
-        <v>6615835</v>
+        <v>6615819</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122842133</v>
+        <v>122845880</v>
       </c>
       <c r="B8" t="n">
-        <v>100613</v>
+        <v>90962</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1319,38 +1309,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>676838</v>
+        <v>677085</v>
       </c>
       <c r="R8" t="n">
-        <v>6615977</v>
+        <v>6615732</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122841986</v>
+        <v>122841068</v>
       </c>
       <c r="B9" t="n">
-        <v>105453</v>
+        <v>4867</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,34 +1415,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>101675</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>676779</v>
+        <v>676872</v>
       </c>
       <c r="R9" t="n">
-        <v>6615963</v>
+        <v>6615746</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1511,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122841077</v>
+        <v>122841301</v>
       </c>
       <c r="B10" t="n">
-        <v>5193</v>
+        <v>8430</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,43 +1522,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>105930</v>
+        <v>106554</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>676870</v>
+        <v>676893</v>
       </c>
       <c r="R10" t="n">
-        <v>6615757</v>
+        <v>6615790</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1604,7 +1595,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1623,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122845448</v>
+        <v>122843861</v>
       </c>
       <c r="B11" t="n">
-        <v>105453</v>
+        <v>57494</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1635,38 +1625,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>676972</v>
+        <v>676804</v>
       </c>
       <c r="R11" t="n">
-        <v>6615705</v>
+        <v>6615893</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1725,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122842185</v>
+        <v>122845448</v>
       </c>
       <c r="B12" t="n">
-        <v>100613</v>
+        <v>105461</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1741,34 +1736,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>676831</v>
+        <v>676972</v>
       </c>
       <c r="R12" t="n">
-        <v>6615990</v>
+        <v>6615705</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1827,10 +1822,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122842832</v>
+        <v>122842479</v>
       </c>
       <c r="B13" t="n">
-        <v>57631</v>
+        <v>8430</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1839,46 +1834,46 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>106554</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>676682</v>
+        <v>676756</v>
       </c>
       <c r="R13" t="n">
-        <v>6615846</v>
+        <v>6615927</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1934,10 +1929,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122845288</v>
+        <v>122840989</v>
       </c>
       <c r="B14" t="n">
-        <v>8430</v>
+        <v>5173</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1950,21 +1945,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106554</v>
+        <v>100526</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1979,10 +1974,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>677007</v>
+        <v>676899</v>
       </c>
       <c r="R14" t="n">
-        <v>6615684</v>
+        <v>6615760</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2041,10 +2036,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122844921</v>
+        <v>122845245</v>
       </c>
       <c r="B15" t="n">
-        <v>79803</v>
+        <v>8441</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2057,34 +2052,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229497</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>676904</v>
+        <v>677001</v>
       </c>
       <c r="R15" t="n">
-        <v>6615766</v>
+        <v>6615675</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2143,10 +2143,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122842642</v>
+        <v>122842819</v>
       </c>
       <c r="B16" t="n">
-        <v>100613</v>
+        <v>105461</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2159,34 +2159,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>676714</v>
+        <v>676682</v>
       </c>
       <c r="R16" t="n">
-        <v>6615824</v>
+        <v>6615846</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2245,10 +2245,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122841332</v>
+        <v>122840712</v>
       </c>
       <c r="B17" t="n">
-        <v>57494</v>
+        <v>4867</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2257,31 +2257,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>101675</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2290,13 +2290,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>676864</v>
+        <v>676921</v>
       </c>
       <c r="R17" t="n">
-        <v>6615776</v>
+        <v>6615744</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2352,10 +2352,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122840712</v>
+        <v>122842680</v>
       </c>
       <c r="B18" t="n">
-        <v>4867</v>
+        <v>57848</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2368,42 +2368,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>101675</v>
+        <v>103015</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>676921</v>
+        <v>676711</v>
       </c>
       <c r="R18" t="n">
-        <v>6615744</v>
+        <v>6615822</v>
       </c>
       <c r="S18" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2459,10 +2459,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122843664</v>
+        <v>122843696</v>
       </c>
       <c r="B19" t="n">
-        <v>100613</v>
+        <v>90962</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2471,25 +2471,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2499,10 +2499,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>676656</v>
+        <v>676651</v>
       </c>
       <c r="R19" t="n">
-        <v>6615859</v>
+        <v>6615875</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2561,10 +2561,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122842401</v>
+        <v>122842185</v>
       </c>
       <c r="B20" t="n">
-        <v>57494</v>
+        <v>100621</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2573,43 +2573,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>676742</v>
+        <v>676831</v>
       </c>
       <c r="R20" t="n">
-        <v>6615954</v>
+        <v>6615990</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2668,10 +2663,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122840922</v>
+        <v>122841077</v>
       </c>
       <c r="B21" t="n">
-        <v>105453</v>
+        <v>5193</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2684,34 +2679,43 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221144</v>
+        <v>105930</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>676912</v>
+        <v>676870</v>
       </c>
       <c r="R21" t="n">
-        <v>6615761</v>
+        <v>6615757</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2752,6 +2756,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2770,10 +2775,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122841068</v>
+        <v>122843664</v>
       </c>
       <c r="B22" t="n">
-        <v>4867</v>
+        <v>100621</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2786,39 +2791,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>101675</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>676872</v>
+        <v>676656</v>
       </c>
       <c r="R22" t="n">
-        <v>6615746</v>
+        <v>6615859</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2877,10 +2877,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122843696</v>
+        <v>122845736</v>
       </c>
       <c r="B23" t="n">
-        <v>90958</v>
+        <v>8441</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2889,38 +2889,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>676651</v>
+        <v>677104</v>
       </c>
       <c r="R23" t="n">
-        <v>6615875</v>
+        <v>6615675</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2979,10 +2984,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122842434</v>
+        <v>122842792</v>
       </c>
       <c r="B24" t="n">
-        <v>57494</v>
+        <v>90909</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2991,43 +2996,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>676739</v>
+        <v>676683</v>
       </c>
       <c r="R24" t="n">
-        <v>6615944</v>
+        <v>6615843</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3086,10 +3086,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122843888</v>
+        <v>122842273</v>
       </c>
       <c r="B25" t="n">
-        <v>8430</v>
+        <v>100621</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3102,43 +3102,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>676813</v>
+        <v>676787</v>
       </c>
       <c r="R25" t="n">
-        <v>6615903</v>
+        <v>6615980</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3179,7 +3170,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3198,10 +3188,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122840972</v>
+        <v>122842642</v>
       </c>
       <c r="B26" t="n">
-        <v>90940</v>
+        <v>100621</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3210,38 +3200,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>676898</v>
+        <v>676714</v>
       </c>
       <c r="R26" t="n">
-        <v>6615759</v>
+        <v>6615824</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3300,10 +3290,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122840652</v>
+        <v>122845288</v>
       </c>
       <c r="B27" t="n">
-        <v>90905</v>
+        <v>8430</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3316,34 +3306,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>106554</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>676670</v>
+        <v>677007</v>
       </c>
       <c r="R27" t="n">
-        <v>6615860</v>
+        <v>6615684</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3402,10 +3397,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122840392</v>
+        <v>122843888</v>
       </c>
       <c r="B28" t="n">
-        <v>57494</v>
+        <v>8430</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3414,43 +3409,47 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>676983</v>
+        <v>676813</v>
       </c>
       <c r="R28" t="n">
-        <v>6615701</v>
+        <v>6615903</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3491,6 +3490,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3509,10 +3509,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122841301</v>
+        <v>122841332</v>
       </c>
       <c r="B29" t="n">
-        <v>8430</v>
+        <v>57494</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3521,31 +3521,31 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3554,10 +3554,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>676893</v>
+        <v>676864</v>
       </c>
       <c r="R29" t="n">
-        <v>6615790</v>
+        <v>6615776</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3616,10 +3616,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122843607</v>
+        <v>122841097</v>
       </c>
       <c r="B30" t="n">
-        <v>100613</v>
+        <v>5173</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3632,34 +3632,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>676666</v>
+        <v>676861</v>
       </c>
       <c r="R30" t="n">
-        <v>6615819</v>
+        <v>6615758</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3718,10 +3723,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122840989</v>
+        <v>122842133</v>
       </c>
       <c r="B31" t="n">
-        <v>5173</v>
+        <v>100621</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3734,39 +3739,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>676899</v>
+        <v>676838</v>
       </c>
       <c r="R31" t="n">
-        <v>6615760</v>
+        <v>6615977</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3825,10 +3825,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122842206</v>
+        <v>122842144</v>
       </c>
       <c r="B32" t="n">
-        <v>100613</v>
+        <v>100621</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3865,10 +3865,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>676816</v>
+        <v>676841</v>
       </c>
       <c r="R32" t="n">
-        <v>6615981</v>
+        <v>6615983</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3927,10 +3927,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122842950</v>
+        <v>122842088</v>
       </c>
       <c r="B33" t="n">
-        <v>105453</v>
+        <v>100621</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3943,34 +3943,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>676690</v>
+        <v>676779</v>
       </c>
       <c r="R33" t="n">
-        <v>6615799</v>
+        <v>6615963</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4029,10 +4029,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122840992</v>
+        <v>122842950</v>
       </c>
       <c r="B34" t="n">
-        <v>90940</v>
+        <v>105461</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4041,38 +4041,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>676900</v>
+        <v>676690</v>
       </c>
       <c r="R34" t="n">
-        <v>6615757</v>
+        <v>6615799</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4131,10 +4131,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122842792</v>
+        <v>122845926</v>
       </c>
       <c r="B35" t="n">
-        <v>90905</v>
+        <v>90909</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4167,14 +4167,14 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>676683</v>
+        <v>677084</v>
       </c>
       <c r="R35" t="n">
-        <v>6615843</v>
+        <v>6615718</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4233,10 +4233,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122842088</v>
+        <v>122845093</v>
       </c>
       <c r="B36" t="n">
-        <v>100613</v>
+        <v>90909</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4249,34 +4249,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>676779</v>
+        <v>676956</v>
       </c>
       <c r="R36" t="n">
-        <v>6615963</v>
+        <v>6615718</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4335,10 +4335,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122843861</v>
+        <v>122842832</v>
       </c>
       <c r="B37" t="n">
-        <v>57494</v>
+        <v>57631</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4351,42 +4351,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>676804</v>
+        <v>676682</v>
       </c>
       <c r="R37" t="n">
-        <v>6615893</v>
+        <v>6615846</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4442,10 +4442,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122842680</v>
+        <v>122840495</v>
       </c>
       <c r="B38" t="n">
-        <v>57848</v>
+        <v>5193</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4458,16 +4458,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103015</v>
+        <v>105930</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4478,19 +4478,19 @@
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>676711</v>
+        <v>676936</v>
       </c>
       <c r="R38" t="n">
-        <v>6615822</v>
+        <v>6615736</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4549,10 +4549,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122842479</v>
+        <v>122842206</v>
       </c>
       <c r="B39" t="n">
-        <v>8430</v>
+        <v>100621</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4565,39 +4565,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>676756</v>
+        <v>676816</v>
       </c>
       <c r="R39" t="n">
-        <v>6615927</v>
+        <v>6615981</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4656,10 +4651,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122845093</v>
+        <v>122842557</v>
       </c>
       <c r="B40" t="n">
-        <v>90905</v>
+        <v>90944</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4668,38 +4663,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>676956</v>
+        <v>676745</v>
       </c>
       <c r="R40" t="n">
-        <v>6615718</v>
+        <v>6615878</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4758,10 +4753,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122845736</v>
+        <v>122842748</v>
       </c>
       <c r="B41" t="n">
-        <v>8441</v>
+        <v>5193</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4774,21 +4769,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4799,14 +4794,14 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>677104</v>
+        <v>676684</v>
       </c>
       <c r="R41" t="n">
-        <v>6615675</v>
+        <v>6615835</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4865,10 +4860,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122840804</v>
+        <v>122842401</v>
       </c>
       <c r="B42" t="n">
-        <v>5358</v>
+        <v>57494</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4881,39 +4876,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>101728</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>676921</v>
+        <v>676742</v>
       </c>
       <c r="R42" t="n">
-        <v>6615744</v>
+        <v>6615954</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4972,10 +4967,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122840930</v>
+        <v>122840652</v>
       </c>
       <c r="B43" t="n">
-        <v>57494</v>
+        <v>90909</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4984,43 +4979,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>676913</v>
+        <v>676670</v>
       </c>
       <c r="R43" t="n">
-        <v>6615763</v>
+        <v>6615860</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5079,10 +5069,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122842819</v>
+        <v>122840392</v>
       </c>
       <c r="B44" t="n">
-        <v>105453</v>
+        <v>57494</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5091,38 +5081,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>676682</v>
+        <v>676983</v>
       </c>
       <c r="R44" t="n">
-        <v>6615846</v>
+        <v>6615701</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5181,10 +5176,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122840896</v>
+        <v>122842434</v>
       </c>
       <c r="B45" t="n">
-        <v>5358</v>
+        <v>57494</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5197,39 +5192,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>101728</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>676913</v>
+        <v>676739</v>
       </c>
       <c r="R45" t="n">
-        <v>6615766</v>
+        <v>6615944</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5288,10 +5283,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122845880</v>
+        <v>122840896</v>
       </c>
       <c r="B46" t="n">
-        <v>90958</v>
+        <v>5358</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5304,34 +5299,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>101728</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>677085</v>
+        <v>676913</v>
       </c>
       <c r="R46" t="n">
-        <v>6615732</v>
+        <v>6615766</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5390,10 +5390,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122845926</v>
+        <v>122840804</v>
       </c>
       <c r="B47" t="n">
-        <v>90905</v>
+        <v>5358</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5402,38 +5402,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5447</v>
+        <v>101728</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>677084</v>
+        <v>676921</v>
       </c>
       <c r="R47" t="n">
-        <v>6615718</v>
+        <v>6615744</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5492,10 +5497,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122842557</v>
+        <v>122841986</v>
       </c>
       <c r="B48" t="n">
-        <v>90940</v>
+        <v>105461</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5504,25 +5509,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5532,10 +5537,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>676745</v>
+        <v>676779</v>
       </c>
       <c r="R48" t="n">
-        <v>6615878</v>
+        <v>6615963</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5594,10 +5599,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122845245</v>
+        <v>122840930</v>
       </c>
       <c r="B49" t="n">
-        <v>8441</v>
+        <v>57494</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5606,31 +5611,31 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5639,10 +5644,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>677001</v>
+        <v>676913</v>
       </c>
       <c r="R49" t="n">
-        <v>6615675</v>
+        <v>6615763</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5701,10 +5706,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122840495</v>
+        <v>122840922</v>
       </c>
       <c r="B50" t="n">
-        <v>5193</v>
+        <v>105461</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5717,39 +5722,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>105930</v>
+        <v>221144</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>676936</v>
+        <v>676912</v>
       </c>
       <c r="R50" t="n">
-        <v>6615736</v>
+        <v>6615761</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>

--- a/artfynd/A 9000-2025 artfynd.xlsx
+++ b/artfynd/A 9000-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY50"/>
+  <dimension ref="A1:AY49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122844921</v>
+        <v>122840623</v>
       </c>
       <c r="B5" t="n">
-        <v>79807</v>
+        <v>57494</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,38 +998,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229497</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>676904</v>
+        <v>676932</v>
       </c>
       <c r="R5" t="n">
-        <v>6615766</v>
+        <v>6615725</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122840623</v>
+        <v>122843607</v>
       </c>
       <c r="B6" t="n">
-        <v>57494</v>
+        <v>100621</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,43 +1105,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>676932</v>
+        <v>676666</v>
       </c>
       <c r="R6" t="n">
-        <v>6615725</v>
+        <v>6615819</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122843607</v>
+        <v>122845880</v>
       </c>
       <c r="B7" t="n">
-        <v>100621</v>
+        <v>90962</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,38 +1207,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>676666</v>
+        <v>677085</v>
       </c>
       <c r="R7" t="n">
-        <v>6615819</v>
+        <v>6615732</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122845880</v>
+        <v>122841068</v>
       </c>
       <c r="B8" t="n">
-        <v>90962</v>
+        <v>4867</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,38 +1309,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>101675</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>677085</v>
+        <v>676872</v>
       </c>
       <c r="R8" t="n">
-        <v>6615732</v>
+        <v>6615746</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122841068</v>
+        <v>122841301</v>
       </c>
       <c r="B9" t="n">
-        <v>4867</v>
+        <v>8430</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,21 +1420,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>101675</v>
+        <v>106554</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>676872</v>
+        <v>676893</v>
       </c>
       <c r="R9" t="n">
-        <v>6615746</v>
+        <v>6615790</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,7 +1511,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122841301</v>
+        <v>122842479</v>
       </c>
       <c r="B10" t="n">
         <v>8430</v>
@@ -1547,14 +1552,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>676893</v>
+        <v>676756</v>
       </c>
       <c r="R10" t="n">
-        <v>6615790</v>
+        <v>6615927</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1822,10 +1827,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122842479</v>
+        <v>122842819</v>
       </c>
       <c r="B13" t="n">
-        <v>8430</v>
+        <v>105461</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1838,39 +1843,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106554</v>
+        <v>221144</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>676756</v>
+        <v>676682</v>
       </c>
       <c r="R13" t="n">
-        <v>6615927</v>
+        <v>6615846</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1929,10 +1929,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122840989</v>
+        <v>122845245</v>
       </c>
       <c r="B14" t="n">
-        <v>5173</v>
+        <v>8441</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1945,21 +1945,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1974,10 +1974,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>676899</v>
+        <v>677001</v>
       </c>
       <c r="R14" t="n">
-        <v>6615760</v>
+        <v>6615675</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2036,10 +2036,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122845245</v>
+        <v>122840989</v>
       </c>
       <c r="B15" t="n">
-        <v>8441</v>
+        <v>5173</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2052,21 +2052,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>677001</v>
+        <v>676899</v>
       </c>
       <c r="R15" t="n">
-        <v>6615675</v>
+        <v>6615760</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2143,10 +2143,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122842819</v>
+        <v>122840712</v>
       </c>
       <c r="B16" t="n">
-        <v>105461</v>
+        <v>4867</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2159,37 +2159,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221144</v>
+        <v>101675</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>676682</v>
+        <v>676921</v>
       </c>
       <c r="R16" t="n">
-        <v>6615846</v>
+        <v>6615744</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2245,10 +2250,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122840712</v>
+        <v>122842680</v>
       </c>
       <c r="B17" t="n">
-        <v>4867</v>
+        <v>57848</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2261,42 +2266,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>101675</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>676921</v>
+        <v>676711</v>
       </c>
       <c r="R17" t="n">
-        <v>6615744</v>
+        <v>6615822</v>
       </c>
       <c r="S17" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2352,10 +2357,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122842680</v>
+        <v>122843696</v>
       </c>
       <c r="B18" t="n">
-        <v>57848</v>
+        <v>90962</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2364,43 +2369,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103015</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>676711</v>
+        <v>676651</v>
       </c>
       <c r="R18" t="n">
-        <v>6615822</v>
+        <v>6615875</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2459,10 +2459,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122843696</v>
+        <v>122842185</v>
       </c>
       <c r="B19" t="n">
-        <v>90962</v>
+        <v>100621</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2471,38 +2471,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>676651</v>
+        <v>676831</v>
       </c>
       <c r="R19" t="n">
-        <v>6615875</v>
+        <v>6615990</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2561,10 +2561,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122842185</v>
+        <v>122841077</v>
       </c>
       <c r="B20" t="n">
-        <v>100621</v>
+        <v>5193</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2577,34 +2577,43 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>676831</v>
+        <v>676870</v>
       </c>
       <c r="R20" t="n">
-        <v>6615990</v>
+        <v>6615757</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2645,6 +2654,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2663,10 +2673,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122841077</v>
+        <v>122843664</v>
       </c>
       <c r="B21" t="n">
-        <v>5193</v>
+        <v>100621</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2679,43 +2689,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>676870</v>
+        <v>676656</v>
       </c>
       <c r="R21" t="n">
-        <v>6615757</v>
+        <v>6615859</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2756,7 +2757,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2775,10 +2775,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122843664</v>
+        <v>122845736</v>
       </c>
       <c r="B22" t="n">
-        <v>100621</v>
+        <v>8441</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2791,34 +2791,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>676656</v>
+        <v>677104</v>
       </c>
       <c r="R22" t="n">
-        <v>6615859</v>
+        <v>6615675</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2877,10 +2882,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122845736</v>
+        <v>122842792</v>
       </c>
       <c r="B23" t="n">
-        <v>8441</v>
+        <v>90909</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2893,39 +2898,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>677104</v>
+        <v>676683</v>
       </c>
       <c r="R23" t="n">
-        <v>6615675</v>
+        <v>6615843</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122842792</v>
+        <v>122841332</v>
       </c>
       <c r="B24" t="n">
-        <v>90909</v>
+        <v>57494</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2996,38 +2996,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>676683</v>
+        <v>676864</v>
       </c>
       <c r="R24" t="n">
-        <v>6615843</v>
+        <v>6615776</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3509,10 +3514,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122841332</v>
+        <v>122841097</v>
       </c>
       <c r="B29" t="n">
-        <v>57494</v>
+        <v>5173</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3521,31 +3526,31 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3554,10 +3559,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>676864</v>
+        <v>676861</v>
       </c>
       <c r="R29" t="n">
-        <v>6615776</v>
+        <v>6615758</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3616,10 +3621,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122841097</v>
+        <v>122842133</v>
       </c>
       <c r="B30" t="n">
-        <v>5173</v>
+        <v>100621</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3632,39 +3637,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>676861</v>
+        <v>676838</v>
       </c>
       <c r="R30" t="n">
-        <v>6615758</v>
+        <v>6615977</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3723,7 +3723,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122842133</v>
+        <v>122842144</v>
       </c>
       <c r="B31" t="n">
         <v>100621</v>
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>676838</v>
+        <v>676841</v>
       </c>
       <c r="R31" t="n">
-        <v>6615977</v>
+        <v>6615983</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3825,7 +3825,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122842144</v>
+        <v>122842088</v>
       </c>
       <c r="B32" t="n">
         <v>100621</v>
@@ -3865,10 +3865,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>676841</v>
+        <v>676779</v>
       </c>
       <c r="R32" t="n">
-        <v>6615983</v>
+        <v>6615963</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3927,10 +3927,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122842088</v>
+        <v>122842950</v>
       </c>
       <c r="B33" t="n">
-        <v>100621</v>
+        <v>105461</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3943,34 +3943,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>676779</v>
+        <v>676690</v>
       </c>
       <c r="R33" t="n">
-        <v>6615963</v>
+        <v>6615799</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4029,10 +4029,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122842950</v>
+        <v>122845926</v>
       </c>
       <c r="B34" t="n">
-        <v>105461</v>
+        <v>90909</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4045,34 +4045,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221144</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>676690</v>
+        <v>677084</v>
       </c>
       <c r="R34" t="n">
-        <v>6615799</v>
+        <v>6615718</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4131,7 +4131,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122845926</v>
+        <v>122845093</v>
       </c>
       <c r="B35" t="n">
         <v>90909</v>
@@ -4171,7 +4171,7 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>677084</v>
+        <v>676956</v>
       </c>
       <c r="R35" t="n">
         <v>6615718</v>
@@ -4233,10 +4233,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122845093</v>
+        <v>122842832</v>
       </c>
       <c r="B36" t="n">
-        <v>90909</v>
+        <v>57631</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4245,41 +4245,46 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>676956</v>
+        <v>676682</v>
       </c>
       <c r="R36" t="n">
-        <v>6615718</v>
+        <v>6615846</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4335,10 +4340,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122842832</v>
+        <v>122840495</v>
       </c>
       <c r="B37" t="n">
-        <v>57631</v>
+        <v>5193</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4347,46 +4352,46 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>105930</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>676682</v>
+        <v>676936</v>
       </c>
       <c r="R37" t="n">
-        <v>6615846</v>
+        <v>6615736</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4442,10 +4447,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122840495</v>
+        <v>122842206</v>
       </c>
       <c r="B38" t="n">
-        <v>5193</v>
+        <v>100621</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4458,39 +4463,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>676936</v>
+        <v>676816</v>
       </c>
       <c r="R38" t="n">
-        <v>6615736</v>
+        <v>6615981</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4549,10 +4549,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122842206</v>
+        <v>122842557</v>
       </c>
       <c r="B39" t="n">
-        <v>100621</v>
+        <v>90944</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4561,25 +4561,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4589,10 +4589,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>676816</v>
+        <v>676745</v>
       </c>
       <c r="R39" t="n">
-        <v>6615981</v>
+        <v>6615878</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4651,10 +4651,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122842557</v>
+        <v>122842748</v>
       </c>
       <c r="B40" t="n">
-        <v>90944</v>
+        <v>5193</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4663,38 +4663,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>676745</v>
+        <v>676684</v>
       </c>
       <c r="R40" t="n">
-        <v>6615878</v>
+        <v>6615835</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4753,10 +4758,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122842748</v>
+        <v>122842401</v>
       </c>
       <c r="B41" t="n">
-        <v>5193</v>
+        <v>57494</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4765,20 +4770,20 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4789,19 +4794,19 @@
       <c r="I41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>676684</v>
+        <v>676742</v>
       </c>
       <c r="R41" t="n">
-        <v>6615835</v>
+        <v>6615954</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4860,10 +4865,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122842401</v>
+        <v>122840896</v>
       </c>
       <c r="B42" t="n">
-        <v>57494</v>
+        <v>5358</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4876,39 +4881,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>101728</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>676742</v>
+        <v>676913</v>
       </c>
       <c r="R42" t="n">
-        <v>6615954</v>
+        <v>6615766</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5283,7 +5288,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122840896</v>
+        <v>122840804</v>
       </c>
       <c r="B46" t="n">
         <v>5358</v>
@@ -5328,10 +5333,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>676913</v>
+        <v>676921</v>
       </c>
       <c r="R46" t="n">
-        <v>6615766</v>
+        <v>6615744</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5390,10 +5395,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122840804</v>
+        <v>122841986</v>
       </c>
       <c r="B47" t="n">
-        <v>5358</v>
+        <v>105461</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5402,43 +5407,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>101728</v>
+        <v>221144</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>676921</v>
+        <v>676779</v>
       </c>
       <c r="R47" t="n">
-        <v>6615744</v>
+        <v>6615963</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5497,10 +5497,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122841986</v>
+        <v>122840930</v>
       </c>
       <c r="B48" t="n">
-        <v>105461</v>
+        <v>57494</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5509,38 +5509,43 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>676779</v>
+        <v>676913</v>
       </c>
       <c r="R48" t="n">
-        <v>6615963</v>
+        <v>6615763</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5599,10 +5604,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122840930</v>
+        <v>122840922</v>
       </c>
       <c r="B49" t="n">
-        <v>57494</v>
+        <v>105461</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5611,43 +5616,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>676913</v>
+        <v>676912</v>
       </c>
       <c r="R49" t="n">
-        <v>6615763</v>
+        <v>6615761</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5703,108 +5703,6 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>122840922</v>
-      </c>
-      <c r="B50" t="n">
-        <v>105461</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>221144</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Grönpyrola</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Pyrola chlorantha</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>Lugnet, Lugnet, Upl</t>
-        </is>
-      </c>
-      <c r="Q50" t="n">
-        <v>676912</v>
-      </c>
-      <c r="R50" t="n">
-        <v>6615761</v>
-      </c>
-      <c r="S50" t="n">
-        <v>10</v>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>Stockholm</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>Vallentuna</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>Frösunda</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AD50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT50" t="inlineStr"/>
-      <c r="AW50" t="inlineStr">
-        <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9000-2025 artfynd.xlsx
+++ b/artfynd/A 9000-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122840992</v>
+        <v>122840972</v>
       </c>
       <c r="B2" t="n">
         <v>90944</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>676900</v>
+        <v>676898</v>
       </c>
       <c r="R2" t="n">
-        <v>6615757</v>
+        <v>6615759</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122840972</v>
+        <v>122845245</v>
       </c>
       <c r="B3" t="n">
-        <v>90944</v>
+        <v>8441</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>676898</v>
+        <v>677001</v>
       </c>
       <c r="R3" t="n">
-        <v>6615759</v>
+        <v>6615675</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122840378</v>
+        <v>122841986</v>
       </c>
       <c r="B4" t="n">
-        <v>57848</v>
+        <v>105461</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,39 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>676985</v>
+        <v>676779</v>
       </c>
       <c r="R4" t="n">
-        <v>6615696</v>
+        <v>6615963</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122840623</v>
+        <v>122845880</v>
       </c>
       <c r="B5" t="n">
-        <v>57494</v>
+        <v>90962</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,39 +1002,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>676932</v>
+        <v>677085</v>
       </c>
       <c r="R5" t="n">
-        <v>6615725</v>
+        <v>6615732</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122843607</v>
+        <v>122843888</v>
       </c>
       <c r="B6" t="n">
-        <v>100621</v>
+        <v>8430</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,34 +1104,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>676666</v>
+        <v>676813</v>
       </c>
       <c r="R6" t="n">
-        <v>6615819</v>
+        <v>6615903</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1177,6 +1181,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1195,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122845880</v>
+        <v>122842832</v>
       </c>
       <c r="B7" t="n">
-        <v>90962</v>
+        <v>57631</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,37 +1216,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>677085</v>
+        <v>676682</v>
       </c>
       <c r="R7" t="n">
-        <v>6615732</v>
+        <v>6615846</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1297,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122841068</v>
+        <v>122842642</v>
       </c>
       <c r="B8" t="n">
-        <v>4867</v>
+        <v>100621</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,39 +1323,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>101675</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>676872</v>
+        <v>676714</v>
       </c>
       <c r="R8" t="n">
-        <v>6615746</v>
+        <v>6615824</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122841301</v>
+        <v>122842133</v>
       </c>
       <c r="B9" t="n">
-        <v>8430</v>
+        <v>100621</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1420,39 +1425,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>676893</v>
+        <v>676838</v>
       </c>
       <c r="R9" t="n">
-        <v>6615790</v>
+        <v>6615977</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1511,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122842479</v>
+        <v>122845448</v>
       </c>
       <c r="B10" t="n">
-        <v>8430</v>
+        <v>105461</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,39 +1527,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106554</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>676756</v>
+        <v>676972</v>
       </c>
       <c r="R10" t="n">
-        <v>6615927</v>
+        <v>6615705</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1618,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122843861</v>
+        <v>122843696</v>
       </c>
       <c r="B11" t="n">
-        <v>57494</v>
+        <v>90962</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1634,39 +1629,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>676804</v>
+        <v>676651</v>
       </c>
       <c r="R11" t="n">
-        <v>6615893</v>
+        <v>6615875</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1725,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122845448</v>
+        <v>122841097</v>
       </c>
       <c r="B12" t="n">
-        <v>105461</v>
+        <v>5173</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1741,34 +1731,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>100526</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>676972</v>
+        <v>676861</v>
       </c>
       <c r="R12" t="n">
-        <v>6615705</v>
+        <v>6615758</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1827,10 +1822,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122842819</v>
+        <v>122842792</v>
       </c>
       <c r="B13" t="n">
-        <v>105461</v>
+        <v>90909</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1843,21 +1838,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221144</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1867,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>676682</v>
+        <v>676683</v>
       </c>
       <c r="R13" t="n">
-        <v>6615846</v>
+        <v>6615843</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1929,10 +1924,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122845245</v>
+        <v>122845288</v>
       </c>
       <c r="B14" t="n">
-        <v>8441</v>
+        <v>8430</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1945,21 +1940,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1974,10 +1969,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>677001</v>
+        <v>677007</v>
       </c>
       <c r="R14" t="n">
-        <v>6615675</v>
+        <v>6615684</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2036,10 +2031,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122840989</v>
+        <v>122845736</v>
       </c>
       <c r="B15" t="n">
-        <v>5173</v>
+        <v>8441</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2052,21 +2047,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2081,10 +2076,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>676899</v>
+        <v>677104</v>
       </c>
       <c r="R15" t="n">
-        <v>6615760</v>
+        <v>6615675</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2143,10 +2138,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122840712</v>
+        <v>122840992</v>
       </c>
       <c r="B16" t="n">
-        <v>4867</v>
+        <v>90944</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2155,46 +2150,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>101675</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>676921</v>
+        <v>676900</v>
       </c>
       <c r="R16" t="n">
-        <v>6615744</v>
+        <v>6615757</v>
       </c>
       <c r="S16" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2250,10 +2240,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122842680</v>
+        <v>122842434</v>
       </c>
       <c r="B17" t="n">
-        <v>57848</v>
+        <v>57494</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2262,20 +2252,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2286,7 +2276,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2295,10 +2285,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>676711</v>
+        <v>676739</v>
       </c>
       <c r="R17" t="n">
-        <v>6615822</v>
+        <v>6615944</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2357,10 +2347,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122843696</v>
+        <v>122842950</v>
       </c>
       <c r="B18" t="n">
-        <v>90962</v>
+        <v>105461</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2369,25 +2359,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2397,10 +2387,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>676651</v>
+        <v>676690</v>
       </c>
       <c r="R18" t="n">
-        <v>6615875</v>
+        <v>6615799</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2459,10 +2449,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122842185</v>
+        <v>122840495</v>
       </c>
       <c r="B19" t="n">
-        <v>100621</v>
+        <v>5193</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2475,34 +2465,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>676831</v>
+        <v>676936</v>
       </c>
       <c r="R19" t="n">
-        <v>6615990</v>
+        <v>6615736</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2561,10 +2556,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122841077</v>
+        <v>122841332</v>
       </c>
       <c r="B20" t="n">
-        <v>5193</v>
+        <v>57494</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2573,20 +2568,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2595,25 +2590,21 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>676870</v>
+        <v>676864</v>
       </c>
       <c r="R20" t="n">
-        <v>6615757</v>
+        <v>6615776</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2654,7 +2645,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2673,10 +2663,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122843664</v>
+        <v>122841068</v>
       </c>
       <c r="B21" t="n">
-        <v>100621</v>
+        <v>4867</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2689,34 +2679,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>101675</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>676656</v>
+        <v>676872</v>
       </c>
       <c r="R21" t="n">
-        <v>6615859</v>
+        <v>6615746</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2775,10 +2770,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122845736</v>
+        <v>122841301</v>
       </c>
       <c r="B22" t="n">
-        <v>8441</v>
+        <v>8430</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2791,21 +2786,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2820,10 +2815,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>677104</v>
+        <v>676893</v>
       </c>
       <c r="R22" t="n">
-        <v>6615675</v>
+        <v>6615790</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2882,10 +2877,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122842792</v>
+        <v>122840989</v>
       </c>
       <c r="B23" t="n">
-        <v>90909</v>
+        <v>5173</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2898,34 +2893,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>676683</v>
+        <v>676899</v>
       </c>
       <c r="R23" t="n">
-        <v>6615843</v>
+        <v>6615760</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2984,7 +2984,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122841332</v>
+        <v>122840392</v>
       </c>
       <c r="B24" t="n">
         <v>57494</v>
@@ -3020,7 +3020,7 @@
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3029,10 +3029,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>676864</v>
+        <v>676983</v>
       </c>
       <c r="R24" t="n">
-        <v>6615776</v>
+        <v>6615701</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3091,10 +3091,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122842273</v>
+        <v>122840378</v>
       </c>
       <c r="B25" t="n">
-        <v>100621</v>
+        <v>57848</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3107,34 +3107,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>676787</v>
+        <v>676985</v>
       </c>
       <c r="R25" t="n">
-        <v>6615980</v>
+        <v>6615696</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3193,10 +3198,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122842642</v>
+        <v>122842748</v>
       </c>
       <c r="B26" t="n">
-        <v>100621</v>
+        <v>5193</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3209,34 +3214,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>676714</v>
+        <v>676684</v>
       </c>
       <c r="R26" t="n">
-        <v>6615824</v>
+        <v>6615835</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3295,10 +3305,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122845288</v>
+        <v>122842273</v>
       </c>
       <c r="B27" t="n">
-        <v>8430</v>
+        <v>100621</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3311,39 +3321,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>677007</v>
+        <v>676787</v>
       </c>
       <c r="R27" t="n">
-        <v>6615684</v>
+        <v>6615980</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3402,7 +3407,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122843888</v>
+        <v>122842479</v>
       </c>
       <c r="B28" t="n">
         <v>8430</v>
@@ -3436,25 +3441,21 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>676813</v>
+        <v>676756</v>
       </c>
       <c r="R28" t="n">
-        <v>6615903</v>
+        <v>6615927</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3495,7 +3496,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3514,10 +3514,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122841097</v>
+        <v>122845093</v>
       </c>
       <c r="B29" t="n">
-        <v>5173</v>
+        <v>90909</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3530,39 +3530,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>676861</v>
+        <v>676956</v>
       </c>
       <c r="R29" t="n">
-        <v>6615758</v>
+        <v>6615718</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3621,10 +3616,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122842133</v>
+        <v>122840930</v>
       </c>
       <c r="B30" t="n">
-        <v>100621</v>
+        <v>57494</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3633,38 +3628,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>676838</v>
+        <v>676913</v>
       </c>
       <c r="R30" t="n">
-        <v>6615977</v>
+        <v>6615763</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3723,7 +3723,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122842144</v>
+        <v>122842206</v>
       </c>
       <c r="B31" t="n">
         <v>100621</v>
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>676841</v>
+        <v>676816</v>
       </c>
       <c r="R31" t="n">
-        <v>6615983</v>
+        <v>6615981</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3825,7 +3825,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122842088</v>
+        <v>122842185</v>
       </c>
       <c r="B32" t="n">
         <v>100621</v>
@@ -3865,10 +3865,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>676779</v>
+        <v>676831</v>
       </c>
       <c r="R32" t="n">
-        <v>6615963</v>
+        <v>6615990</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3927,10 +3927,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122842950</v>
+        <v>122840896</v>
       </c>
       <c r="B33" t="n">
-        <v>105461</v>
+        <v>5358</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3939,38 +3939,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221144</v>
+        <v>101728</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>676690</v>
+        <v>676913</v>
       </c>
       <c r="R33" t="n">
-        <v>6615799</v>
+        <v>6615766</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4029,10 +4034,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122845926</v>
+        <v>122841077</v>
       </c>
       <c r="B34" t="n">
-        <v>90909</v>
+        <v>5193</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4045,34 +4050,43 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>105930</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>677084</v>
+        <v>676870</v>
       </c>
       <c r="R34" t="n">
-        <v>6615718</v>
+        <v>6615757</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4113,6 +4127,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4131,10 +4146,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122845093</v>
+        <v>122840712</v>
       </c>
       <c r="B35" t="n">
-        <v>90909</v>
+        <v>4867</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4147,37 +4162,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>101675</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>676956</v>
+        <v>676921</v>
       </c>
       <c r="R35" t="n">
-        <v>6615718</v>
+        <v>6615744</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4233,10 +4253,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122842832</v>
+        <v>122843861</v>
       </c>
       <c r="B36" t="n">
-        <v>57631</v>
+        <v>57494</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4249,42 +4269,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>676682</v>
+        <v>676804</v>
       </c>
       <c r="R36" t="n">
-        <v>6615846</v>
+        <v>6615893</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4340,10 +4360,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122840495</v>
+        <v>122842144</v>
       </c>
       <c r="B37" t="n">
-        <v>5193</v>
+        <v>100621</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4356,39 +4376,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>676936</v>
+        <v>676841</v>
       </c>
       <c r="R37" t="n">
-        <v>6615736</v>
+        <v>6615983</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4447,10 +4462,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122842206</v>
+        <v>122840623</v>
       </c>
       <c r="B38" t="n">
-        <v>100621</v>
+        <v>57494</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4459,38 +4474,43 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>676816</v>
+        <v>676932</v>
       </c>
       <c r="R38" t="n">
-        <v>6615981</v>
+        <v>6615725</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4549,10 +4569,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122842557</v>
+        <v>122843607</v>
       </c>
       <c r="B39" t="n">
-        <v>90944</v>
+        <v>100621</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4561,38 +4581,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>676745</v>
+        <v>676666</v>
       </c>
       <c r="R39" t="n">
-        <v>6615878</v>
+        <v>6615819</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4651,10 +4671,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122842748</v>
+        <v>122842401</v>
       </c>
       <c r="B40" t="n">
-        <v>5193</v>
+        <v>57494</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4663,20 +4683,20 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4687,19 +4707,19 @@
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>676684</v>
+        <v>676742</v>
       </c>
       <c r="R40" t="n">
-        <v>6615835</v>
+        <v>6615954</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4758,10 +4778,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122842401</v>
+        <v>122843664</v>
       </c>
       <c r="B41" t="n">
-        <v>57494</v>
+        <v>100621</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4770,43 +4790,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>676742</v>
+        <v>676656</v>
       </c>
       <c r="R41" t="n">
-        <v>6615954</v>
+        <v>6615859</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4865,10 +4880,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122840896</v>
+        <v>122842557</v>
       </c>
       <c r="B42" t="n">
-        <v>5358</v>
+        <v>90944</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4881,39 +4896,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>101728</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>676913</v>
+        <v>676745</v>
       </c>
       <c r="R42" t="n">
-        <v>6615766</v>
+        <v>6615878</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4972,10 +4982,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122840652</v>
+        <v>122840804</v>
       </c>
       <c r="B43" t="n">
-        <v>90909</v>
+        <v>5358</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4984,38 +4994,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5447</v>
+        <v>101728</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>676670</v>
+        <v>676921</v>
       </c>
       <c r="R43" t="n">
-        <v>6615860</v>
+        <v>6615744</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5074,10 +5089,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122840392</v>
+        <v>122842819</v>
       </c>
       <c r="B44" t="n">
-        <v>57494</v>
+        <v>105461</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5086,43 +5101,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>676983</v>
+        <v>676682</v>
       </c>
       <c r="R44" t="n">
-        <v>6615701</v>
+        <v>6615846</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5181,10 +5191,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122842434</v>
+        <v>122840652</v>
       </c>
       <c r="B45" t="n">
-        <v>57494</v>
+        <v>90909</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5193,43 +5203,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>676739</v>
+        <v>676670</v>
       </c>
       <c r="R45" t="n">
-        <v>6615944</v>
+        <v>6615860</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5288,10 +5293,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122840804</v>
+        <v>122845926</v>
       </c>
       <c r="B46" t="n">
-        <v>5358</v>
+        <v>90909</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5300,43 +5305,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>101728</v>
+        <v>5447</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>676921</v>
+        <v>677084</v>
       </c>
       <c r="R46" t="n">
-        <v>6615744</v>
+        <v>6615718</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5395,10 +5395,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122841986</v>
+        <v>122842088</v>
       </c>
       <c r="B47" t="n">
-        <v>105461</v>
+        <v>100621</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5411,21 +5411,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5497,10 +5497,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122840930</v>
+        <v>122842680</v>
       </c>
       <c r="B48" t="n">
-        <v>57494</v>
+        <v>57848</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5509,20 +5509,20 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5533,19 +5533,19 @@
       <c r="I48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>676913</v>
+        <v>676711</v>
       </c>
       <c r="R48" t="n">
-        <v>6615763</v>
+        <v>6615822</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>

--- a/artfynd/A 9000-2025 artfynd.xlsx
+++ b/artfynd/A 9000-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122840972</v>
+        <v>122842185</v>
       </c>
       <c r="B2" t="n">
-        <v>90944</v>
+        <v>100623</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>676898</v>
+        <v>676831</v>
       </c>
       <c r="R2" t="n">
-        <v>6615759</v>
+        <v>6615990</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122845245</v>
+        <v>122845736</v>
       </c>
       <c r="B3" t="n">
         <v>8441</v>
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>677001</v>
+        <v>677104</v>
       </c>
       <c r="R3" t="n">
         <v>6615675</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122841986</v>
+        <v>122842792</v>
       </c>
       <c r="B4" t="n">
-        <v>105461</v>
+        <v>90909</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,34 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>676779</v>
+        <v>676683</v>
       </c>
       <c r="R4" t="n">
-        <v>6615963</v>
+        <v>6615843</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122843888</v>
+        <v>122840989</v>
       </c>
       <c r="B6" t="n">
-        <v>8430</v>
+        <v>5173</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,43 +1104,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>676813</v>
+        <v>676899</v>
       </c>
       <c r="R6" t="n">
-        <v>6615903</v>
+        <v>6615760</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1181,7 +1177,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1200,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122842832</v>
+        <v>122842680</v>
       </c>
       <c r="B7" t="n">
-        <v>57631</v>
+        <v>57848</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1212,46 +1207,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>676682</v>
+        <v>676711</v>
       </c>
       <c r="R7" t="n">
-        <v>6615846</v>
+        <v>6615822</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1307,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122842642</v>
+        <v>122841077</v>
       </c>
       <c r="B8" t="n">
-        <v>100621</v>
+        <v>5193</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,34 +1318,43 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>676714</v>
+        <v>676870</v>
       </c>
       <c r="R8" t="n">
-        <v>6615824</v>
+        <v>6615757</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1391,6 +1395,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1409,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122842133</v>
+        <v>122840495</v>
       </c>
       <c r="B9" t="n">
-        <v>100621</v>
+        <v>5193</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,34 +1430,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>676838</v>
+        <v>676936</v>
       </c>
       <c r="R9" t="n">
-        <v>6615977</v>
+        <v>6615736</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1511,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122845448</v>
+        <v>122842088</v>
       </c>
       <c r="B10" t="n">
-        <v>105461</v>
+        <v>100623</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,34 +1537,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>676972</v>
+        <v>676779</v>
       </c>
       <c r="R10" t="n">
-        <v>6615705</v>
+        <v>6615963</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1613,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122843696</v>
+        <v>122842950</v>
       </c>
       <c r="B11" t="n">
-        <v>90962</v>
+        <v>105463</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1625,25 +1635,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1653,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>676651</v>
+        <v>676690</v>
       </c>
       <c r="R11" t="n">
-        <v>6615875</v>
+        <v>6615799</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122841097</v>
+        <v>122842557</v>
       </c>
       <c r="B12" t="n">
-        <v>5173</v>
+        <v>90944</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1727,43 +1737,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>676861</v>
+        <v>676745</v>
       </c>
       <c r="R12" t="n">
-        <v>6615758</v>
+        <v>6615878</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1822,10 +1827,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122842792</v>
+        <v>122842144</v>
       </c>
       <c r="B13" t="n">
-        <v>90909</v>
+        <v>100623</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1838,34 +1843,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>676683</v>
+        <v>676841</v>
       </c>
       <c r="R13" t="n">
-        <v>6615843</v>
+        <v>6615983</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1924,10 +1929,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122845288</v>
+        <v>122840392</v>
       </c>
       <c r="B14" t="n">
-        <v>8430</v>
+        <v>57494</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1936,31 +1941,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1969,10 +1974,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>677007</v>
+        <v>676983</v>
       </c>
       <c r="R14" t="n">
-        <v>6615684</v>
+        <v>6615701</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2031,10 +2036,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122845736</v>
+        <v>122840712</v>
       </c>
       <c r="B15" t="n">
-        <v>8441</v>
+        <v>4867</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2047,21 +2052,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>101675</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2076,13 +2081,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>677104</v>
+        <v>676921</v>
       </c>
       <c r="R15" t="n">
-        <v>6615675</v>
+        <v>6615744</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2138,10 +2143,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122840992</v>
+        <v>122840804</v>
       </c>
       <c r="B16" t="n">
-        <v>90944</v>
+        <v>5358</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2154,34 +2159,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>101728</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>676900</v>
+        <v>676921</v>
       </c>
       <c r="R16" t="n">
-        <v>6615757</v>
+        <v>6615744</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2240,10 +2250,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122842434</v>
+        <v>122842273</v>
       </c>
       <c r="B17" t="n">
-        <v>57494</v>
+        <v>100623</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2252,43 +2262,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>676739</v>
+        <v>676787</v>
       </c>
       <c r="R17" t="n">
-        <v>6615944</v>
+        <v>6615980</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2347,10 +2352,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122842950</v>
+        <v>122842819</v>
       </c>
       <c r="B18" t="n">
-        <v>105461</v>
+        <v>105463</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2387,10 +2392,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>676690</v>
+        <v>676682</v>
       </c>
       <c r="R18" t="n">
-        <v>6615799</v>
+        <v>6615846</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2449,10 +2454,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122840495</v>
+        <v>122845448</v>
       </c>
       <c r="B19" t="n">
-        <v>5193</v>
+        <v>105463</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2465,39 +2470,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>105930</v>
+        <v>221144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>676936</v>
+        <v>676972</v>
       </c>
       <c r="R19" t="n">
-        <v>6615736</v>
+        <v>6615705</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2556,7 +2556,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122841332</v>
+        <v>122840930</v>
       </c>
       <c r="B20" t="n">
         <v>57494</v>
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>676864</v>
+        <v>676913</v>
       </c>
       <c r="R20" t="n">
-        <v>6615776</v>
+        <v>6615763</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2663,10 +2663,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122841068</v>
+        <v>122842401</v>
       </c>
       <c r="B21" t="n">
-        <v>4867</v>
+        <v>57494</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2675,43 +2675,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>101675</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>676872</v>
+        <v>676742</v>
       </c>
       <c r="R21" t="n">
-        <v>6615746</v>
+        <v>6615954</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2770,7 +2770,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122841301</v>
+        <v>122845288</v>
       </c>
       <c r="B22" t="n">
         <v>8430</v>
@@ -2815,10 +2815,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>676893</v>
+        <v>677007</v>
       </c>
       <c r="R22" t="n">
-        <v>6615790</v>
+        <v>6615684</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2877,10 +2877,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122840989</v>
+        <v>122841301</v>
       </c>
       <c r="B23" t="n">
-        <v>5173</v>
+        <v>8430</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2893,21 +2893,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100526</v>
+        <v>106554</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2922,10 +2922,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>676899</v>
+        <v>676893</v>
       </c>
       <c r="R23" t="n">
-        <v>6615760</v>
+        <v>6615790</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122840392</v>
+        <v>122842479</v>
       </c>
       <c r="B24" t="n">
-        <v>57494</v>
+        <v>8430</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2996,43 +2996,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>676983</v>
+        <v>676756</v>
       </c>
       <c r="R24" t="n">
-        <v>6615701</v>
+        <v>6615927</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3091,10 +3091,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122840378</v>
+        <v>122842206</v>
       </c>
       <c r="B25" t="n">
-        <v>57848</v>
+        <v>100623</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3107,39 +3107,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>676985</v>
+        <v>676816</v>
       </c>
       <c r="R25" t="n">
-        <v>6615696</v>
+        <v>6615981</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3198,10 +3193,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122842748</v>
+        <v>122840652</v>
       </c>
       <c r="B26" t="n">
-        <v>5193</v>
+        <v>90909</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3214,39 +3209,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>105930</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>676684</v>
+        <v>676670</v>
       </c>
       <c r="R26" t="n">
-        <v>6615835</v>
+        <v>6615860</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3305,10 +3295,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122842273</v>
+        <v>122843861</v>
       </c>
       <c r="B27" t="n">
-        <v>100621</v>
+        <v>57494</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3317,38 +3307,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>676787</v>
+        <v>676804</v>
       </c>
       <c r="R27" t="n">
-        <v>6615980</v>
+        <v>6615893</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3407,10 +3402,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122842479</v>
+        <v>122840896</v>
       </c>
       <c r="B28" t="n">
-        <v>8430</v>
+        <v>5358</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3419,25 +3414,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106554</v>
+        <v>101728</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3448,14 +3443,14 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>676756</v>
+        <v>676913</v>
       </c>
       <c r="R28" t="n">
-        <v>6615927</v>
+        <v>6615766</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3514,10 +3509,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122845093</v>
+        <v>122842133</v>
       </c>
       <c r="B29" t="n">
-        <v>90909</v>
+        <v>100623</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3530,34 +3525,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>676956</v>
+        <v>676838</v>
       </c>
       <c r="R29" t="n">
-        <v>6615718</v>
+        <v>6615977</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3616,10 +3611,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122840930</v>
+        <v>122845926</v>
       </c>
       <c r="B30" t="n">
-        <v>57494</v>
+        <v>90909</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3628,43 +3623,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>676913</v>
+        <v>677084</v>
       </c>
       <c r="R30" t="n">
-        <v>6615763</v>
+        <v>6615718</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3723,10 +3713,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122842206</v>
+        <v>122841097</v>
       </c>
       <c r="B31" t="n">
-        <v>100621</v>
+        <v>5173</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3739,34 +3729,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>676816</v>
+        <v>676861</v>
       </c>
       <c r="R31" t="n">
-        <v>6615981</v>
+        <v>6615758</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3825,10 +3820,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122842185</v>
+        <v>122840378</v>
       </c>
       <c r="B32" t="n">
-        <v>100621</v>
+        <v>57848</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3841,34 +3836,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>676831</v>
+        <v>676985</v>
       </c>
       <c r="R32" t="n">
-        <v>6615990</v>
+        <v>6615696</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3927,10 +3927,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122840896</v>
+        <v>122842832</v>
       </c>
       <c r="B33" t="n">
-        <v>5358</v>
+        <v>57631</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3943,42 +3943,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>101728</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>676913</v>
+        <v>676682</v>
       </c>
       <c r="R33" t="n">
-        <v>6615766</v>
+        <v>6615846</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4034,10 +4034,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122841077</v>
+        <v>122842642</v>
       </c>
       <c r="B34" t="n">
-        <v>5193</v>
+        <v>100623</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4050,43 +4050,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>676870</v>
+        <v>676714</v>
       </c>
       <c r="R34" t="n">
-        <v>6615757</v>
+        <v>6615824</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4127,7 +4118,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4146,10 +4136,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122840712</v>
+        <v>122840623</v>
       </c>
       <c r="B35" t="n">
-        <v>4867</v>
+        <v>57494</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4158,31 +4148,31 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>101675</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4191,13 +4181,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>676921</v>
+        <v>676932</v>
       </c>
       <c r="R35" t="n">
-        <v>6615744</v>
+        <v>6615725</v>
       </c>
       <c r="S35" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4253,10 +4243,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122843861</v>
+        <v>122840972</v>
       </c>
       <c r="B36" t="n">
-        <v>57494</v>
+        <v>90944</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4269,39 +4259,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>676804</v>
+        <v>676898</v>
       </c>
       <c r="R36" t="n">
-        <v>6615893</v>
+        <v>6615759</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4360,10 +4345,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122842144</v>
+        <v>122843664</v>
       </c>
       <c r="B37" t="n">
-        <v>100621</v>
+        <v>100623</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4396,14 +4381,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>676841</v>
+        <v>676656</v>
       </c>
       <c r="R37" t="n">
-        <v>6615983</v>
+        <v>6615859</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4462,10 +4447,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122840623</v>
+        <v>122842748</v>
       </c>
       <c r="B38" t="n">
-        <v>57494</v>
+        <v>5193</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4474,20 +4459,20 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4498,19 +4483,19 @@
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>676932</v>
+        <v>676684</v>
       </c>
       <c r="R38" t="n">
-        <v>6615725</v>
+        <v>6615835</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4569,10 +4554,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122843607</v>
+        <v>122841068</v>
       </c>
       <c r="B39" t="n">
-        <v>100621</v>
+        <v>4867</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4585,34 +4570,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>101675</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>676666</v>
+        <v>676872</v>
       </c>
       <c r="R39" t="n">
-        <v>6615819</v>
+        <v>6615746</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4671,10 +4661,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122842401</v>
+        <v>122845245</v>
       </c>
       <c r="B40" t="n">
-        <v>57494</v>
+        <v>8441</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4683,43 +4673,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>676742</v>
+        <v>677001</v>
       </c>
       <c r="R40" t="n">
-        <v>6615954</v>
+        <v>6615675</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4778,10 +4768,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122843664</v>
+        <v>122843888</v>
       </c>
       <c r="B41" t="n">
-        <v>100621</v>
+        <v>8430</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4794,34 +4784,43 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>676656</v>
+        <v>676813</v>
       </c>
       <c r="R41" t="n">
-        <v>6615859</v>
+        <v>6615903</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4862,6 +4861,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4880,10 +4880,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122842557</v>
+        <v>122841986</v>
       </c>
       <c r="B42" t="n">
-        <v>90944</v>
+        <v>105463</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4892,25 +4892,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4920,10 +4920,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>676745</v>
+        <v>676779</v>
       </c>
       <c r="R42" t="n">
-        <v>6615878</v>
+        <v>6615963</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4982,10 +4982,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122840804</v>
+        <v>122840922</v>
       </c>
       <c r="B43" t="n">
-        <v>5358</v>
+        <v>105463</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4994,43 +4994,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>101728</v>
+        <v>221144</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>676921</v>
+        <v>676912</v>
       </c>
       <c r="R43" t="n">
-        <v>6615744</v>
+        <v>6615761</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5089,10 +5084,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122842819</v>
+        <v>122843696</v>
       </c>
       <c r="B44" t="n">
-        <v>105461</v>
+        <v>90962</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5101,25 +5096,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221144</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5129,10 +5124,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>676682</v>
+        <v>676651</v>
       </c>
       <c r="R44" t="n">
-        <v>6615846</v>
+        <v>6615875</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5191,7 +5186,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122840652</v>
+        <v>122845093</v>
       </c>
       <c r="B45" t="n">
         <v>90909</v>
@@ -5227,14 +5222,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>676670</v>
+        <v>676956</v>
       </c>
       <c r="R45" t="n">
-        <v>6615860</v>
+        <v>6615718</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5293,10 +5288,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122845926</v>
+        <v>122842434</v>
       </c>
       <c r="B46" t="n">
-        <v>90909</v>
+        <v>57494</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5305,38 +5300,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>677084</v>
+        <v>676739</v>
       </c>
       <c r="R46" t="n">
-        <v>6615718</v>
+        <v>6615944</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5395,10 +5395,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122842088</v>
+        <v>122840992</v>
       </c>
       <c r="B47" t="n">
-        <v>100621</v>
+        <v>90944</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5407,38 +5407,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>676779</v>
+        <v>676900</v>
       </c>
       <c r="R47" t="n">
-        <v>6615963</v>
+        <v>6615757</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5497,10 +5497,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122842680</v>
+        <v>122843607</v>
       </c>
       <c r="B48" t="n">
-        <v>57848</v>
+        <v>100623</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5513,39 +5513,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>676711</v>
+        <v>676666</v>
       </c>
       <c r="R48" t="n">
-        <v>6615822</v>
+        <v>6615819</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5604,10 +5599,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122840922</v>
+        <v>122841332</v>
       </c>
       <c r="B49" t="n">
-        <v>105461</v>
+        <v>57494</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5616,38 +5611,43 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>676912</v>
+        <v>676864</v>
       </c>
       <c r="R49" t="n">
-        <v>6615761</v>
+        <v>6615776</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>

--- a/artfynd/A 9000-2025 artfynd.xlsx
+++ b/artfynd/A 9000-2025 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122845736</v>
+        <v>122842792</v>
       </c>
       <c r="B3" t="n">
-        <v>8441</v>
+        <v>90909</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,39 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>677104</v>
+        <v>676683</v>
       </c>
       <c r="R3" t="n">
-        <v>6615675</v>
+        <v>6615843</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122842792</v>
+        <v>122845736</v>
       </c>
       <c r="B4" t="n">
-        <v>90909</v>
+        <v>8441</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,34 +895,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>676683</v>
+        <v>677104</v>
       </c>
       <c r="R4" t="n">
-        <v>6615843</v>
+        <v>6615675</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1929,10 +1929,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122840392</v>
+        <v>122840712</v>
       </c>
       <c r="B14" t="n">
-        <v>57494</v>
+        <v>4867</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1941,31 +1941,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>101675</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1974,13 +1974,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>676983</v>
+        <v>676921</v>
       </c>
       <c r="R14" t="n">
-        <v>6615701</v>
+        <v>6615744</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2036,10 +2036,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122840712</v>
+        <v>122840804</v>
       </c>
       <c r="B15" t="n">
-        <v>4867</v>
+        <v>5358</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2048,25 +2048,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>101675</v>
+        <v>101728</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2087,7 +2087,7 @@
         <v>6615744</v>
       </c>
       <c r="S15" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2143,10 +2143,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122840804</v>
+        <v>122842273</v>
       </c>
       <c r="B16" t="n">
-        <v>5358</v>
+        <v>100623</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2155,43 +2155,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>101728</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>676921</v>
+        <v>676787</v>
       </c>
       <c r="R16" t="n">
-        <v>6615744</v>
+        <v>6615980</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2250,10 +2245,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122842273</v>
+        <v>122842819</v>
       </c>
       <c r="B17" t="n">
-        <v>100623</v>
+        <v>105463</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2266,34 +2261,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>676787</v>
+        <v>676682</v>
       </c>
       <c r="R17" t="n">
-        <v>6615980</v>
+        <v>6615846</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2352,7 +2347,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122842819</v>
+        <v>122845448</v>
       </c>
       <c r="B18" t="n">
         <v>105463</v>
@@ -2388,14 +2383,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>676682</v>
+        <v>676972</v>
       </c>
       <c r="R18" t="n">
-        <v>6615846</v>
+        <v>6615705</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2454,10 +2449,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122845448</v>
+        <v>122840392</v>
       </c>
       <c r="B19" t="n">
-        <v>105463</v>
+        <v>57494</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2466,38 +2461,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>676972</v>
+        <v>676983</v>
       </c>
       <c r="R19" t="n">
-        <v>6615705</v>
+        <v>6615701</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3927,10 +3927,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122842832</v>
+        <v>122842642</v>
       </c>
       <c r="B33" t="n">
-        <v>57631</v>
+        <v>100623</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3939,46 +3939,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>676682</v>
+        <v>676714</v>
       </c>
       <c r="R33" t="n">
-        <v>6615846</v>
+        <v>6615824</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4034,10 +4029,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122842642</v>
+        <v>122842832</v>
       </c>
       <c r="B34" t="n">
-        <v>100623</v>
+        <v>57631</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4046,41 +4041,46 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>676714</v>
+        <v>676682</v>
       </c>
       <c r="R34" t="n">
-        <v>6615824</v>
+        <v>6615846</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>

--- a/artfynd/A 9000-2025 artfynd.xlsx
+++ b/artfynd/A 9000-2025 artfynd.xlsx
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122845880</v>
+        <v>122840989</v>
       </c>
       <c r="B5" t="n">
-        <v>90962</v>
+        <v>5173</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,38 +998,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>677085</v>
+        <v>676899</v>
       </c>
       <c r="R5" t="n">
-        <v>6615732</v>
+        <v>6615760</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122840989</v>
+        <v>122842680</v>
       </c>
       <c r="B6" t="n">
-        <v>5173</v>
+        <v>57848</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,39 +1109,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>676899</v>
+        <v>676711</v>
       </c>
       <c r="R6" t="n">
-        <v>6615760</v>
+        <v>6615822</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122842680</v>
+        <v>122841077</v>
       </c>
       <c r="B7" t="n">
-        <v>57848</v>
+        <v>5193</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,16 +1216,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>105930</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1229,21 +1234,25 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>676711</v>
+        <v>676870</v>
       </c>
       <c r="R7" t="n">
-        <v>6615822</v>
+        <v>6615757</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1284,6 +1293,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1302,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122841077</v>
+        <v>122840495</v>
       </c>
       <c r="B8" t="n">
         <v>5193</v>
@@ -1336,25 +1346,21 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>676870</v>
+        <v>676936</v>
       </c>
       <c r="R8" t="n">
-        <v>6615757</v>
+        <v>6615736</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1395,7 +1401,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1414,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122840495</v>
+        <v>122845880</v>
       </c>
       <c r="B9" t="n">
-        <v>5193</v>
+        <v>90962</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1426,43 +1431,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>105930</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>676936</v>
+        <v>677085</v>
       </c>
       <c r="R9" t="n">
-        <v>6615736</v>
+        <v>6615732</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -3091,10 +3091,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122842206</v>
+        <v>122840896</v>
       </c>
       <c r="B25" t="n">
-        <v>100623</v>
+        <v>5358</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3103,38 +3103,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>101728</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>676816</v>
+        <v>676913</v>
       </c>
       <c r="R25" t="n">
-        <v>6615981</v>
+        <v>6615766</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3402,10 +3407,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122840896</v>
+        <v>122842206</v>
       </c>
       <c r="B28" t="n">
-        <v>5358</v>
+        <v>100623</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3414,43 +3419,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>101728</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>676913</v>
+        <v>676816</v>
       </c>
       <c r="R28" t="n">
-        <v>6615766</v>
+        <v>6615981</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3927,10 +3927,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122842642</v>
+        <v>122842832</v>
       </c>
       <c r="B33" t="n">
-        <v>100623</v>
+        <v>57631</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3939,41 +3939,46 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>676714</v>
+        <v>676682</v>
       </c>
       <c r="R33" t="n">
-        <v>6615824</v>
+        <v>6615846</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4029,10 +4034,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122842832</v>
+        <v>122842642</v>
       </c>
       <c r="B34" t="n">
-        <v>57631</v>
+        <v>100623</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4041,46 +4046,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>676682</v>
+        <v>676714</v>
       </c>
       <c r="R34" t="n">
-        <v>6615846</v>
+        <v>6615824</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>

--- a/artfynd/A 9000-2025 artfynd.xlsx
+++ b/artfynd/A 9000-2025 artfynd.xlsx
@@ -3927,10 +3927,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122842832</v>
+        <v>122842642</v>
       </c>
       <c r="B33" t="n">
-        <v>57631</v>
+        <v>100623</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3939,46 +3939,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>676682</v>
+        <v>676714</v>
       </c>
       <c r="R33" t="n">
-        <v>6615846</v>
+        <v>6615824</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4034,10 +4029,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122842642</v>
+        <v>122842832</v>
       </c>
       <c r="B34" t="n">
-        <v>100623</v>
+        <v>57631</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4046,41 +4041,46 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>676714</v>
+        <v>676682</v>
       </c>
       <c r="R34" t="n">
-        <v>6615824</v>
+        <v>6615846</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>

--- a/artfynd/A 9000-2025 artfynd.xlsx
+++ b/artfynd/A 9000-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122842185</v>
+        <v>122845288</v>
       </c>
       <c r="B2" t="n">
-        <v>100623</v>
+        <v>8430</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>676831</v>
+        <v>677007</v>
       </c>
       <c r="R2" t="n">
-        <v>6615990</v>
+        <v>6615684</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122842792</v>
+        <v>122842401</v>
       </c>
       <c r="B3" t="n">
-        <v>90909</v>
+        <v>57494</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +794,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>676683</v>
+        <v>676742</v>
       </c>
       <c r="R3" t="n">
-        <v>6615843</v>
+        <v>6615954</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122845736</v>
+        <v>122842206</v>
       </c>
       <c r="B4" t="n">
-        <v>8441</v>
+        <v>100623</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,39 +905,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>677104</v>
+        <v>676816</v>
       </c>
       <c r="R4" t="n">
-        <v>6615675</v>
+        <v>6615981</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122840989</v>
+        <v>122845926</v>
       </c>
       <c r="B5" t="n">
-        <v>5173</v>
+        <v>90909</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,39 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>676899</v>
+        <v>677084</v>
       </c>
       <c r="R5" t="n">
-        <v>6615760</v>
+        <v>6615718</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122842680</v>
+        <v>122845245</v>
       </c>
       <c r="B6" t="n">
-        <v>57848</v>
+        <v>8441</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,39 +1109,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>676711</v>
+        <v>677001</v>
       </c>
       <c r="R6" t="n">
-        <v>6615822</v>
+        <v>6615675</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122841077</v>
+        <v>122841301</v>
       </c>
       <c r="B7" t="n">
-        <v>5193</v>
+        <v>8430</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,43 +1216,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>105930</v>
+        <v>106554</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>676870</v>
+        <v>676893</v>
       </c>
       <c r="R7" t="n">
-        <v>6615757</v>
+        <v>6615790</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1293,7 +1289,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1312,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122840495</v>
+        <v>122842950</v>
       </c>
       <c r="B8" t="n">
-        <v>5193</v>
+        <v>105463</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,39 +1323,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>105930</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>676936</v>
+        <v>676690</v>
       </c>
       <c r="R8" t="n">
-        <v>6615736</v>
+        <v>6615799</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122845880</v>
+        <v>122841986</v>
       </c>
       <c r="B9" t="n">
-        <v>90962</v>
+        <v>105463</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1431,38 +1421,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>677085</v>
+        <v>676779</v>
       </c>
       <c r="R9" t="n">
-        <v>6615732</v>
+        <v>6615963</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122842088</v>
+        <v>122842832</v>
       </c>
       <c r="B10" t="n">
-        <v>100623</v>
+        <v>57631</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1533,41 +1523,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>676779</v>
+        <v>676682</v>
       </c>
       <c r="R10" t="n">
-        <v>6615963</v>
+        <v>6615846</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1623,10 +1618,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122842950</v>
+        <v>122842792</v>
       </c>
       <c r="B11" t="n">
-        <v>105463</v>
+        <v>90909</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1639,21 +1634,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>676690</v>
+        <v>676683</v>
       </c>
       <c r="R11" t="n">
-        <v>6615799</v>
+        <v>6615843</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1725,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122842557</v>
+        <v>122840896</v>
       </c>
       <c r="B12" t="n">
-        <v>90944</v>
+        <v>5358</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1741,34 +1736,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>101728</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>676745</v>
+        <v>676913</v>
       </c>
       <c r="R12" t="n">
-        <v>6615878</v>
+        <v>6615766</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1827,7 +1827,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122842144</v>
+        <v>122842273</v>
       </c>
       <c r="B13" t="n">
         <v>100623</v>
@@ -1867,10 +1867,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>676841</v>
+        <v>676787</v>
       </c>
       <c r="R13" t="n">
-        <v>6615983</v>
+        <v>6615980</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1929,10 +1929,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122840712</v>
+        <v>122840930</v>
       </c>
       <c r="B14" t="n">
-        <v>4867</v>
+        <v>57494</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1941,31 +1941,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>101675</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1974,13 +1974,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>676921</v>
+        <v>676913</v>
       </c>
       <c r="R14" t="n">
-        <v>6615744</v>
+        <v>6615763</v>
       </c>
       <c r="S14" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2036,10 +2036,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122840804</v>
+        <v>122845093</v>
       </c>
       <c r="B15" t="n">
-        <v>5358</v>
+        <v>90909</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2048,43 +2048,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>101728</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>676921</v>
+        <v>676956</v>
       </c>
       <c r="R15" t="n">
-        <v>6615744</v>
+        <v>6615718</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2143,10 +2138,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122842273</v>
+        <v>122842680</v>
       </c>
       <c r="B16" t="n">
-        <v>100623</v>
+        <v>57848</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2159,34 +2154,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>676787</v>
+        <v>676711</v>
       </c>
       <c r="R16" t="n">
-        <v>6615980</v>
+        <v>6615822</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2245,10 +2245,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122842819</v>
+        <v>122843888</v>
       </c>
       <c r="B17" t="n">
-        <v>105463</v>
+        <v>8430</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2261,34 +2261,43 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>106554</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>676682</v>
+        <v>676813</v>
       </c>
       <c r="R17" t="n">
-        <v>6615846</v>
+        <v>6615903</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2329,6 +2338,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2347,10 +2357,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122845448</v>
+        <v>122842479</v>
       </c>
       <c r="B18" t="n">
-        <v>105463</v>
+        <v>8430</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2363,34 +2373,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>106554</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>676972</v>
+        <v>676756</v>
       </c>
       <c r="R18" t="n">
-        <v>6615705</v>
+        <v>6615927</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2449,10 +2464,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122840392</v>
+        <v>122842088</v>
       </c>
       <c r="B19" t="n">
-        <v>57494</v>
+        <v>100623</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2461,43 +2476,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>676983</v>
+        <v>676779</v>
       </c>
       <c r="R19" t="n">
-        <v>6615701</v>
+        <v>6615963</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2556,7 +2566,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122840930</v>
+        <v>122840623</v>
       </c>
       <c r="B20" t="n">
         <v>57494</v>
@@ -2601,10 +2611,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>676913</v>
+        <v>676932</v>
       </c>
       <c r="R20" t="n">
-        <v>6615763</v>
+        <v>6615725</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2663,10 +2673,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122842401</v>
+        <v>122840989</v>
       </c>
       <c r="B21" t="n">
-        <v>57494</v>
+        <v>5173</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2675,43 +2685,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>676742</v>
+        <v>676899</v>
       </c>
       <c r="R21" t="n">
-        <v>6615954</v>
+        <v>6615760</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2770,10 +2780,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122845288</v>
+        <v>122842144</v>
       </c>
       <c r="B22" t="n">
-        <v>8430</v>
+        <v>100623</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2786,39 +2796,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>677007</v>
+        <v>676841</v>
       </c>
       <c r="R22" t="n">
-        <v>6615684</v>
+        <v>6615983</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2877,10 +2882,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122841301</v>
+        <v>122842185</v>
       </c>
       <c r="B23" t="n">
-        <v>8430</v>
+        <v>100623</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2893,39 +2898,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>676893</v>
+        <v>676831</v>
       </c>
       <c r="R23" t="n">
-        <v>6615790</v>
+        <v>6615990</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122842479</v>
+        <v>122842557</v>
       </c>
       <c r="B24" t="n">
-        <v>8430</v>
+        <v>90944</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2996,43 +2996,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106554</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>676756</v>
+        <v>676745</v>
       </c>
       <c r="R24" t="n">
-        <v>6615927</v>
+        <v>6615878</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3091,10 +3086,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122840896</v>
+        <v>122843696</v>
       </c>
       <c r="B25" t="n">
-        <v>5358</v>
+        <v>90962</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3107,39 +3102,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>101728</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>676913</v>
+        <v>676651</v>
       </c>
       <c r="R25" t="n">
-        <v>6615766</v>
+        <v>6615875</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3198,10 +3188,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122840652</v>
+        <v>122845736</v>
       </c>
       <c r="B26" t="n">
-        <v>90909</v>
+        <v>8441</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3214,34 +3204,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>676670</v>
+        <v>677104</v>
       </c>
       <c r="R26" t="n">
-        <v>6615860</v>
+        <v>6615675</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3300,10 +3295,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122843861</v>
+        <v>122841077</v>
       </c>
       <c r="B27" t="n">
-        <v>57494</v>
+        <v>5193</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3312,20 +3307,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3334,21 +3329,25 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>676804</v>
+        <v>676870</v>
       </c>
       <c r="R27" t="n">
-        <v>6615893</v>
+        <v>6615757</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3389,6 +3388,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3407,10 +3407,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122842206</v>
+        <v>122840972</v>
       </c>
       <c r="B28" t="n">
-        <v>100623</v>
+        <v>90944</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3419,38 +3419,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>676816</v>
+        <v>676898</v>
       </c>
       <c r="R28" t="n">
-        <v>6615981</v>
+        <v>6615759</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3509,10 +3509,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122842133</v>
+        <v>122840922</v>
       </c>
       <c r="B29" t="n">
-        <v>100623</v>
+        <v>105463</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3525,34 +3525,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>676838</v>
+        <v>676912</v>
       </c>
       <c r="R29" t="n">
-        <v>6615977</v>
+        <v>6615761</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3611,10 +3611,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122845926</v>
+        <v>122841097</v>
       </c>
       <c r="B30" t="n">
-        <v>90909</v>
+        <v>5173</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3627,34 +3627,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>677084</v>
+        <v>676861</v>
       </c>
       <c r="R30" t="n">
-        <v>6615718</v>
+        <v>6615758</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3713,10 +3718,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122841097</v>
+        <v>122842642</v>
       </c>
       <c r="B31" t="n">
-        <v>5173</v>
+        <v>100623</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3729,39 +3734,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>676861</v>
+        <v>676714</v>
       </c>
       <c r="R31" t="n">
-        <v>6615758</v>
+        <v>6615824</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3820,10 +3820,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122840378</v>
+        <v>122845448</v>
       </c>
       <c r="B32" t="n">
-        <v>57848</v>
+        <v>105463</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3836,39 +3836,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103015</v>
+        <v>221144</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>676985</v>
+        <v>676972</v>
       </c>
       <c r="R32" t="n">
-        <v>6615696</v>
+        <v>6615705</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3927,10 +3922,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122842642</v>
+        <v>122840378</v>
       </c>
       <c r="B33" t="n">
-        <v>100623</v>
+        <v>57848</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3943,34 +3938,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>676714</v>
+        <v>676985</v>
       </c>
       <c r="R33" t="n">
-        <v>6615824</v>
+        <v>6615696</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4029,10 +4029,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122842832</v>
+        <v>122845880</v>
       </c>
       <c r="B34" t="n">
-        <v>57631</v>
+        <v>90962</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4045,42 +4045,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>676682</v>
+        <v>677085</v>
       </c>
       <c r="R34" t="n">
-        <v>6615846</v>
+        <v>6615732</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4136,7 +4131,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122840623</v>
+        <v>122841332</v>
       </c>
       <c r="B35" t="n">
         <v>57494</v>
@@ -4181,10 +4176,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>676932</v>
+        <v>676864</v>
       </c>
       <c r="R35" t="n">
-        <v>6615725</v>
+        <v>6615776</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4243,10 +4238,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122840972</v>
+        <v>122842133</v>
       </c>
       <c r="B36" t="n">
-        <v>90944</v>
+        <v>100623</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4255,38 +4250,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>676898</v>
+        <v>676838</v>
       </c>
       <c r="R36" t="n">
-        <v>6615759</v>
+        <v>6615977</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4345,10 +4340,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122843664</v>
+        <v>122843861</v>
       </c>
       <c r="B37" t="n">
-        <v>100623</v>
+        <v>57494</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4357,38 +4352,43 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>676656</v>
+        <v>676804</v>
       </c>
       <c r="R37" t="n">
-        <v>6615859</v>
+        <v>6615893</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4447,10 +4447,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122842748</v>
+        <v>122840804</v>
       </c>
       <c r="B38" t="n">
-        <v>5193</v>
+        <v>5358</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4459,25 +4459,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>105930</v>
+        <v>101728</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4488,14 +4488,14 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>676684</v>
+        <v>676921</v>
       </c>
       <c r="R38" t="n">
-        <v>6615835</v>
+        <v>6615744</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4554,10 +4554,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122841068</v>
+        <v>122842434</v>
       </c>
       <c r="B39" t="n">
-        <v>4867</v>
+        <v>57494</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4566,43 +4566,43 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>101675</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>676872</v>
+        <v>676739</v>
       </c>
       <c r="R39" t="n">
-        <v>6615746</v>
+        <v>6615944</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4661,10 +4661,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122845245</v>
+        <v>122840712</v>
       </c>
       <c r="B40" t="n">
-        <v>8441</v>
+        <v>4867</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4677,21 +4677,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>101675</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4706,13 +4706,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>677001</v>
+        <v>676921</v>
       </c>
       <c r="R40" t="n">
-        <v>6615675</v>
+        <v>6615744</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4768,10 +4768,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122843888</v>
+        <v>122840495</v>
       </c>
       <c r="B41" t="n">
-        <v>8430</v>
+        <v>5193</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4784,43 +4784,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>676813</v>
+        <v>676936</v>
       </c>
       <c r="R41" t="n">
-        <v>6615903</v>
+        <v>6615736</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4861,7 +4857,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4880,10 +4875,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122841986</v>
+        <v>122840392</v>
       </c>
       <c r="B42" t="n">
-        <v>105463</v>
+        <v>57494</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4892,38 +4887,43 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>676779</v>
+        <v>676983</v>
       </c>
       <c r="R42" t="n">
-        <v>6615963</v>
+        <v>6615701</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4982,10 +4982,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122840922</v>
+        <v>122843607</v>
       </c>
       <c r="B43" t="n">
-        <v>105463</v>
+        <v>100623</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4998,34 +4998,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>676912</v>
+        <v>676666</v>
       </c>
       <c r="R43" t="n">
-        <v>6615761</v>
+        <v>6615819</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5084,10 +5084,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122843696</v>
+        <v>122840652</v>
       </c>
       <c r="B44" t="n">
-        <v>90962</v>
+        <v>90909</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5096,25 +5096,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5124,10 +5124,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>676651</v>
+        <v>676670</v>
       </c>
       <c r="R44" t="n">
-        <v>6615875</v>
+        <v>6615860</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5186,10 +5186,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122845093</v>
+        <v>122840992</v>
       </c>
       <c r="B45" t="n">
-        <v>90909</v>
+        <v>90944</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5198,25 +5198,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5226,10 +5226,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>676956</v>
+        <v>676900</v>
       </c>
       <c r="R45" t="n">
-        <v>6615718</v>
+        <v>6615757</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5288,10 +5288,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122842434</v>
+        <v>122841068</v>
       </c>
       <c r="B46" t="n">
-        <v>57494</v>
+        <v>4867</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5300,43 +5300,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>101675</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>676739</v>
+        <v>676872</v>
       </c>
       <c r="R46" t="n">
-        <v>6615944</v>
+        <v>6615746</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5395,10 +5395,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122840992</v>
+        <v>122842748</v>
       </c>
       <c r="B47" t="n">
-        <v>90944</v>
+        <v>5193</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5407,38 +5407,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>676900</v>
+        <v>676684</v>
       </c>
       <c r="R47" t="n">
-        <v>6615757</v>
+        <v>6615835</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5497,7 +5502,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122843607</v>
+        <v>122843664</v>
       </c>
       <c r="B48" t="n">
         <v>100623</v>
@@ -5537,10 +5542,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>676666</v>
+        <v>676656</v>
       </c>
       <c r="R48" t="n">
-        <v>6615819</v>
+        <v>6615859</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5599,10 +5604,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122841332</v>
+        <v>122842819</v>
       </c>
       <c r="B49" t="n">
-        <v>57494</v>
+        <v>105463</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5611,43 +5616,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>676864</v>
+        <v>676682</v>
       </c>
       <c r="R49" t="n">
-        <v>6615776</v>
+        <v>6615846</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>

--- a/artfynd/A 9000-2025 artfynd.xlsx
+++ b/artfynd/A 9000-2025 artfynd.xlsx
@@ -4238,10 +4238,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122842133</v>
+        <v>122840804</v>
       </c>
       <c r="B36" t="n">
-        <v>100623</v>
+        <v>5358</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4250,38 +4250,43 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>101728</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>676838</v>
+        <v>676921</v>
       </c>
       <c r="R36" t="n">
-        <v>6615977</v>
+        <v>6615744</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4340,10 +4345,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122843861</v>
+        <v>122842133</v>
       </c>
       <c r="B37" t="n">
-        <v>57494</v>
+        <v>100623</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4352,43 +4357,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>676804</v>
+        <v>676838</v>
       </c>
       <c r="R37" t="n">
-        <v>6615893</v>
+        <v>6615977</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4447,10 +4447,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122840804</v>
+        <v>122843861</v>
       </c>
       <c r="B38" t="n">
-        <v>5358</v>
+        <v>57494</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4463,39 +4463,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>101728</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>676921</v>
+        <v>676804</v>
       </c>
       <c r="R38" t="n">
-        <v>6615744</v>
+        <v>6615893</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4661,10 +4661,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122840712</v>
+        <v>122840495</v>
       </c>
       <c r="B40" t="n">
-        <v>4867</v>
+        <v>5193</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4677,21 +4677,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>101675</v>
+        <v>105930</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4706,13 +4706,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>676921</v>
+        <v>676936</v>
       </c>
       <c r="R40" t="n">
-        <v>6615744</v>
+        <v>6615736</v>
       </c>
       <c r="S40" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4768,10 +4768,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122840495</v>
+        <v>122840712</v>
       </c>
       <c r="B41" t="n">
-        <v>5193</v>
+        <v>4867</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4784,21 +4784,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>105930</v>
+        <v>101675</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4813,13 +4813,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>676936</v>
+        <v>676921</v>
       </c>
       <c r="R41" t="n">
-        <v>6615736</v>
+        <v>6615744</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4875,10 +4875,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122840392</v>
+        <v>122843607</v>
       </c>
       <c r="B42" t="n">
-        <v>57494</v>
+        <v>100623</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4887,43 +4887,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>676983</v>
+        <v>676666</v>
       </c>
       <c r="R42" t="n">
-        <v>6615701</v>
+        <v>6615819</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4982,10 +4977,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122843607</v>
+        <v>122840392</v>
       </c>
       <c r="B43" t="n">
-        <v>100623</v>
+        <v>57494</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4994,38 +4989,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>676666</v>
+        <v>676983</v>
       </c>
       <c r="R43" t="n">
-        <v>6615819</v>
+        <v>6615701</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>

--- a/artfynd/A 9000-2025 artfynd.xlsx
+++ b/artfynd/A 9000-2025 artfynd.xlsx
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122845926</v>
+        <v>122845245</v>
       </c>
       <c r="B5" t="n">
-        <v>90909</v>
+        <v>8441</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,34 +1007,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>677084</v>
+        <v>677001</v>
       </c>
       <c r="R5" t="n">
-        <v>6615718</v>
+        <v>6615675</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122845245</v>
+        <v>122841301</v>
       </c>
       <c r="B6" t="n">
-        <v>8441</v>
+        <v>8430</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>677001</v>
+        <v>676893</v>
       </c>
       <c r="R6" t="n">
-        <v>6615675</v>
+        <v>6615790</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122841301</v>
+        <v>122842950</v>
       </c>
       <c r="B7" t="n">
-        <v>8430</v>
+        <v>105463</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,39 +1221,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106554</v>
+        <v>221144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>676893</v>
+        <v>676690</v>
       </c>
       <c r="R7" t="n">
-        <v>6615790</v>
+        <v>6615799</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,7 +1307,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122842950</v>
+        <v>122841986</v>
       </c>
       <c r="B8" t="n">
         <v>105463</v>
@@ -1343,14 +1343,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>676690</v>
+        <v>676779</v>
       </c>
       <c r="R8" t="n">
-        <v>6615799</v>
+        <v>6615963</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122841986</v>
+        <v>122845926</v>
       </c>
       <c r="B9" t="n">
-        <v>105463</v>
+        <v>90909</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,34 +1425,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>676779</v>
+        <v>677084</v>
       </c>
       <c r="R9" t="n">
-        <v>6615963</v>
+        <v>6615718</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1618,10 +1618,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122842792</v>
+        <v>122840896</v>
       </c>
       <c r="B11" t="n">
-        <v>90909</v>
+        <v>5358</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1630,38 +1630,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>101728</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>676683</v>
+        <v>676913</v>
       </c>
       <c r="R11" t="n">
-        <v>6615843</v>
+        <v>6615766</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1720,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122840896</v>
+        <v>122842792</v>
       </c>
       <c r="B12" t="n">
-        <v>5358</v>
+        <v>90909</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1732,43 +1737,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>101728</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>676913</v>
+        <v>676683</v>
       </c>
       <c r="R12" t="n">
-        <v>6615766</v>
+        <v>6615843</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1929,10 +1929,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122840930</v>
+        <v>122843888</v>
       </c>
       <c r="B14" t="n">
-        <v>57494</v>
+        <v>8430</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1941,43 +1941,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>676913</v>
+        <v>676813</v>
       </c>
       <c r="R14" t="n">
-        <v>6615763</v>
+        <v>6615903</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2018,6 +2022,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2036,10 +2041,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122845093</v>
+        <v>122842479</v>
       </c>
       <c r="B15" t="n">
-        <v>90909</v>
+        <v>8430</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2052,34 +2057,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>106554</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>676956</v>
+        <v>676756</v>
       </c>
       <c r="R15" t="n">
-        <v>6615718</v>
+        <v>6615927</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2138,10 +2148,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122842680</v>
+        <v>122842088</v>
       </c>
       <c r="B16" t="n">
-        <v>57848</v>
+        <v>100623</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2154,39 +2164,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>676711</v>
+        <v>676779</v>
       </c>
       <c r="R16" t="n">
-        <v>6615822</v>
+        <v>6615963</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2245,10 +2250,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122843888</v>
+        <v>122845093</v>
       </c>
       <c r="B17" t="n">
-        <v>8430</v>
+        <v>90909</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2261,43 +2266,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106554</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>676813</v>
+        <v>676956</v>
       </c>
       <c r="R17" t="n">
-        <v>6615903</v>
+        <v>6615718</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2338,7 +2334,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2357,10 +2352,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122842479</v>
+        <v>122840930</v>
       </c>
       <c r="B18" t="n">
-        <v>8430</v>
+        <v>57494</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2369,43 +2364,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>676756</v>
+        <v>676913</v>
       </c>
       <c r="R18" t="n">
-        <v>6615927</v>
+        <v>6615763</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2464,10 +2459,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122842088</v>
+        <v>122842680</v>
       </c>
       <c r="B19" t="n">
-        <v>100623</v>
+        <v>57848</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2480,34 +2475,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>676779</v>
+        <v>676711</v>
       </c>
       <c r="R19" t="n">
-        <v>6615963</v>
+        <v>6615822</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2566,10 +2566,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122840623</v>
+        <v>122842144</v>
       </c>
       <c r="B20" t="n">
-        <v>57494</v>
+        <v>100623</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2578,43 +2578,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>676932</v>
+        <v>676841</v>
       </c>
       <c r="R20" t="n">
-        <v>6615725</v>
+        <v>6615983</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2673,10 +2668,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122840989</v>
+        <v>122842185</v>
       </c>
       <c r="B21" t="n">
-        <v>5173</v>
+        <v>100623</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2689,39 +2684,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>676899</v>
+        <v>676831</v>
       </c>
       <c r="R21" t="n">
-        <v>6615760</v>
+        <v>6615990</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2780,10 +2770,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122842144</v>
+        <v>122840989</v>
       </c>
       <c r="B22" t="n">
-        <v>100623</v>
+        <v>5173</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2796,34 +2786,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>676841</v>
+        <v>676899</v>
       </c>
       <c r="R22" t="n">
-        <v>6615983</v>
+        <v>6615760</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2882,10 +2877,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122842185</v>
+        <v>122840623</v>
       </c>
       <c r="B23" t="n">
-        <v>100623</v>
+        <v>57494</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2894,38 +2889,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>676831</v>
+        <v>676932</v>
       </c>
       <c r="R23" t="n">
-        <v>6615990</v>
+        <v>6615725</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -4875,10 +4875,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122843607</v>
+        <v>122840392</v>
       </c>
       <c r="B42" t="n">
-        <v>100623</v>
+        <v>57494</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4887,38 +4887,43 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>676666</v>
+        <v>676983</v>
       </c>
       <c r="R42" t="n">
-        <v>6615819</v>
+        <v>6615701</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4977,10 +4982,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122840392</v>
+        <v>122843607</v>
       </c>
       <c r="B43" t="n">
-        <v>57494</v>
+        <v>100623</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4989,43 +4994,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>676983</v>
+        <v>676666</v>
       </c>
       <c r="R43" t="n">
-        <v>6615701</v>
+        <v>6615819</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>

--- a/artfynd/A 9000-2025 artfynd.xlsx
+++ b/artfynd/A 9000-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122845288</v>
+        <v>122840992</v>
       </c>
       <c r="B2" t="n">
-        <v>8430</v>
+        <v>90952</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106554</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>677007</v>
+        <v>676900</v>
       </c>
       <c r="R2" t="n">
-        <v>6615684</v>
+        <v>6615757</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122842401</v>
+        <v>122840712</v>
       </c>
       <c r="B3" t="n">
-        <v>57494</v>
+        <v>4867</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,46 +789,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>101675</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>676742</v>
+        <v>676921</v>
       </c>
       <c r="R3" t="n">
-        <v>6615954</v>
+        <v>6615744</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -889,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122842206</v>
+        <v>122842557</v>
       </c>
       <c r="B4" t="n">
-        <v>100623</v>
+        <v>90952</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>676816</v>
+        <v>676745</v>
       </c>
       <c r="R4" t="n">
-        <v>6615981</v>
+        <v>6615878</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122845245</v>
+        <v>122840652</v>
       </c>
       <c r="B5" t="n">
-        <v>8441</v>
+        <v>90917</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,39 +1002,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>677001</v>
+        <v>676670</v>
       </c>
       <c r="R5" t="n">
-        <v>6615675</v>
+        <v>6615860</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122841301</v>
+        <v>122843664</v>
       </c>
       <c r="B6" t="n">
-        <v>8430</v>
+        <v>100631</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,39 +1104,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>676893</v>
+        <v>676656</v>
       </c>
       <c r="R6" t="n">
-        <v>6615790</v>
+        <v>6615859</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122842950</v>
+        <v>122841301</v>
       </c>
       <c r="B7" t="n">
-        <v>105463</v>
+        <v>8430</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,34 +1206,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>106554</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>676690</v>
+        <v>676893</v>
       </c>
       <c r="R7" t="n">
-        <v>6615799</v>
+        <v>6615790</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122841986</v>
+        <v>122842792</v>
       </c>
       <c r="B8" t="n">
-        <v>105463</v>
+        <v>90917</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,34 +1313,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>676779</v>
+        <v>676683</v>
       </c>
       <c r="R8" t="n">
-        <v>6615963</v>
+        <v>6615843</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122845926</v>
+        <v>122841332</v>
       </c>
       <c r="B9" t="n">
-        <v>90909</v>
+        <v>57494</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1421,38 +1411,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>677084</v>
+        <v>676864</v>
       </c>
       <c r="R9" t="n">
-        <v>6615718</v>
+        <v>6615776</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1511,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122842832</v>
+        <v>122843861</v>
       </c>
       <c r="B10" t="n">
-        <v>57631</v>
+        <v>57494</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,42 +1522,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>676682</v>
+        <v>676804</v>
       </c>
       <c r="R10" t="n">
-        <v>6615846</v>
+        <v>6615893</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1618,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122840896</v>
+        <v>122841068</v>
       </c>
       <c r="B11" t="n">
-        <v>5358</v>
+        <v>4867</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1630,25 +1625,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>101728</v>
+        <v>101675</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>676913</v>
+        <v>676872</v>
       </c>
       <c r="R11" t="n">
-        <v>6615766</v>
+        <v>6615746</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1725,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122842792</v>
+        <v>122842832</v>
       </c>
       <c r="B12" t="n">
-        <v>90909</v>
+        <v>57631</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1737,41 +1732,46 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>676683</v>
+        <v>676682</v>
       </c>
       <c r="R12" t="n">
-        <v>6615843</v>
+        <v>6615846</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1827,10 +1827,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122842273</v>
+        <v>122841986</v>
       </c>
       <c r="B13" t="n">
-        <v>100623</v>
+        <v>105471</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1843,21 +1843,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1867,10 +1867,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>676787</v>
+        <v>676779</v>
       </c>
       <c r="R13" t="n">
-        <v>6615980</v>
+        <v>6615963</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1929,10 +1929,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122843888</v>
+        <v>122842748</v>
       </c>
       <c r="B14" t="n">
-        <v>8430</v>
+        <v>5193</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1945,43 +1945,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>676813</v>
+        <v>676684</v>
       </c>
       <c r="R14" t="n">
-        <v>6615903</v>
+        <v>6615835</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2022,7 +2018,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2041,10 +2036,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122842479</v>
+        <v>122842950</v>
       </c>
       <c r="B15" t="n">
-        <v>8430</v>
+        <v>105471</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2057,39 +2052,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106554</v>
+        <v>221144</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>676756</v>
+        <v>676690</v>
       </c>
       <c r="R15" t="n">
-        <v>6615927</v>
+        <v>6615799</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2148,10 +2138,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122842088</v>
+        <v>122842642</v>
       </c>
       <c r="B16" t="n">
-        <v>100623</v>
+        <v>100631</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2188,10 +2178,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>676779</v>
+        <v>676714</v>
       </c>
       <c r="R16" t="n">
-        <v>6615963</v>
+        <v>6615824</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2250,10 +2240,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122845093</v>
+        <v>122843607</v>
       </c>
       <c r="B17" t="n">
-        <v>90909</v>
+        <v>100631</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2266,34 +2256,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>676956</v>
+        <v>676666</v>
       </c>
       <c r="R17" t="n">
-        <v>6615718</v>
+        <v>6615819</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2352,10 +2342,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122840930</v>
+        <v>122842185</v>
       </c>
       <c r="B18" t="n">
-        <v>57494</v>
+        <v>100631</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2364,43 +2354,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>676913</v>
+        <v>676831</v>
       </c>
       <c r="R18" t="n">
-        <v>6615763</v>
+        <v>6615990</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2459,10 +2444,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122842680</v>
+        <v>122840930</v>
       </c>
       <c r="B19" t="n">
-        <v>57848</v>
+        <v>57494</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2471,20 +2456,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2495,19 +2480,19 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>676711</v>
+        <v>676913</v>
       </c>
       <c r="R19" t="n">
-        <v>6615822</v>
+        <v>6615763</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2566,10 +2551,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122842144</v>
+        <v>122840989</v>
       </c>
       <c r="B20" t="n">
-        <v>100623</v>
+        <v>5173</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2582,34 +2567,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>676841</v>
+        <v>676899</v>
       </c>
       <c r="R20" t="n">
-        <v>6615983</v>
+        <v>6615760</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2668,10 +2658,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122842185</v>
+        <v>122842434</v>
       </c>
       <c r="B21" t="n">
-        <v>100623</v>
+        <v>57494</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2680,38 +2670,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>676831</v>
+        <v>676739</v>
       </c>
       <c r="R21" t="n">
-        <v>6615990</v>
+        <v>6615944</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2770,10 +2765,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122840989</v>
+        <v>122840922</v>
       </c>
       <c r="B22" t="n">
-        <v>5173</v>
+        <v>105471</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2786,39 +2781,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100526</v>
+        <v>221144</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>676899</v>
+        <v>676912</v>
       </c>
       <c r="R22" t="n">
-        <v>6615760</v>
+        <v>6615761</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2877,10 +2867,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122840623</v>
+        <v>122842088</v>
       </c>
       <c r="B23" t="n">
-        <v>57494</v>
+        <v>100631</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2889,43 +2879,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>676932</v>
+        <v>676779</v>
       </c>
       <c r="R23" t="n">
-        <v>6615725</v>
+        <v>6615963</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2984,10 +2969,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122842557</v>
+        <v>122841077</v>
       </c>
       <c r="B24" t="n">
-        <v>90944</v>
+        <v>5193</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2996,38 +2981,47 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>676745</v>
+        <v>676870</v>
       </c>
       <c r="R24" t="n">
-        <v>6615878</v>
+        <v>6615757</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3068,6 +3062,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3086,10 +3081,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122843696</v>
+        <v>122845736</v>
       </c>
       <c r="B25" t="n">
-        <v>90962</v>
+        <v>8441</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3098,38 +3093,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>676651</v>
+        <v>677104</v>
       </c>
       <c r="R25" t="n">
-        <v>6615875</v>
+        <v>6615675</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3188,10 +3188,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122845736</v>
+        <v>122842401</v>
       </c>
       <c r="B26" t="n">
-        <v>8441</v>
+        <v>57494</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3200,43 +3200,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>677104</v>
+        <v>676742</v>
       </c>
       <c r="R26" t="n">
-        <v>6615675</v>
+        <v>6615954</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3295,10 +3295,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122841077</v>
+        <v>122840378</v>
       </c>
       <c r="B27" t="n">
-        <v>5193</v>
+        <v>57848</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3311,16 +3311,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>105930</v>
+        <v>103015</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3329,25 +3329,21 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>676870</v>
+        <v>676985</v>
       </c>
       <c r="R27" t="n">
-        <v>6615757</v>
+        <v>6615696</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3388,7 +3384,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3407,10 +3402,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122840972</v>
+        <v>122842273</v>
       </c>
       <c r="B28" t="n">
-        <v>90944</v>
+        <v>100631</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3419,38 +3414,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>676898</v>
+        <v>676787</v>
       </c>
       <c r="R28" t="n">
-        <v>6615759</v>
+        <v>6615980</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3509,10 +3504,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122840922</v>
+        <v>122840972</v>
       </c>
       <c r="B29" t="n">
-        <v>105463</v>
+        <v>90952</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3521,25 +3516,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3549,10 +3544,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>676912</v>
+        <v>676898</v>
       </c>
       <c r="R29" t="n">
-        <v>6615761</v>
+        <v>6615759</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3611,10 +3606,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122841097</v>
+        <v>122845880</v>
       </c>
       <c r="B30" t="n">
-        <v>5173</v>
+        <v>90970</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3623,43 +3618,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100526</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>676861</v>
+        <v>677085</v>
       </c>
       <c r="R30" t="n">
-        <v>6615758</v>
+        <v>6615732</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3718,10 +3708,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122842642</v>
+        <v>122842819</v>
       </c>
       <c r="B31" t="n">
-        <v>100623</v>
+        <v>105471</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3734,34 +3724,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>676714</v>
+        <v>676682</v>
       </c>
       <c r="R31" t="n">
-        <v>6615824</v>
+        <v>6615846</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3823,7 +3813,7 @@
         <v>122845448</v>
       </c>
       <c r="B32" t="n">
-        <v>105463</v>
+        <v>105471</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3922,10 +3912,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122840378</v>
+        <v>122840495</v>
       </c>
       <c r="B33" t="n">
-        <v>57848</v>
+        <v>5193</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3938,16 +3928,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103015</v>
+        <v>105930</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3958,7 +3948,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3967,10 +3957,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>676985</v>
+        <v>676936</v>
       </c>
       <c r="R33" t="n">
-        <v>6615696</v>
+        <v>6615736</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4029,10 +4019,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122845880</v>
+        <v>122840896</v>
       </c>
       <c r="B34" t="n">
-        <v>90962</v>
+        <v>5358</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4045,34 +4035,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>101728</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>677085</v>
+        <v>676913</v>
       </c>
       <c r="R34" t="n">
-        <v>6615732</v>
+        <v>6615766</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4131,10 +4126,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122841332</v>
+        <v>122841097</v>
       </c>
       <c r="B35" t="n">
-        <v>57494</v>
+        <v>5173</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4143,31 +4138,31 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4176,10 +4171,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>676864</v>
+        <v>676861</v>
       </c>
       <c r="R35" t="n">
-        <v>6615776</v>
+        <v>6615758</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4238,10 +4233,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122840804</v>
+        <v>122840392</v>
       </c>
       <c r="B36" t="n">
-        <v>5358</v>
+        <v>57494</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4254,27 +4249,27 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>101728</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4283,10 +4278,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>676921</v>
+        <v>676983</v>
       </c>
       <c r="R36" t="n">
-        <v>6615744</v>
+        <v>6615701</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4345,10 +4340,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122842133</v>
+        <v>122843696</v>
       </c>
       <c r="B37" t="n">
-        <v>100623</v>
+        <v>90970</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4357,38 +4352,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>676838</v>
+        <v>676651</v>
       </c>
       <c r="R37" t="n">
-        <v>6615977</v>
+        <v>6615875</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4447,10 +4442,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122843861</v>
+        <v>122842479</v>
       </c>
       <c r="B38" t="n">
-        <v>57494</v>
+        <v>8430</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4459,31 +4454,31 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4492,10 +4487,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>676804</v>
+        <v>676756</v>
       </c>
       <c r="R38" t="n">
-        <v>6615893</v>
+        <v>6615927</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4554,10 +4549,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122842434</v>
+        <v>122845245</v>
       </c>
       <c r="B39" t="n">
-        <v>57494</v>
+        <v>8441</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4566,43 +4561,43 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>676739</v>
+        <v>677001</v>
       </c>
       <c r="R39" t="n">
-        <v>6615944</v>
+        <v>6615675</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4661,10 +4656,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122840495</v>
+        <v>122842133</v>
       </c>
       <c r="B40" t="n">
-        <v>5193</v>
+        <v>100631</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4677,39 +4672,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>676936</v>
+        <v>676838</v>
       </c>
       <c r="R40" t="n">
-        <v>6615736</v>
+        <v>6615977</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4768,10 +4758,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122840712</v>
+        <v>122840804</v>
       </c>
       <c r="B41" t="n">
-        <v>4867</v>
+        <v>5358</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4780,25 +4770,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>101675</v>
+        <v>101728</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4819,7 +4809,7 @@
         <v>6615744</v>
       </c>
       <c r="S41" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4875,10 +4865,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122840392</v>
+        <v>122845926</v>
       </c>
       <c r="B42" t="n">
-        <v>57494</v>
+        <v>90917</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4887,43 +4877,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>676983</v>
+        <v>677084</v>
       </c>
       <c r="R42" t="n">
-        <v>6615701</v>
+        <v>6615718</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4982,10 +4967,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122843607</v>
+        <v>122845093</v>
       </c>
       <c r="B43" t="n">
-        <v>100623</v>
+        <v>90917</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4998,34 +4983,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>676666</v>
+        <v>676956</v>
       </c>
       <c r="R43" t="n">
-        <v>6615819</v>
+        <v>6615718</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5084,10 +5069,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122840652</v>
+        <v>122840623</v>
       </c>
       <c r="B44" t="n">
-        <v>90909</v>
+        <v>57494</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5096,38 +5081,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>676670</v>
+        <v>676932</v>
       </c>
       <c r="R44" t="n">
-        <v>6615860</v>
+        <v>6615725</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5186,10 +5176,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122840992</v>
+        <v>122842680</v>
       </c>
       <c r="B45" t="n">
-        <v>90944</v>
+        <v>57848</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5198,38 +5188,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>103015</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>676900</v>
+        <v>676711</v>
       </c>
       <c r="R45" t="n">
-        <v>6615757</v>
+        <v>6615822</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5288,10 +5283,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122841068</v>
+        <v>122845288</v>
       </c>
       <c r="B46" t="n">
-        <v>4867</v>
+        <v>8430</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5304,21 +5299,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>101675</v>
+        <v>106554</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5333,10 +5328,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>676872</v>
+        <v>677007</v>
       </c>
       <c r="R46" t="n">
-        <v>6615746</v>
+        <v>6615684</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5395,10 +5390,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122842748</v>
+        <v>122842206</v>
       </c>
       <c r="B47" t="n">
-        <v>5193</v>
+        <v>100631</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5411,39 +5406,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>676684</v>
+        <v>676816</v>
       </c>
       <c r="R47" t="n">
-        <v>6615835</v>
+        <v>6615981</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5502,10 +5492,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122843664</v>
+        <v>122843888</v>
       </c>
       <c r="B48" t="n">
-        <v>100623</v>
+        <v>8430</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5518,34 +5508,43 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>676656</v>
+        <v>676813</v>
       </c>
       <c r="R48" t="n">
-        <v>6615859</v>
+        <v>6615903</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5586,6 +5585,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5604,10 +5604,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122842819</v>
+        <v>122842144</v>
       </c>
       <c r="B49" t="n">
-        <v>105463</v>
+        <v>100631</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5620,34 +5620,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>676682</v>
+        <v>676841</v>
       </c>
       <c r="R49" t="n">
-        <v>6615846</v>
+        <v>6615983</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>

--- a/artfynd/A 9000-2025 artfynd.xlsx
+++ b/artfynd/A 9000-2025 artfynd.xlsx
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122841301</v>
+        <v>122842792</v>
       </c>
       <c r="B7" t="n">
-        <v>8430</v>
+        <v>90917</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,39 +1206,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106554</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>676893</v>
+        <v>676683</v>
       </c>
       <c r="R7" t="n">
-        <v>6615790</v>
+        <v>6615843</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122842792</v>
+        <v>122841301</v>
       </c>
       <c r="B8" t="n">
-        <v>90917</v>
+        <v>8430</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,34 +1308,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>106554</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>676683</v>
+        <v>676893</v>
       </c>
       <c r="R8" t="n">
-        <v>6615843</v>
+        <v>6615790</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1929,10 +1929,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122842748</v>
+        <v>122842642</v>
       </c>
       <c r="B14" t="n">
-        <v>5193</v>
+        <v>100631</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1945,39 +1945,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>676684</v>
+        <v>676714</v>
       </c>
       <c r="R14" t="n">
-        <v>6615835</v>
+        <v>6615824</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2036,10 +2031,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122842950</v>
+        <v>122842748</v>
       </c>
       <c r="B15" t="n">
-        <v>105471</v>
+        <v>5193</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2052,34 +2047,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221144</v>
+        <v>105930</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>676690</v>
+        <v>676684</v>
       </c>
       <c r="R15" t="n">
-        <v>6615799</v>
+        <v>6615835</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2138,10 +2138,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122842642</v>
+        <v>122842950</v>
       </c>
       <c r="B16" t="n">
-        <v>100631</v>
+        <v>105471</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2154,34 +2154,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>676714</v>
+        <v>676690</v>
       </c>
       <c r="R16" t="n">
-        <v>6615824</v>
+        <v>6615799</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -4340,10 +4340,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122843696</v>
+        <v>122842479</v>
       </c>
       <c r="B37" t="n">
-        <v>90970</v>
+        <v>8430</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4352,38 +4352,43 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>106554</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>676651</v>
+        <v>676756</v>
       </c>
       <c r="R37" t="n">
-        <v>6615875</v>
+        <v>6615927</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4442,10 +4447,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122842479</v>
+        <v>122843696</v>
       </c>
       <c r="B38" t="n">
-        <v>8430</v>
+        <v>90970</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4454,43 +4459,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106554</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>676756</v>
+        <v>676651</v>
       </c>
       <c r="R38" t="n">
-        <v>6615927</v>
+        <v>6615875</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4758,10 +4758,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122840804</v>
+        <v>122845926</v>
       </c>
       <c r="B41" t="n">
-        <v>5358</v>
+        <v>90917</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4770,43 +4770,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>101728</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>676921</v>
+        <v>677084</v>
       </c>
       <c r="R41" t="n">
-        <v>6615744</v>
+        <v>6615718</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4865,10 +4860,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122845926</v>
+        <v>122840804</v>
       </c>
       <c r="B42" t="n">
-        <v>90917</v>
+        <v>5358</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4877,38 +4872,43 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>101728</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>677084</v>
+        <v>676921</v>
       </c>
       <c r="R42" t="n">
-        <v>6615718</v>
+        <v>6615744</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5390,10 +5390,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122842206</v>
+        <v>122843888</v>
       </c>
       <c r="B47" t="n">
-        <v>100631</v>
+        <v>8430</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5406,34 +5406,43 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>676816</v>
+        <v>676813</v>
       </c>
       <c r="R47" t="n">
-        <v>6615981</v>
+        <v>6615903</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5474,6 +5483,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5492,10 +5502,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122843888</v>
+        <v>122842206</v>
       </c>
       <c r="B48" t="n">
-        <v>8430</v>
+        <v>100631</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5508,43 +5518,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>676813</v>
+        <v>676816</v>
       </c>
       <c r="R48" t="n">
-        <v>6615903</v>
+        <v>6615981</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5585,7 +5586,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 9000-2025 artfynd.xlsx
+++ b/artfynd/A 9000-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122840992</v>
+        <v>122843664</v>
       </c>
       <c r="B2" t="n">
-        <v>90952</v>
+        <v>100631</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>676900</v>
+        <v>676656</v>
       </c>
       <c r="R2" t="n">
-        <v>6615757</v>
+        <v>6615859</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122840712</v>
+        <v>122845288</v>
       </c>
       <c r="B3" t="n">
-        <v>4867</v>
+        <v>8430</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101675</v>
+        <v>106554</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,13 +822,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>676921</v>
+        <v>677007</v>
       </c>
       <c r="R3" t="n">
-        <v>6615744</v>
+        <v>6615684</v>
       </c>
       <c r="S3" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122842557</v>
+        <v>122840623</v>
       </c>
       <c r="B4" t="n">
-        <v>90952</v>
+        <v>57494</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,34 +900,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>676745</v>
+        <v>676932</v>
       </c>
       <c r="R4" t="n">
-        <v>6615878</v>
+        <v>6615725</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122840652</v>
+        <v>122840930</v>
       </c>
       <c r="B5" t="n">
-        <v>90917</v>
+        <v>57494</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,38 +1003,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>676670</v>
+        <v>676913</v>
       </c>
       <c r="R5" t="n">
-        <v>6615860</v>
+        <v>6615763</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122843664</v>
+        <v>122840378</v>
       </c>
       <c r="B6" t="n">
-        <v>100631</v>
+        <v>57848</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,34 +1114,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>676656</v>
+        <v>676985</v>
       </c>
       <c r="R6" t="n">
-        <v>6615859</v>
+        <v>6615696</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122842792</v>
+        <v>122843607</v>
       </c>
       <c r="B7" t="n">
-        <v>90917</v>
+        <v>100631</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>676683</v>
+        <v>676666</v>
       </c>
       <c r="R7" t="n">
-        <v>6615843</v>
+        <v>6615819</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122841301</v>
+        <v>122842206</v>
       </c>
       <c r="B8" t="n">
-        <v>8430</v>
+        <v>100631</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,39 +1323,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>676893</v>
+        <v>676816</v>
       </c>
       <c r="R8" t="n">
-        <v>6615790</v>
+        <v>6615981</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122841332</v>
+        <v>122843696</v>
       </c>
       <c r="B9" t="n">
-        <v>57494</v>
+        <v>90970</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,39 +1425,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>676864</v>
+        <v>676651</v>
       </c>
       <c r="R9" t="n">
-        <v>6615776</v>
+        <v>6615875</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122843861</v>
+        <v>122842642</v>
       </c>
       <c r="B10" t="n">
-        <v>57494</v>
+        <v>100631</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1518,43 +1523,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>676804</v>
+        <v>676714</v>
       </c>
       <c r="R10" t="n">
-        <v>6615893</v>
+        <v>6615824</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1613,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122841068</v>
+        <v>122845245</v>
       </c>
       <c r="B11" t="n">
-        <v>4867</v>
+        <v>8441</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1629,21 +1629,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>101675</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1658,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>676872</v>
+        <v>677001</v>
       </c>
       <c r="R11" t="n">
-        <v>6615746</v>
+        <v>6615675</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122842832</v>
+        <v>122840712</v>
       </c>
       <c r="B12" t="n">
-        <v>57631</v>
+        <v>4867</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1732,46 +1732,46 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>101675</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>676682</v>
+        <v>676921</v>
       </c>
       <c r="R12" t="n">
-        <v>6615846</v>
+        <v>6615744</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1827,10 +1827,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122841986</v>
+        <v>122841301</v>
       </c>
       <c r="B13" t="n">
-        <v>105471</v>
+        <v>8430</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1843,34 +1843,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221144</v>
+        <v>106554</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>676779</v>
+        <v>676893</v>
       </c>
       <c r="R13" t="n">
-        <v>6615963</v>
+        <v>6615790</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1929,10 +1934,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122842642</v>
+        <v>122845736</v>
       </c>
       <c r="B14" t="n">
-        <v>100631</v>
+        <v>8441</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1945,34 +1950,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>676714</v>
+        <v>677104</v>
       </c>
       <c r="R14" t="n">
-        <v>6615824</v>
+        <v>6615675</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2031,10 +2041,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122842748</v>
+        <v>122845880</v>
       </c>
       <c r="B15" t="n">
-        <v>5193</v>
+        <v>90970</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2043,43 +2053,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>105930</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>676684</v>
+        <v>677085</v>
       </c>
       <c r="R15" t="n">
-        <v>6615835</v>
+        <v>6615732</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2138,10 +2143,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122842950</v>
+        <v>122843888</v>
       </c>
       <c r="B16" t="n">
-        <v>105471</v>
+        <v>8430</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2154,34 +2159,43 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221144</v>
+        <v>106554</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>676690</v>
+        <v>676813</v>
       </c>
       <c r="R16" t="n">
-        <v>6615799</v>
+        <v>6615903</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2222,6 +2236,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2240,10 +2255,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122843607</v>
+        <v>122842950</v>
       </c>
       <c r="B17" t="n">
-        <v>100631</v>
+        <v>105471</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2256,21 +2271,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2280,10 +2295,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>676666</v>
+        <v>676690</v>
       </c>
       <c r="R17" t="n">
-        <v>6615819</v>
+        <v>6615799</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2342,10 +2357,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122842185</v>
+        <v>122841332</v>
       </c>
       <c r="B18" t="n">
-        <v>100631</v>
+        <v>57494</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2354,38 +2369,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>676831</v>
+        <v>676864</v>
       </c>
       <c r="R18" t="n">
-        <v>6615990</v>
+        <v>6615776</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2444,10 +2464,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122840930</v>
+        <v>122841097</v>
       </c>
       <c r="B19" t="n">
-        <v>57494</v>
+        <v>5173</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2456,31 +2476,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2489,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>676913</v>
+        <v>676861</v>
       </c>
       <c r="R19" t="n">
-        <v>6615763</v>
+        <v>6615758</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2551,10 +2571,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122840989</v>
+        <v>122842792</v>
       </c>
       <c r="B20" t="n">
-        <v>5173</v>
+        <v>90917</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2567,39 +2587,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>676899</v>
+        <v>676683</v>
       </c>
       <c r="R20" t="n">
-        <v>6615760</v>
+        <v>6615843</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2658,10 +2673,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122842434</v>
+        <v>122845926</v>
       </c>
       <c r="B21" t="n">
-        <v>57494</v>
+        <v>90917</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2670,43 +2685,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>676739</v>
+        <v>677084</v>
       </c>
       <c r="R21" t="n">
-        <v>6615944</v>
+        <v>6615718</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2765,10 +2775,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122840922</v>
+        <v>122842088</v>
       </c>
       <c r="B22" t="n">
-        <v>105471</v>
+        <v>100631</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2781,34 +2791,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>676912</v>
+        <v>676779</v>
       </c>
       <c r="R22" t="n">
-        <v>6615761</v>
+        <v>6615963</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2867,10 +2877,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122842088</v>
+        <v>122842819</v>
       </c>
       <c r="B23" t="n">
-        <v>100631</v>
+        <v>105471</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2883,34 +2893,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>676779</v>
+        <v>676682</v>
       </c>
       <c r="R23" t="n">
-        <v>6615963</v>
+        <v>6615846</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2969,7 +2979,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122841077</v>
+        <v>122842748</v>
       </c>
       <c r="B24" t="n">
         <v>5193</v>
@@ -3003,25 +3013,21 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>676870</v>
+        <v>676684</v>
       </c>
       <c r="R24" t="n">
-        <v>6615757</v>
+        <v>6615835</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3062,7 +3068,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3081,10 +3086,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122845736</v>
+        <v>122842557</v>
       </c>
       <c r="B25" t="n">
-        <v>8441</v>
+        <v>90952</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3093,43 +3098,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>677104</v>
+        <v>676745</v>
       </c>
       <c r="R25" t="n">
-        <v>6615675</v>
+        <v>6615878</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3188,10 +3188,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122842401</v>
+        <v>122840896</v>
       </c>
       <c r="B26" t="n">
-        <v>57494</v>
+        <v>5358</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3204,39 +3204,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>101728</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>676742</v>
+        <v>676913</v>
       </c>
       <c r="R26" t="n">
-        <v>6615954</v>
+        <v>6615766</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3295,10 +3295,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122840378</v>
+        <v>122841068</v>
       </c>
       <c r="B27" t="n">
-        <v>57848</v>
+        <v>4867</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3311,27 +3311,27 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103015</v>
+        <v>101675</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3340,10 +3340,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>676985</v>
+        <v>676872</v>
       </c>
       <c r="R27" t="n">
-        <v>6615696</v>
+        <v>6615746</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3402,10 +3402,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122842273</v>
+        <v>122842680</v>
       </c>
       <c r="B28" t="n">
-        <v>100631</v>
+        <v>57848</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3418,34 +3418,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>676787</v>
+        <v>676711</v>
       </c>
       <c r="R28" t="n">
-        <v>6615980</v>
+        <v>6615822</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3504,10 +3509,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122840972</v>
+        <v>122842273</v>
       </c>
       <c r="B29" t="n">
-        <v>90952</v>
+        <v>100631</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3516,38 +3521,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>676898</v>
+        <v>676787</v>
       </c>
       <c r="R29" t="n">
-        <v>6615759</v>
+        <v>6615980</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3606,10 +3611,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122845880</v>
+        <v>122842133</v>
       </c>
       <c r="B30" t="n">
-        <v>90970</v>
+        <v>100631</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3618,38 +3623,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>677085</v>
+        <v>676838</v>
       </c>
       <c r="R30" t="n">
-        <v>6615732</v>
+        <v>6615977</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3708,10 +3713,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122842819</v>
+        <v>122845093</v>
       </c>
       <c r="B31" t="n">
-        <v>105471</v>
+        <v>90917</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3724,34 +3729,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221144</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>676682</v>
+        <v>676956</v>
       </c>
       <c r="R31" t="n">
-        <v>6615846</v>
+        <v>6615718</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3810,10 +3815,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122845448</v>
+        <v>122840989</v>
       </c>
       <c r="B32" t="n">
-        <v>105471</v>
+        <v>5173</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3826,34 +3831,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221144</v>
+        <v>100526</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>676972</v>
+        <v>676899</v>
       </c>
       <c r="R32" t="n">
-        <v>6615705</v>
+        <v>6615760</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3912,10 +3922,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122840495</v>
+        <v>122842832</v>
       </c>
       <c r="B33" t="n">
-        <v>5193</v>
+        <v>57631</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3924,46 +3934,46 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>105930</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>676936</v>
+        <v>676682</v>
       </c>
       <c r="R33" t="n">
-        <v>6615736</v>
+        <v>6615846</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4019,10 +4029,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122840896</v>
+        <v>122840652</v>
       </c>
       <c r="B34" t="n">
-        <v>5358</v>
+        <v>90917</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4031,43 +4041,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>101728</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>676913</v>
+        <v>676670</v>
       </c>
       <c r="R34" t="n">
-        <v>6615766</v>
+        <v>6615860</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4126,10 +4131,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122841097</v>
+        <v>122842434</v>
       </c>
       <c r="B35" t="n">
-        <v>5173</v>
+        <v>57494</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4138,43 +4143,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>676861</v>
+        <v>676739</v>
       </c>
       <c r="R35" t="n">
-        <v>6615758</v>
+        <v>6615944</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4233,10 +4238,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122840392</v>
+        <v>122840804</v>
       </c>
       <c r="B36" t="n">
-        <v>57494</v>
+        <v>5358</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4249,27 +4254,27 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>101728</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4278,10 +4283,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>676983</v>
+        <v>676921</v>
       </c>
       <c r="R36" t="n">
-        <v>6615701</v>
+        <v>6615744</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4340,10 +4345,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122842479</v>
+        <v>122842401</v>
       </c>
       <c r="B37" t="n">
-        <v>8430</v>
+        <v>57494</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4352,31 +4357,31 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4385,10 +4390,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>676756</v>
+        <v>676742</v>
       </c>
       <c r="R37" t="n">
-        <v>6615927</v>
+        <v>6615954</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4447,10 +4452,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122843696</v>
+        <v>122840392</v>
       </c>
       <c r="B38" t="n">
-        <v>90970</v>
+        <v>57494</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4463,34 +4468,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>676651</v>
+        <v>676983</v>
       </c>
       <c r="R38" t="n">
-        <v>6615875</v>
+        <v>6615701</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4549,10 +4559,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122845245</v>
+        <v>122842144</v>
       </c>
       <c r="B39" t="n">
-        <v>8441</v>
+        <v>100631</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4565,39 +4575,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>222498</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>677001</v>
+        <v>676841</v>
       </c>
       <c r="R39" t="n">
-        <v>6615675</v>
+        <v>6615983</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4656,10 +4661,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122842133</v>
+        <v>122840495</v>
       </c>
       <c r="B40" t="n">
-        <v>100631</v>
+        <v>5193</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4672,34 +4677,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>676838</v>
+        <v>676936</v>
       </c>
       <c r="R40" t="n">
-        <v>6615977</v>
+        <v>6615736</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4758,10 +4768,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122845926</v>
+        <v>122841077</v>
       </c>
       <c r="B41" t="n">
-        <v>90917</v>
+        <v>5193</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4774,34 +4784,43 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>105930</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>677084</v>
+        <v>676870</v>
       </c>
       <c r="R41" t="n">
-        <v>6615718</v>
+        <v>6615757</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4842,6 +4861,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4860,10 +4880,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122840804</v>
+        <v>122845448</v>
       </c>
       <c r="B42" t="n">
-        <v>5358</v>
+        <v>105471</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4872,43 +4892,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>101728</v>
+        <v>221144</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>676921</v>
+        <v>676972</v>
       </c>
       <c r="R42" t="n">
-        <v>6615744</v>
+        <v>6615705</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4967,10 +4982,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122845093</v>
+        <v>122840992</v>
       </c>
       <c r="B43" t="n">
-        <v>90917</v>
+        <v>90952</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4979,25 +4994,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5007,10 +5022,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>676956</v>
+        <v>676900</v>
       </c>
       <c r="R43" t="n">
-        <v>6615718</v>
+        <v>6615757</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5069,10 +5084,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122840623</v>
+        <v>122840972</v>
       </c>
       <c r="B44" t="n">
-        <v>57494</v>
+        <v>90952</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5085,39 +5100,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>676932</v>
+        <v>676898</v>
       </c>
       <c r="R44" t="n">
-        <v>6615725</v>
+        <v>6615759</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5176,10 +5186,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122842680</v>
+        <v>122842185</v>
       </c>
       <c r="B45" t="n">
-        <v>57848</v>
+        <v>100631</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5192,39 +5202,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>676711</v>
+        <v>676831</v>
       </c>
       <c r="R45" t="n">
-        <v>6615822</v>
+        <v>6615990</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5283,10 +5288,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122845288</v>
+        <v>122840922</v>
       </c>
       <c r="B46" t="n">
-        <v>8430</v>
+        <v>105471</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5299,39 +5304,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106554</v>
+        <v>221144</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>677007</v>
+        <v>676912</v>
       </c>
       <c r="R46" t="n">
-        <v>6615684</v>
+        <v>6615761</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5390,10 +5390,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122843888</v>
+        <v>122841986</v>
       </c>
       <c r="B47" t="n">
-        <v>8430</v>
+        <v>105471</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5406,43 +5406,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106554</v>
+        <v>221144</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>676813</v>
+        <v>676779</v>
       </c>
       <c r="R47" t="n">
-        <v>6615903</v>
+        <v>6615963</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5483,7 +5474,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5502,10 +5492,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122842206</v>
+        <v>122842479</v>
       </c>
       <c r="B48" t="n">
-        <v>100631</v>
+        <v>8430</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5518,34 +5508,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>676816</v>
+        <v>676756</v>
       </c>
       <c r="R48" t="n">
-        <v>6615981</v>
+        <v>6615927</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5604,10 +5599,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122842144</v>
+        <v>122843861</v>
       </c>
       <c r="B49" t="n">
-        <v>100631</v>
+        <v>57494</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5616,38 +5611,43 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>676841</v>
+        <v>676804</v>
       </c>
       <c r="R49" t="n">
-        <v>6615983</v>
+        <v>6615893</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>

--- a/artfynd/A 9000-2025 artfynd.xlsx
+++ b/artfynd/A 9000-2025 artfynd.xlsx
@@ -2979,10 +2979,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122842748</v>
+        <v>122842557</v>
       </c>
       <c r="B24" t="n">
-        <v>5193</v>
+        <v>90952</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2991,43 +2991,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>676684</v>
+        <v>676745</v>
       </c>
       <c r="R24" t="n">
-        <v>6615835</v>
+        <v>6615878</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3086,10 +3081,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122842557</v>
+        <v>122842748</v>
       </c>
       <c r="B25" t="n">
-        <v>90952</v>
+        <v>5193</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3098,38 +3093,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>676745</v>
+        <v>676684</v>
       </c>
       <c r="R25" t="n">
-        <v>6615878</v>
+        <v>6615835</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -5186,10 +5186,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122842185</v>
+        <v>122840922</v>
       </c>
       <c r="B45" t="n">
-        <v>100631</v>
+        <v>105471</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5202,34 +5202,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>676831</v>
+        <v>676912</v>
       </c>
       <c r="R45" t="n">
-        <v>6615990</v>
+        <v>6615761</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5288,7 +5288,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122840922</v>
+        <v>122841986</v>
       </c>
       <c r="B46" t="n">
         <v>105471</v>
@@ -5324,14 +5324,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>676912</v>
+        <v>676779</v>
       </c>
       <c r="R46" t="n">
-        <v>6615761</v>
+        <v>6615963</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5390,10 +5390,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122841986</v>
+        <v>122842185</v>
       </c>
       <c r="B47" t="n">
-        <v>105471</v>
+        <v>100631</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5406,21 +5406,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5430,10 +5430,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>676779</v>
+        <v>676831</v>
       </c>
       <c r="R47" t="n">
-        <v>6615963</v>
+        <v>6615990</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5492,10 +5492,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122842479</v>
+        <v>122843861</v>
       </c>
       <c r="B48" t="n">
-        <v>8430</v>
+        <v>57494</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5504,31 +5504,31 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5537,10 +5537,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>676756</v>
+        <v>676804</v>
       </c>
       <c r="R48" t="n">
-        <v>6615927</v>
+        <v>6615893</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5599,10 +5599,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122843861</v>
+        <v>122842479</v>
       </c>
       <c r="B49" t="n">
-        <v>57494</v>
+        <v>8430</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5611,31 +5611,31 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5644,10 +5644,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>676804</v>
+        <v>676756</v>
       </c>
       <c r="R49" t="n">
-        <v>6615893</v>
+        <v>6615927</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>

--- a/artfynd/A 9000-2025 artfynd.xlsx
+++ b/artfynd/A 9000-2025 artfynd.xlsx
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122840930</v>
+        <v>122840378</v>
       </c>
       <c r="B5" t="n">
-        <v>57494</v>
+        <v>57848</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,20 +1003,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1027,7 +1027,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>676913</v>
+        <v>676985</v>
       </c>
       <c r="R5" t="n">
-        <v>6615763</v>
+        <v>6615696</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122840378</v>
+        <v>122840930</v>
       </c>
       <c r="B6" t="n">
-        <v>57848</v>
+        <v>57494</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1110,20 +1110,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1134,7 +1134,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>676985</v>
+        <v>676913</v>
       </c>
       <c r="R6" t="n">
-        <v>6615696</v>
+        <v>6615763</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -3402,10 +3402,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122842680</v>
+        <v>122842273</v>
       </c>
       <c r="B28" t="n">
-        <v>57848</v>
+        <v>100631</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3418,39 +3418,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>676711</v>
+        <v>676787</v>
       </c>
       <c r="R28" t="n">
-        <v>6615822</v>
+        <v>6615980</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3509,7 +3504,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122842273</v>
+        <v>122842133</v>
       </c>
       <c r="B29" t="n">
         <v>100631</v>
@@ -3549,10 +3544,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>676787</v>
+        <v>676838</v>
       </c>
       <c r="R29" t="n">
-        <v>6615980</v>
+        <v>6615977</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3611,10 +3606,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122842133</v>
+        <v>122842680</v>
       </c>
       <c r="B30" t="n">
-        <v>100631</v>
+        <v>57848</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3627,34 +3622,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>676838</v>
+        <v>676711</v>
       </c>
       <c r="R30" t="n">
-        <v>6615977</v>
+        <v>6615822</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -5492,10 +5492,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122843861</v>
+        <v>122842479</v>
       </c>
       <c r="B48" t="n">
-        <v>57494</v>
+        <v>8430</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5504,31 +5504,31 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5537,10 +5537,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>676804</v>
+        <v>676756</v>
       </c>
       <c r="R48" t="n">
-        <v>6615893</v>
+        <v>6615927</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5599,10 +5599,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122842479</v>
+        <v>122843861</v>
       </c>
       <c r="B49" t="n">
-        <v>8430</v>
+        <v>57494</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5611,31 +5611,31 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5644,10 +5644,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>676756</v>
+        <v>676804</v>
       </c>
       <c r="R49" t="n">
-        <v>6615927</v>
+        <v>6615893</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>

--- a/artfynd/A 9000-2025 artfynd.xlsx
+++ b/artfynd/A 9000-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122843664</v>
+        <v>122842479</v>
       </c>
       <c r="B2" t="n">
-        <v>100631</v>
+        <v>8430</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>676656</v>
+        <v>676756</v>
       </c>
       <c r="R2" t="n">
-        <v>6615859</v>
+        <v>6615927</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122845288</v>
+        <v>122842133</v>
       </c>
       <c r="B3" t="n">
-        <v>8430</v>
+        <v>100631</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,39 +798,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>677007</v>
+        <v>676838</v>
       </c>
       <c r="R3" t="n">
-        <v>6615684</v>
+        <v>6615977</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122840623</v>
+        <v>122842680</v>
       </c>
       <c r="B4" t="n">
-        <v>57494</v>
+        <v>57848</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,20 +896,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -920,19 +920,19 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>676932</v>
+        <v>676711</v>
       </c>
       <c r="R4" t="n">
-        <v>6615725</v>
+        <v>6615822</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122840378</v>
+        <v>122842185</v>
       </c>
       <c r="B5" t="n">
-        <v>57848</v>
+        <v>100631</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,39 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>676985</v>
+        <v>676831</v>
       </c>
       <c r="R5" t="n">
-        <v>6615696</v>
+        <v>6615990</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122840930</v>
+        <v>122845926</v>
       </c>
       <c r="B6" t="n">
-        <v>57494</v>
+        <v>90917</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1110,43 +1105,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>676913</v>
+        <v>677084</v>
       </c>
       <c r="R6" t="n">
-        <v>6615763</v>
+        <v>6615718</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122843607</v>
+        <v>122842832</v>
       </c>
       <c r="B7" t="n">
-        <v>100631</v>
+        <v>57631</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,41 +1207,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>676666</v>
+        <v>676682</v>
       </c>
       <c r="R7" t="n">
-        <v>6615819</v>
+        <v>6615846</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1307,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122842206</v>
+        <v>122845245</v>
       </c>
       <c r="B8" t="n">
-        <v>100631</v>
+        <v>8441</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,34 +1318,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>676816</v>
+        <v>677001</v>
       </c>
       <c r="R8" t="n">
-        <v>6615981</v>
+        <v>6615675</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122843696</v>
+        <v>122840392</v>
       </c>
       <c r="B9" t="n">
-        <v>90970</v>
+        <v>57494</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,34 +1425,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>676651</v>
+        <v>676983</v>
       </c>
       <c r="R9" t="n">
-        <v>6615875</v>
+        <v>6615701</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1511,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122842642</v>
+        <v>122840378</v>
       </c>
       <c r="B10" t="n">
-        <v>100631</v>
+        <v>57848</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,34 +1532,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>676714</v>
+        <v>676985</v>
       </c>
       <c r="R10" t="n">
-        <v>6615824</v>
+        <v>6615696</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1613,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122845245</v>
+        <v>122840972</v>
       </c>
       <c r="B11" t="n">
-        <v>8441</v>
+        <v>90952</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1625,43 +1635,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>677001</v>
+        <v>676898</v>
       </c>
       <c r="R11" t="n">
-        <v>6615675</v>
+        <v>6615759</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1720,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122840712</v>
+        <v>122840992</v>
       </c>
       <c r="B12" t="n">
-        <v>4867</v>
+        <v>90952</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1732,46 +1737,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>101675</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>676921</v>
+        <v>676900</v>
       </c>
       <c r="R12" t="n">
-        <v>6615744</v>
+        <v>6615757</v>
       </c>
       <c r="S12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1827,10 +1827,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122841301</v>
+        <v>122841097</v>
       </c>
       <c r="B13" t="n">
-        <v>8430</v>
+        <v>5173</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1843,21 +1843,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106554</v>
+        <v>100526</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1872,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>676893</v>
+        <v>676861</v>
       </c>
       <c r="R13" t="n">
-        <v>6615790</v>
+        <v>6615758</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1934,10 +1934,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122845736</v>
+        <v>122843888</v>
       </c>
       <c r="B14" t="n">
-        <v>8441</v>
+        <v>8430</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1950,39 +1950,43 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>677104</v>
+        <v>676813</v>
       </c>
       <c r="R14" t="n">
-        <v>6615675</v>
+        <v>6615903</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2023,6 +2027,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2041,10 +2046,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122845880</v>
+        <v>122840712</v>
       </c>
       <c r="B15" t="n">
-        <v>90970</v>
+        <v>4867</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2053,41 +2058,46 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>101675</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>677085</v>
+        <v>676921</v>
       </c>
       <c r="R15" t="n">
-        <v>6615732</v>
+        <v>6615744</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2143,10 +2153,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122843888</v>
+        <v>122840652</v>
       </c>
       <c r="B16" t="n">
-        <v>8430</v>
+        <v>90917</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2159,43 +2169,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106554</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>676813</v>
+        <v>676670</v>
       </c>
       <c r="R16" t="n">
-        <v>6615903</v>
+        <v>6615860</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2236,7 +2237,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2255,7 +2255,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122842950</v>
+        <v>122842819</v>
       </c>
       <c r="B17" t="n">
         <v>105471</v>
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>676690</v>
+        <v>676682</v>
       </c>
       <c r="R17" t="n">
-        <v>6615799</v>
+        <v>6615846</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2357,10 +2357,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122841332</v>
+        <v>122845288</v>
       </c>
       <c r="B18" t="n">
-        <v>57494</v>
+        <v>8430</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2369,31 +2369,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2402,10 +2402,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>676864</v>
+        <v>677007</v>
       </c>
       <c r="R18" t="n">
-        <v>6615776</v>
+        <v>6615684</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2464,10 +2464,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122841097</v>
+        <v>122842401</v>
       </c>
       <c r="B19" t="n">
-        <v>5173</v>
+        <v>57494</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2476,43 +2476,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>676861</v>
+        <v>676742</v>
       </c>
       <c r="R19" t="n">
-        <v>6615758</v>
+        <v>6615954</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2571,10 +2571,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122842792</v>
+        <v>122841077</v>
       </c>
       <c r="B20" t="n">
-        <v>90917</v>
+        <v>5193</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2587,34 +2587,43 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>105930</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>676683</v>
+        <v>676870</v>
       </c>
       <c r="R20" t="n">
-        <v>6615843</v>
+        <v>6615757</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2655,6 +2664,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2673,7 +2683,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122845926</v>
+        <v>122842792</v>
       </c>
       <c r="B21" t="n">
         <v>90917</v>
@@ -2709,14 +2719,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>677084</v>
+        <v>676683</v>
       </c>
       <c r="R21" t="n">
-        <v>6615718</v>
+        <v>6615843</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2775,10 +2785,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122842088</v>
+        <v>122842557</v>
       </c>
       <c r="B22" t="n">
-        <v>100631</v>
+        <v>90952</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2787,25 +2797,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2815,10 +2825,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>676779</v>
+        <v>676745</v>
       </c>
       <c r="R22" t="n">
-        <v>6615963</v>
+        <v>6615878</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2877,10 +2887,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122842819</v>
+        <v>122842642</v>
       </c>
       <c r="B23" t="n">
-        <v>105471</v>
+        <v>100631</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2893,34 +2903,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>676682</v>
+        <v>676714</v>
       </c>
       <c r="R23" t="n">
-        <v>6615846</v>
+        <v>6615824</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2979,10 +2989,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122842557</v>
+        <v>122840930</v>
       </c>
       <c r="B24" t="n">
-        <v>90952</v>
+        <v>57494</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2995,34 +3005,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>676745</v>
+        <v>676913</v>
       </c>
       <c r="R24" t="n">
-        <v>6615878</v>
+        <v>6615763</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3081,10 +3096,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122842748</v>
+        <v>122841068</v>
       </c>
       <c r="B25" t="n">
-        <v>5193</v>
+        <v>4867</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3097,21 +3112,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>105930</v>
+        <v>101675</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3122,14 +3137,14 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>676684</v>
+        <v>676872</v>
       </c>
       <c r="R25" t="n">
-        <v>6615835</v>
+        <v>6615746</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3188,7 +3203,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122840896</v>
+        <v>122840804</v>
       </c>
       <c r="B26" t="n">
         <v>5358</v>
@@ -3233,10 +3248,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>676913</v>
+        <v>676921</v>
       </c>
       <c r="R26" t="n">
-        <v>6615766</v>
+        <v>6615744</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3295,10 +3310,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122841068</v>
+        <v>122841332</v>
       </c>
       <c r="B27" t="n">
-        <v>4867</v>
+        <v>57494</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3307,31 +3322,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>101675</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3340,10 +3355,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>676872</v>
+        <v>676864</v>
       </c>
       <c r="R27" t="n">
-        <v>6615746</v>
+        <v>6615776</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3402,10 +3417,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122842273</v>
+        <v>122841301</v>
       </c>
       <c r="B28" t="n">
-        <v>100631</v>
+        <v>8430</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3418,34 +3433,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>676787</v>
+        <v>676893</v>
       </c>
       <c r="R28" t="n">
-        <v>6615980</v>
+        <v>6615790</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3504,10 +3524,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122842133</v>
+        <v>122841986</v>
       </c>
       <c r="B29" t="n">
-        <v>100631</v>
+        <v>105471</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3520,21 +3540,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3544,10 +3564,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>676838</v>
+        <v>676779</v>
       </c>
       <c r="R29" t="n">
-        <v>6615977</v>
+        <v>6615963</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3606,10 +3626,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122842680</v>
+        <v>122843664</v>
       </c>
       <c r="B30" t="n">
-        <v>57848</v>
+        <v>100631</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3622,39 +3642,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>676711</v>
+        <v>676656</v>
       </c>
       <c r="R30" t="n">
-        <v>6615822</v>
+        <v>6615859</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3713,10 +3728,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122845093</v>
+        <v>122842273</v>
       </c>
       <c r="B31" t="n">
-        <v>90917</v>
+        <v>100631</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3729,34 +3744,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>676956</v>
+        <v>676787</v>
       </c>
       <c r="R31" t="n">
-        <v>6615718</v>
+        <v>6615980</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3815,10 +3830,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122840989</v>
+        <v>122842950</v>
       </c>
       <c r="B32" t="n">
-        <v>5173</v>
+        <v>105471</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3831,39 +3846,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100526</v>
+        <v>221144</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>676899</v>
+        <v>676690</v>
       </c>
       <c r="R32" t="n">
-        <v>6615760</v>
+        <v>6615799</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3922,10 +3932,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122842832</v>
+        <v>122843861</v>
       </c>
       <c r="B33" t="n">
-        <v>57631</v>
+        <v>57494</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3938,42 +3948,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>676682</v>
+        <v>676804</v>
       </c>
       <c r="R33" t="n">
-        <v>6615846</v>
+        <v>6615893</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4029,7 +4039,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122840652</v>
+        <v>122845093</v>
       </c>
       <c r="B34" t="n">
         <v>90917</v>
@@ -4065,14 +4075,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>676670</v>
+        <v>676956</v>
       </c>
       <c r="R34" t="n">
-        <v>6615860</v>
+        <v>6615718</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4131,10 +4141,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122842434</v>
+        <v>122842088</v>
       </c>
       <c r="B35" t="n">
-        <v>57494</v>
+        <v>100631</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4143,43 +4153,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>676739</v>
+        <v>676779</v>
       </c>
       <c r="R35" t="n">
-        <v>6615944</v>
+        <v>6615963</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4238,10 +4243,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122840804</v>
+        <v>122845448</v>
       </c>
       <c r="B36" t="n">
-        <v>5358</v>
+        <v>105471</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4250,43 +4255,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>101728</v>
+        <v>221144</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>676921</v>
+        <v>676972</v>
       </c>
       <c r="R36" t="n">
-        <v>6615744</v>
+        <v>6615705</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4345,10 +4345,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122842401</v>
+        <v>122840896</v>
       </c>
       <c r="B37" t="n">
-        <v>57494</v>
+        <v>5358</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4361,39 +4361,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>101728</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>676742</v>
+        <v>676913</v>
       </c>
       <c r="R37" t="n">
-        <v>6615954</v>
+        <v>6615766</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4452,7 +4452,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122840392</v>
+        <v>122842434</v>
       </c>
       <c r="B38" t="n">
         <v>57494</v>
@@ -4488,19 +4488,19 @@
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>676983</v>
+        <v>676739</v>
       </c>
       <c r="R38" t="n">
-        <v>6615701</v>
+        <v>6615944</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4559,10 +4559,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122842144</v>
+        <v>122840495</v>
       </c>
       <c r="B39" t="n">
-        <v>100631</v>
+        <v>5193</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4575,34 +4575,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>676841</v>
+        <v>676936</v>
       </c>
       <c r="R39" t="n">
-        <v>6615983</v>
+        <v>6615736</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4661,10 +4666,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122840495</v>
+        <v>122843696</v>
       </c>
       <c r="B40" t="n">
-        <v>5193</v>
+        <v>90970</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4673,43 +4678,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>105930</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>676936</v>
+        <v>676651</v>
       </c>
       <c r="R40" t="n">
-        <v>6615736</v>
+        <v>6615875</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4768,10 +4768,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122841077</v>
+        <v>122845880</v>
       </c>
       <c r="B41" t="n">
-        <v>5193</v>
+        <v>90970</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4780,47 +4780,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>105930</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>676870</v>
+        <v>677085</v>
       </c>
       <c r="R41" t="n">
-        <v>6615757</v>
+        <v>6615732</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4861,7 +4852,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4880,10 +4870,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122845448</v>
+        <v>122840623</v>
       </c>
       <c r="B42" t="n">
-        <v>105471</v>
+        <v>57494</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4892,38 +4882,43 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>676972</v>
+        <v>676932</v>
       </c>
       <c r="R42" t="n">
-        <v>6615705</v>
+        <v>6615725</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4982,10 +4977,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122840992</v>
+        <v>122842748</v>
       </c>
       <c r="B43" t="n">
-        <v>90952</v>
+        <v>5193</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4994,38 +4989,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>676900</v>
+        <v>676684</v>
       </c>
       <c r="R43" t="n">
-        <v>6615757</v>
+        <v>6615835</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5084,10 +5084,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122840972</v>
+        <v>122840922</v>
       </c>
       <c r="B44" t="n">
-        <v>90952</v>
+        <v>105471</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5096,25 +5096,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5124,10 +5124,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>676898</v>
+        <v>676912</v>
       </c>
       <c r="R44" t="n">
-        <v>6615759</v>
+        <v>6615761</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5186,10 +5186,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122840922</v>
+        <v>122842144</v>
       </c>
       <c r="B45" t="n">
-        <v>105471</v>
+        <v>100631</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5202,34 +5202,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>676912</v>
+        <v>676841</v>
       </c>
       <c r="R45" t="n">
-        <v>6615761</v>
+        <v>6615983</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5288,10 +5288,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122841986</v>
+        <v>122840989</v>
       </c>
       <c r="B46" t="n">
-        <v>105471</v>
+        <v>5173</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5304,34 +5304,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221144</v>
+        <v>100526</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>676779</v>
+        <v>676899</v>
       </c>
       <c r="R46" t="n">
-        <v>6615963</v>
+        <v>6615760</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5390,7 +5395,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122842185</v>
+        <v>122843607</v>
       </c>
       <c r="B47" t="n">
         <v>100631</v>
@@ -5426,14 +5431,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>676831</v>
+        <v>676666</v>
       </c>
       <c r="R47" t="n">
-        <v>6615990</v>
+        <v>6615819</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5492,10 +5497,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122842479</v>
+        <v>122842206</v>
       </c>
       <c r="B48" t="n">
-        <v>8430</v>
+        <v>100631</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5508,39 +5513,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>676756</v>
+        <v>676816</v>
       </c>
       <c r="R48" t="n">
-        <v>6615927</v>
+        <v>6615981</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5599,10 +5599,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122843861</v>
+        <v>122845736</v>
       </c>
       <c r="B49" t="n">
-        <v>57494</v>
+        <v>8441</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5611,43 +5611,43 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>676804</v>
+        <v>677104</v>
       </c>
       <c r="R49" t="n">
-        <v>6615893</v>
+        <v>6615675</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>

--- a/artfynd/A 9000-2025 artfynd.xlsx
+++ b/artfynd/A 9000-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122842479</v>
+        <v>122840712</v>
       </c>
       <c r="B2" t="n">
-        <v>8430</v>
+        <v>4867</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106554</v>
+        <v>101675</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -716,17 +716,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>676756</v>
+        <v>676921</v>
       </c>
       <c r="R2" t="n">
-        <v>6615927</v>
+        <v>6615744</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122842133</v>
+        <v>122840804</v>
       </c>
       <c r="B3" t="n">
-        <v>100631</v>
+        <v>5358</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,38 +794,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>101728</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>676838</v>
+        <v>676921</v>
       </c>
       <c r="R3" t="n">
-        <v>6615977</v>
+        <v>6615744</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122842680</v>
+        <v>122840623</v>
       </c>
       <c r="B4" t="n">
-        <v>57848</v>
+        <v>57494</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,20 +901,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -920,19 +925,19 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>676711</v>
+        <v>676932</v>
       </c>
       <c r="R4" t="n">
-        <v>6615822</v>
+        <v>6615725</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122842185</v>
+        <v>122845448</v>
       </c>
       <c r="B5" t="n">
-        <v>100631</v>
+        <v>105471</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,34 +1012,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>676831</v>
+        <v>676972</v>
       </c>
       <c r="R5" t="n">
-        <v>6615990</v>
+        <v>6615705</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122845926</v>
+        <v>122841097</v>
       </c>
       <c r="B6" t="n">
-        <v>90917</v>
+        <v>5173</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,34 +1114,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>677084</v>
+        <v>676861</v>
       </c>
       <c r="R6" t="n">
-        <v>6615718</v>
+        <v>6615758</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122842832</v>
+        <v>122840989</v>
       </c>
       <c r="B7" t="n">
-        <v>57631</v>
+        <v>5173</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,46 +1217,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>676682</v>
+        <v>676899</v>
       </c>
       <c r="R7" t="n">
-        <v>6615846</v>
+        <v>6615760</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1302,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122845245</v>
+        <v>122842133</v>
       </c>
       <c r="B8" t="n">
-        <v>8441</v>
+        <v>100631</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1318,39 +1328,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>677001</v>
+        <v>676838</v>
       </c>
       <c r="R8" t="n">
-        <v>6615675</v>
+        <v>6615977</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122840392</v>
+        <v>122840922</v>
       </c>
       <c r="B9" t="n">
-        <v>57494</v>
+        <v>105471</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1421,43 +1426,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>676983</v>
+        <v>676912</v>
       </c>
       <c r="R9" t="n">
-        <v>6615701</v>
+        <v>6615761</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122840378</v>
+        <v>122842950</v>
       </c>
       <c r="B10" t="n">
-        <v>57848</v>
+        <v>105471</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1532,39 +1532,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>676985</v>
+        <v>676690</v>
       </c>
       <c r="R10" t="n">
-        <v>6615696</v>
+        <v>6615799</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1623,10 +1618,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122840972</v>
+        <v>122843664</v>
       </c>
       <c r="B11" t="n">
-        <v>90952</v>
+        <v>100631</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1635,38 +1630,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>676898</v>
+        <v>676656</v>
       </c>
       <c r="R11" t="n">
-        <v>6615759</v>
+        <v>6615859</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1725,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122840992</v>
+        <v>122842680</v>
       </c>
       <c r="B12" t="n">
-        <v>90952</v>
+        <v>57848</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1737,38 +1732,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>676900</v>
+        <v>676711</v>
       </c>
       <c r="R12" t="n">
-        <v>6615757</v>
+        <v>6615822</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1827,10 +1827,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122841097</v>
+        <v>122841301</v>
       </c>
       <c r="B13" t="n">
-        <v>5173</v>
+        <v>8430</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1843,21 +1843,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100526</v>
+        <v>106554</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1872,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>676861</v>
+        <v>676893</v>
       </c>
       <c r="R13" t="n">
-        <v>6615758</v>
+        <v>6615790</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1934,10 +1934,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122843888</v>
+        <v>122840392</v>
       </c>
       <c r="B14" t="n">
-        <v>8430</v>
+        <v>57494</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1946,47 +1946,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>676813</v>
+        <v>676983</v>
       </c>
       <c r="R14" t="n">
-        <v>6615903</v>
+        <v>6615701</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2027,7 +2023,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2046,10 +2041,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122840712</v>
+        <v>122840930</v>
       </c>
       <c r="B15" t="n">
-        <v>4867</v>
+        <v>57494</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2058,31 +2053,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>101675</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2091,13 +2086,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>676921</v>
+        <v>676913</v>
       </c>
       <c r="R15" t="n">
-        <v>6615744</v>
+        <v>6615763</v>
       </c>
       <c r="S15" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2153,10 +2148,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122840652</v>
+        <v>122840896</v>
       </c>
       <c r="B16" t="n">
-        <v>90917</v>
+        <v>5358</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2165,38 +2160,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>101728</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>676670</v>
+        <v>676913</v>
       </c>
       <c r="R16" t="n">
-        <v>6615860</v>
+        <v>6615766</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2255,10 +2255,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122842819</v>
+        <v>122842185</v>
       </c>
       <c r="B17" t="n">
-        <v>105471</v>
+        <v>100631</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2271,34 +2271,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>676682</v>
+        <v>676831</v>
       </c>
       <c r="R17" t="n">
-        <v>6615846</v>
+        <v>6615990</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2357,10 +2357,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122845288</v>
+        <v>122840652</v>
       </c>
       <c r="B18" t="n">
-        <v>8430</v>
+        <v>90917</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2373,39 +2373,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106554</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>677007</v>
+        <v>676670</v>
       </c>
       <c r="R18" t="n">
-        <v>6615684</v>
+        <v>6615860</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2464,7 +2459,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122842401</v>
+        <v>122841332</v>
       </c>
       <c r="B19" t="n">
         <v>57494</v>
@@ -2505,14 +2500,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>676742</v>
+        <v>676864</v>
       </c>
       <c r="R19" t="n">
-        <v>6615954</v>
+        <v>6615776</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2571,10 +2566,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122841077</v>
+        <v>122843696</v>
       </c>
       <c r="B20" t="n">
-        <v>5193</v>
+        <v>90970</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2583,47 +2578,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>105930</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>676870</v>
+        <v>676651</v>
       </c>
       <c r="R20" t="n">
-        <v>6615757</v>
+        <v>6615875</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2664,7 +2650,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2683,10 +2668,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122842792</v>
+        <v>122845736</v>
       </c>
       <c r="B21" t="n">
-        <v>90917</v>
+        <v>8441</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2699,34 +2684,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>676683</v>
+        <v>677104</v>
       </c>
       <c r="R21" t="n">
-        <v>6615843</v>
+        <v>6615675</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2785,10 +2775,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122842557</v>
+        <v>122842401</v>
       </c>
       <c r="B22" t="n">
-        <v>90952</v>
+        <v>57494</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2801,34 +2791,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>676745</v>
+        <v>676742</v>
       </c>
       <c r="R22" t="n">
-        <v>6615878</v>
+        <v>6615954</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2989,10 +2984,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122840930</v>
+        <v>122842792</v>
       </c>
       <c r="B24" t="n">
-        <v>57494</v>
+        <v>90917</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3001,43 +2996,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>676913</v>
+        <v>676683</v>
       </c>
       <c r="R24" t="n">
-        <v>6615763</v>
+        <v>6615843</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3096,10 +3086,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122841068</v>
+        <v>122840378</v>
       </c>
       <c r="B25" t="n">
-        <v>4867</v>
+        <v>57848</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3112,27 +3102,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>101675</v>
+        <v>103015</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3141,10 +3131,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>676872</v>
+        <v>676985</v>
       </c>
       <c r="R25" t="n">
-        <v>6615746</v>
+        <v>6615696</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3203,10 +3193,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122840804</v>
+        <v>122842819</v>
       </c>
       <c r="B26" t="n">
-        <v>5358</v>
+        <v>105471</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3215,43 +3205,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>101728</v>
+        <v>221144</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>676921</v>
+        <v>676682</v>
       </c>
       <c r="R26" t="n">
-        <v>6615744</v>
+        <v>6615846</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3310,7 +3295,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122841332</v>
+        <v>122843861</v>
       </c>
       <c r="B27" t="n">
         <v>57494</v>
@@ -3351,14 +3336,14 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>676864</v>
+        <v>676804</v>
       </c>
       <c r="R27" t="n">
-        <v>6615776</v>
+        <v>6615893</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3417,10 +3402,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122841301</v>
+        <v>122841068</v>
       </c>
       <c r="B28" t="n">
-        <v>8430</v>
+        <v>4867</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3433,21 +3418,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106554</v>
+        <v>101675</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3462,10 +3447,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>676893</v>
+        <v>676872</v>
       </c>
       <c r="R28" t="n">
-        <v>6615790</v>
+        <v>6615746</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3524,10 +3509,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122841986</v>
+        <v>122841077</v>
       </c>
       <c r="B29" t="n">
-        <v>105471</v>
+        <v>5193</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3540,34 +3525,43 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221144</v>
+        <v>105930</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>676779</v>
+        <v>676870</v>
       </c>
       <c r="R29" t="n">
-        <v>6615963</v>
+        <v>6615757</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3608,6 +3602,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3626,10 +3621,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122843664</v>
+        <v>122840992</v>
       </c>
       <c r="B30" t="n">
-        <v>100631</v>
+        <v>90952</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3638,38 +3633,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>676656</v>
+        <v>676900</v>
       </c>
       <c r="R30" t="n">
-        <v>6615859</v>
+        <v>6615757</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3728,10 +3723,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122842273</v>
+        <v>122842748</v>
       </c>
       <c r="B31" t="n">
-        <v>100631</v>
+        <v>5193</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3744,34 +3739,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>676787</v>
+        <v>676684</v>
       </c>
       <c r="R31" t="n">
-        <v>6615980</v>
+        <v>6615835</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3830,10 +3830,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122842950</v>
+        <v>122842088</v>
       </c>
       <c r="B32" t="n">
-        <v>105471</v>
+        <v>100631</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3846,34 +3846,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>676690</v>
+        <v>676779</v>
       </c>
       <c r="R32" t="n">
-        <v>6615799</v>
+        <v>6615963</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3932,10 +3932,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122843861</v>
+        <v>122840972</v>
       </c>
       <c r="B33" t="n">
-        <v>57494</v>
+        <v>90952</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3948,39 +3948,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>676804</v>
+        <v>676898</v>
       </c>
       <c r="R33" t="n">
-        <v>6615893</v>
+        <v>6615759</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4039,10 +4034,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122845093</v>
+        <v>122842557</v>
       </c>
       <c r="B34" t="n">
-        <v>90917</v>
+        <v>90952</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4051,38 +4046,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>676956</v>
+        <v>676745</v>
       </c>
       <c r="R34" t="n">
-        <v>6615718</v>
+        <v>6615878</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4141,10 +4136,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122842088</v>
+        <v>122843888</v>
       </c>
       <c r="B35" t="n">
-        <v>100631</v>
+        <v>8430</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4157,34 +4152,43 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>676779</v>
+        <v>676813</v>
       </c>
       <c r="R35" t="n">
-        <v>6615963</v>
+        <v>6615903</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4225,6 +4229,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4243,10 +4248,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122845448</v>
+        <v>122842273</v>
       </c>
       <c r="B36" t="n">
-        <v>105471</v>
+        <v>100631</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4259,34 +4264,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>676972</v>
+        <v>676787</v>
       </c>
       <c r="R36" t="n">
-        <v>6615705</v>
+        <v>6615980</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4345,10 +4350,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122840896</v>
+        <v>122842144</v>
       </c>
       <c r="B37" t="n">
-        <v>5358</v>
+        <v>100631</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4357,43 +4362,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>101728</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>676913</v>
+        <v>676841</v>
       </c>
       <c r="R37" t="n">
-        <v>6615766</v>
+        <v>6615983</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4452,10 +4452,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122842434</v>
+        <v>122845926</v>
       </c>
       <c r="B38" t="n">
-        <v>57494</v>
+        <v>90917</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4464,43 +4464,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>676739</v>
+        <v>677084</v>
       </c>
       <c r="R38" t="n">
-        <v>6615944</v>
+        <v>6615718</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4666,10 +4661,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122843696</v>
+        <v>122841986</v>
       </c>
       <c r="B40" t="n">
-        <v>90970</v>
+        <v>105471</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4678,38 +4673,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>221144</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>676651</v>
+        <v>676779</v>
       </c>
       <c r="R40" t="n">
-        <v>6615875</v>
+        <v>6615963</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4768,10 +4763,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122845880</v>
+        <v>122843607</v>
       </c>
       <c r="B41" t="n">
-        <v>90970</v>
+        <v>100631</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4780,38 +4775,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>677085</v>
+        <v>676666</v>
       </c>
       <c r="R41" t="n">
-        <v>6615732</v>
+        <v>6615819</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4870,10 +4865,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122840623</v>
+        <v>122845288</v>
       </c>
       <c r="B42" t="n">
-        <v>57494</v>
+        <v>8430</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4882,31 +4877,31 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -4915,10 +4910,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>676932</v>
+        <v>677007</v>
       </c>
       <c r="R42" t="n">
-        <v>6615725</v>
+        <v>6615684</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4977,10 +4972,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122842748</v>
+        <v>122842479</v>
       </c>
       <c r="B43" t="n">
-        <v>5193</v>
+        <v>8430</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4993,21 +4988,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>105930</v>
+        <v>106554</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5018,14 +5013,14 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>676684</v>
+        <v>676756</v>
       </c>
       <c r="R43" t="n">
-        <v>6615835</v>
+        <v>6615927</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5084,10 +5079,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122840922</v>
+        <v>122845880</v>
       </c>
       <c r="B44" t="n">
-        <v>105471</v>
+        <v>90970</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5096,25 +5091,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221144</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5124,10 +5119,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>676912</v>
+        <v>677085</v>
       </c>
       <c r="R44" t="n">
-        <v>6615761</v>
+        <v>6615732</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5186,10 +5181,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122842144</v>
+        <v>122842434</v>
       </c>
       <c r="B45" t="n">
-        <v>100631</v>
+        <v>57494</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5198,38 +5193,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>676841</v>
+        <v>676739</v>
       </c>
       <c r="R45" t="n">
-        <v>6615983</v>
+        <v>6615944</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5288,10 +5288,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122840989</v>
+        <v>122845245</v>
       </c>
       <c r="B46" t="n">
-        <v>5173</v>
+        <v>8441</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5304,21 +5304,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5333,10 +5333,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>676899</v>
+        <v>677001</v>
       </c>
       <c r="R46" t="n">
-        <v>6615760</v>
+        <v>6615675</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5395,7 +5395,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122843607</v>
+        <v>122842206</v>
       </c>
       <c r="B47" t="n">
         <v>100631</v>
@@ -5431,14 +5431,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>676666</v>
+        <v>676816</v>
       </c>
       <c r="R47" t="n">
-        <v>6615819</v>
+        <v>6615981</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5497,10 +5497,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122842206</v>
+        <v>122845093</v>
       </c>
       <c r="B48" t="n">
-        <v>100631</v>
+        <v>90917</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5513,34 +5513,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>676816</v>
+        <v>676956</v>
       </c>
       <c r="R48" t="n">
-        <v>6615981</v>
+        <v>6615718</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5599,10 +5599,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122845736</v>
+        <v>122842832</v>
       </c>
       <c r="B49" t="n">
-        <v>8441</v>
+        <v>57631</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5611,46 +5611,46 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>677104</v>
+        <v>676682</v>
       </c>
       <c r="R49" t="n">
-        <v>6615675</v>
+        <v>6615846</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>

--- a/artfynd/A 9000-2025 artfynd.xlsx
+++ b/artfynd/A 9000-2025 artfynd.xlsx
@@ -1934,10 +1934,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122840392</v>
+        <v>122842185</v>
       </c>
       <c r="B14" t="n">
-        <v>57494</v>
+        <v>100631</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1946,43 +1946,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>676983</v>
+        <v>676831</v>
       </c>
       <c r="R14" t="n">
-        <v>6615701</v>
+        <v>6615990</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2041,7 +2036,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122840930</v>
+        <v>122840392</v>
       </c>
       <c r="B15" t="n">
         <v>57494</v>
@@ -2077,7 +2072,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2086,10 +2081,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>676913</v>
+        <v>676983</v>
       </c>
       <c r="R15" t="n">
-        <v>6615763</v>
+        <v>6615701</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2148,10 +2143,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122840896</v>
+        <v>122840930</v>
       </c>
       <c r="B16" t="n">
-        <v>5358</v>
+        <v>57494</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2164,27 +2159,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>101728</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2196,7 +2191,7 @@
         <v>676913</v>
       </c>
       <c r="R16" t="n">
-        <v>6615766</v>
+        <v>6615763</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2255,10 +2250,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122842185</v>
+        <v>122840896</v>
       </c>
       <c r="B17" t="n">
-        <v>100631</v>
+        <v>5358</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2267,38 +2262,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>101728</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>676831</v>
+        <v>676913</v>
       </c>
       <c r="R17" t="n">
-        <v>6615990</v>
+        <v>6615766</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -3509,10 +3509,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122841077</v>
+        <v>122840992</v>
       </c>
       <c r="B29" t="n">
-        <v>5193</v>
+        <v>90952</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3521,44 +3521,35 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>676870</v>
+        <v>676900</v>
       </c>
       <c r="R29" t="n">
         <v>6615757</v>
@@ -3602,7 +3593,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3621,10 +3611,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122840992</v>
+        <v>122841077</v>
       </c>
       <c r="B30" t="n">
-        <v>90952</v>
+        <v>5193</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3633,35 +3623,44 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>676900</v>
+        <v>676870</v>
       </c>
       <c r="R30" t="n">
         <v>6615757</v>
@@ -3705,6 +3704,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3932,10 +3932,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122840972</v>
+        <v>122843888</v>
       </c>
       <c r="B33" t="n">
-        <v>90952</v>
+        <v>8430</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3944,38 +3944,47 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>106554</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>676898</v>
+        <v>676813</v>
       </c>
       <c r="R33" t="n">
-        <v>6615759</v>
+        <v>6615903</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4016,6 +4025,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4034,10 +4044,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122842557</v>
+        <v>122842273</v>
       </c>
       <c r="B34" t="n">
-        <v>90952</v>
+        <v>100631</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4046,25 +4056,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4074,10 +4084,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>676745</v>
+        <v>676787</v>
       </c>
       <c r="R34" t="n">
-        <v>6615878</v>
+        <v>6615980</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4136,10 +4146,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122843888</v>
+        <v>122842144</v>
       </c>
       <c r="B35" t="n">
-        <v>8430</v>
+        <v>100631</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4152,43 +4162,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>676813</v>
+        <v>676841</v>
       </c>
       <c r="R35" t="n">
-        <v>6615903</v>
+        <v>6615983</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4229,7 +4230,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4248,10 +4248,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122842273</v>
+        <v>122840972</v>
       </c>
       <c r="B36" t="n">
-        <v>100631</v>
+        <v>90952</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4260,38 +4260,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>676787</v>
+        <v>676898</v>
       </c>
       <c r="R36" t="n">
-        <v>6615980</v>
+        <v>6615759</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4350,10 +4350,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122842144</v>
+        <v>122842557</v>
       </c>
       <c r="B37" t="n">
-        <v>100631</v>
+        <v>90952</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4362,25 +4362,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4390,10 +4390,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>676841</v>
+        <v>676745</v>
       </c>
       <c r="R37" t="n">
-        <v>6615983</v>
+        <v>6615878</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5181,10 +5181,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122842434</v>
+        <v>122842206</v>
       </c>
       <c r="B45" t="n">
-        <v>57494</v>
+        <v>100631</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5193,43 +5193,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>676739</v>
+        <v>676816</v>
       </c>
       <c r="R45" t="n">
-        <v>6615944</v>
+        <v>6615981</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5288,10 +5283,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122845245</v>
+        <v>122842434</v>
       </c>
       <c r="B46" t="n">
-        <v>8441</v>
+        <v>57494</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5300,43 +5295,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>677001</v>
+        <v>676739</v>
       </c>
       <c r="R46" t="n">
-        <v>6615675</v>
+        <v>6615944</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5395,10 +5390,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122842206</v>
+        <v>122845245</v>
       </c>
       <c r="B47" t="n">
-        <v>100631</v>
+        <v>8441</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5411,34 +5406,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>222498</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>676816</v>
+        <v>677001</v>
       </c>
       <c r="R47" t="n">
-        <v>6615981</v>
+        <v>6615675</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>

--- a/artfynd/A 9000-2025 artfynd.xlsx
+++ b/artfynd/A 9000-2025 artfynd.xlsx
@@ -3932,10 +3932,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122843888</v>
+        <v>122840972</v>
       </c>
       <c r="B33" t="n">
-        <v>8430</v>
+        <v>90952</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3944,47 +3944,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106554</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>676813</v>
+        <v>676898</v>
       </c>
       <c r="R33" t="n">
-        <v>6615903</v>
+        <v>6615759</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4025,7 +4016,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4044,10 +4034,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122842273</v>
+        <v>122842557</v>
       </c>
       <c r="B34" t="n">
-        <v>100631</v>
+        <v>90952</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4056,25 +4046,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4084,10 +4074,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>676787</v>
+        <v>676745</v>
       </c>
       <c r="R34" t="n">
-        <v>6615980</v>
+        <v>6615878</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4146,10 +4136,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122842144</v>
+        <v>122843888</v>
       </c>
       <c r="B35" t="n">
-        <v>100631</v>
+        <v>8430</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4162,34 +4152,43 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>676841</v>
+        <v>676813</v>
       </c>
       <c r="R35" t="n">
-        <v>6615983</v>
+        <v>6615903</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4230,6 +4229,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4248,10 +4248,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122840972</v>
+        <v>122842273</v>
       </c>
       <c r="B36" t="n">
-        <v>90952</v>
+        <v>100631</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4260,38 +4260,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>676898</v>
+        <v>676787</v>
       </c>
       <c r="R36" t="n">
-        <v>6615759</v>
+        <v>6615980</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4350,10 +4350,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122842557</v>
+        <v>122842144</v>
       </c>
       <c r="B37" t="n">
-        <v>90952</v>
+        <v>100631</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4362,25 +4362,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4390,10 +4390,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>676745</v>
+        <v>676841</v>
       </c>
       <c r="R37" t="n">
-        <v>6615878</v>
+        <v>6615983</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>

--- a/artfynd/A 9000-2025 artfynd.xlsx
+++ b/artfynd/A 9000-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122840712</v>
+        <v>122840804</v>
       </c>
       <c r="B2" t="n">
-        <v>4867</v>
+        <v>5358</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101675</v>
+        <v>101728</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -726,7 +726,7 @@
         <v>6615744</v>
       </c>
       <c r="S2" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122840804</v>
+        <v>122841077</v>
       </c>
       <c r="B3" t="n">
-        <v>5358</v>
+        <v>5193</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,43 +794,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101728</v>
+        <v>105930</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>676921</v>
+        <v>676870</v>
       </c>
       <c r="R3" t="n">
-        <v>6615744</v>
+        <v>6615757</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,6 +875,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -889,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122840623</v>
+        <v>122842819</v>
       </c>
       <c r="B4" t="n">
-        <v>57494</v>
+        <v>105474</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,43 +906,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>676932</v>
+        <v>676682</v>
       </c>
       <c r="R4" t="n">
-        <v>6615725</v>
+        <v>6615846</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122845448</v>
+        <v>122840495</v>
       </c>
       <c r="B5" t="n">
-        <v>105471</v>
+        <v>5193</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,34 +1012,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>105930</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>676972</v>
+        <v>676936</v>
       </c>
       <c r="R5" t="n">
-        <v>6615705</v>
+        <v>6615736</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122841097</v>
+        <v>122842748</v>
       </c>
       <c r="B6" t="n">
-        <v>5173</v>
+        <v>5193</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,14 +1144,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>676861</v>
+        <v>676684</v>
       </c>
       <c r="R6" t="n">
-        <v>6615758</v>
+        <v>6615835</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122840989</v>
+        <v>122843696</v>
       </c>
       <c r="B7" t="n">
-        <v>5173</v>
+        <v>90973</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,43 +1222,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>676899</v>
+        <v>676651</v>
       </c>
       <c r="R7" t="n">
-        <v>6615760</v>
+        <v>6615875</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122842133</v>
+        <v>122845880</v>
       </c>
       <c r="B8" t="n">
-        <v>100631</v>
+        <v>90973</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1324,38 +1324,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>676838</v>
+        <v>677085</v>
       </c>
       <c r="R8" t="n">
-        <v>6615977</v>
+        <v>6615732</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122840922</v>
+        <v>122840623</v>
       </c>
       <c r="B9" t="n">
-        <v>105471</v>
+        <v>57497</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1426,38 +1426,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>676912</v>
+        <v>676932</v>
       </c>
       <c r="R9" t="n">
-        <v>6615761</v>
+        <v>6615725</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122842950</v>
+        <v>122842642</v>
       </c>
       <c r="B10" t="n">
-        <v>105471</v>
+        <v>100634</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1532,34 +1537,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>676690</v>
+        <v>676714</v>
       </c>
       <c r="R10" t="n">
-        <v>6615799</v>
+        <v>6615824</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1618,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122843664</v>
+        <v>122842950</v>
       </c>
       <c r="B11" t="n">
-        <v>100631</v>
+        <v>105474</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1634,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1658,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>676656</v>
+        <v>676690</v>
       </c>
       <c r="R11" t="n">
-        <v>6615859</v>
+        <v>6615799</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1720,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122842680</v>
+        <v>122840930</v>
       </c>
       <c r="B12" t="n">
-        <v>57848</v>
+        <v>57497</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1732,20 +1737,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1756,19 +1761,19 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>676711</v>
+        <v>676913</v>
       </c>
       <c r="R12" t="n">
-        <v>6615822</v>
+        <v>6615763</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1827,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122841301</v>
+        <v>122845245</v>
       </c>
       <c r="B13" t="n">
-        <v>8430</v>
+        <v>8441</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1843,21 +1848,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1872,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>676893</v>
+        <v>677001</v>
       </c>
       <c r="R13" t="n">
-        <v>6615790</v>
+        <v>6615675</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1934,10 +1939,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122842185</v>
+        <v>122840712</v>
       </c>
       <c r="B14" t="n">
-        <v>100631</v>
+        <v>4867</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1950,37 +1955,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>101675</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>676831</v>
+        <v>676921</v>
       </c>
       <c r="R14" t="n">
-        <v>6615990</v>
+        <v>6615744</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2036,10 +2046,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122840392</v>
+        <v>122841301</v>
       </c>
       <c r="B15" t="n">
-        <v>57494</v>
+        <v>8430</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2048,31 +2058,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2081,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>676983</v>
+        <v>676893</v>
       </c>
       <c r="R15" t="n">
-        <v>6615701</v>
+        <v>6615790</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2143,10 +2153,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122840930</v>
+        <v>122842680</v>
       </c>
       <c r="B16" t="n">
-        <v>57494</v>
+        <v>57851</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2155,20 +2165,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2179,19 +2189,19 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>676913</v>
+        <v>676711</v>
       </c>
       <c r="R16" t="n">
-        <v>6615763</v>
+        <v>6615822</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2250,10 +2260,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122840896</v>
+        <v>122842479</v>
       </c>
       <c r="B17" t="n">
-        <v>5358</v>
+        <v>8430</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2262,25 +2272,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>101728</v>
+        <v>106554</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2291,14 +2301,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>676913</v>
+        <v>676756</v>
       </c>
       <c r="R17" t="n">
-        <v>6615766</v>
+        <v>6615927</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2357,10 +2367,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122840652</v>
+        <v>122843664</v>
       </c>
       <c r="B18" t="n">
-        <v>90917</v>
+        <v>100634</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2373,21 +2383,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2397,10 +2407,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>676670</v>
+        <v>676656</v>
       </c>
       <c r="R18" t="n">
-        <v>6615860</v>
+        <v>6615859</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2459,10 +2469,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122841332</v>
+        <v>122843607</v>
       </c>
       <c r="B19" t="n">
-        <v>57494</v>
+        <v>100634</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2471,43 +2481,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>676864</v>
+        <v>676666</v>
       </c>
       <c r="R19" t="n">
-        <v>6615776</v>
+        <v>6615819</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2566,10 +2571,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122843696</v>
+        <v>122842185</v>
       </c>
       <c r="B20" t="n">
-        <v>90970</v>
+        <v>100634</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2578,38 +2583,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>676651</v>
+        <v>676831</v>
       </c>
       <c r="R20" t="n">
-        <v>6615875</v>
+        <v>6615990</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2668,10 +2673,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122845736</v>
+        <v>122840989</v>
       </c>
       <c r="B21" t="n">
-        <v>8441</v>
+        <v>5173</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2684,21 +2689,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2713,10 +2718,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>677104</v>
+        <v>676899</v>
       </c>
       <c r="R21" t="n">
-        <v>6615675</v>
+        <v>6615760</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2775,10 +2780,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122842401</v>
+        <v>122840972</v>
       </c>
       <c r="B22" t="n">
-        <v>57494</v>
+        <v>90955</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2791,39 +2796,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>676742</v>
+        <v>676898</v>
       </c>
       <c r="R22" t="n">
-        <v>6615954</v>
+        <v>6615759</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2882,10 +2882,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122842642</v>
+        <v>122845448</v>
       </c>
       <c r="B23" t="n">
-        <v>100631</v>
+        <v>105474</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2898,34 +2898,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>676714</v>
+        <v>676972</v>
       </c>
       <c r="R23" t="n">
-        <v>6615824</v>
+        <v>6615705</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122842792</v>
+        <v>122842434</v>
       </c>
       <c r="B24" t="n">
-        <v>90917</v>
+        <v>57497</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2996,38 +2996,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>676683</v>
+        <v>676739</v>
       </c>
       <c r="R24" t="n">
-        <v>6615843</v>
+        <v>6615944</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3086,10 +3091,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122840378</v>
+        <v>122842133</v>
       </c>
       <c r="B25" t="n">
-        <v>57848</v>
+        <v>100634</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3102,39 +3107,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>676985</v>
+        <v>676838</v>
       </c>
       <c r="R25" t="n">
-        <v>6615696</v>
+        <v>6615977</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3193,10 +3193,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122842819</v>
+        <v>122842144</v>
       </c>
       <c r="B26" t="n">
-        <v>105471</v>
+        <v>100634</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3209,34 +3209,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>676682</v>
+        <v>676841</v>
       </c>
       <c r="R26" t="n">
-        <v>6615846</v>
+        <v>6615983</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3295,10 +3295,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122843861</v>
+        <v>122845926</v>
       </c>
       <c r="B27" t="n">
-        <v>57494</v>
+        <v>90920</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3307,43 +3307,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>676804</v>
+        <v>677084</v>
       </c>
       <c r="R27" t="n">
-        <v>6615893</v>
+        <v>6615718</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3402,10 +3397,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122841068</v>
+        <v>122843861</v>
       </c>
       <c r="B28" t="n">
-        <v>4867</v>
+        <v>57497</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3414,43 +3409,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>101675</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>676872</v>
+        <v>676804</v>
       </c>
       <c r="R28" t="n">
-        <v>6615746</v>
+        <v>6615893</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3509,10 +3504,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122840992</v>
+        <v>122840896</v>
       </c>
       <c r="B29" t="n">
-        <v>90952</v>
+        <v>5358</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3525,34 +3520,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>101728</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>676900</v>
+        <v>676913</v>
       </c>
       <c r="R29" t="n">
-        <v>6615757</v>
+        <v>6615766</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3611,10 +3611,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122841077</v>
+        <v>122840922</v>
       </c>
       <c r="B30" t="n">
-        <v>5193</v>
+        <v>105474</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3627,43 +3627,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>105930</v>
+        <v>221144</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>676870</v>
+        <v>676912</v>
       </c>
       <c r="R30" t="n">
-        <v>6615757</v>
+        <v>6615761</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3704,7 +3695,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3723,10 +3713,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122842748</v>
+        <v>122842792</v>
       </c>
       <c r="B31" t="n">
-        <v>5193</v>
+        <v>90920</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3739,39 +3729,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>105930</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>676684</v>
+        <v>676683</v>
       </c>
       <c r="R31" t="n">
-        <v>6615835</v>
+        <v>6615843</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3830,10 +3815,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122842088</v>
+        <v>122840378</v>
       </c>
       <c r="B32" t="n">
-        <v>100631</v>
+        <v>57851</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3846,34 +3831,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>676779</v>
+        <v>676985</v>
       </c>
       <c r="R32" t="n">
-        <v>6615963</v>
+        <v>6615696</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3932,10 +3922,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122840972</v>
+        <v>122840992</v>
       </c>
       <c r="B33" t="n">
-        <v>90952</v>
+        <v>90955</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3972,10 +3962,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>676898</v>
+        <v>676900</v>
       </c>
       <c r="R33" t="n">
-        <v>6615759</v>
+        <v>6615757</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4034,10 +4024,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122842557</v>
+        <v>122842832</v>
       </c>
       <c r="B34" t="n">
-        <v>90952</v>
+        <v>57634</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4050,37 +4040,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>676745</v>
+        <v>676682</v>
       </c>
       <c r="R34" t="n">
-        <v>6615878</v>
+        <v>6615846</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4136,7 +4131,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122843888</v>
+        <v>122845288</v>
       </c>
       <c r="B35" t="n">
         <v>8430</v>
@@ -4170,25 +4165,21 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>676813</v>
+        <v>677007</v>
       </c>
       <c r="R35" t="n">
-        <v>6615903</v>
+        <v>6615684</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4229,7 +4220,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4248,10 +4238,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122842273</v>
+        <v>122843888</v>
       </c>
       <c r="B36" t="n">
-        <v>100631</v>
+        <v>8430</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4264,34 +4254,43 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>676787</v>
+        <v>676813</v>
       </c>
       <c r="R36" t="n">
-        <v>6615980</v>
+        <v>6615903</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4332,6 +4331,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4350,10 +4350,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122842144</v>
+        <v>122841068</v>
       </c>
       <c r="B37" t="n">
-        <v>100631</v>
+        <v>4867</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4366,34 +4366,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
+        <v>101675</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>676841</v>
+        <v>676872</v>
       </c>
       <c r="R37" t="n">
-        <v>6615983</v>
+        <v>6615746</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4452,10 +4457,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122845926</v>
+        <v>122842206</v>
       </c>
       <c r="B38" t="n">
-        <v>90917</v>
+        <v>100634</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4468,34 +4473,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>677084</v>
+        <v>676816</v>
       </c>
       <c r="R38" t="n">
-        <v>6615718</v>
+        <v>6615981</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4554,10 +4559,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122840495</v>
+        <v>122842557</v>
       </c>
       <c r="B39" t="n">
-        <v>5193</v>
+        <v>90955</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4566,43 +4571,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>676936</v>
+        <v>676745</v>
       </c>
       <c r="R39" t="n">
-        <v>6615736</v>
+        <v>6615878</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4661,10 +4661,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122841986</v>
+        <v>122842401</v>
       </c>
       <c r="B40" t="n">
-        <v>105471</v>
+        <v>57497</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4673,38 +4673,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>676779</v>
+        <v>676742</v>
       </c>
       <c r="R40" t="n">
-        <v>6615963</v>
+        <v>6615954</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4763,10 +4768,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122843607</v>
+        <v>122842088</v>
       </c>
       <c r="B41" t="n">
-        <v>100631</v>
+        <v>100634</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4799,14 +4804,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>676666</v>
+        <v>676779</v>
       </c>
       <c r="R41" t="n">
-        <v>6615819</v>
+        <v>6615963</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4865,10 +4870,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122845288</v>
+        <v>122840652</v>
       </c>
       <c r="B42" t="n">
-        <v>8430</v>
+        <v>90920</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4881,39 +4886,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106554</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>677007</v>
+        <v>676670</v>
       </c>
       <c r="R42" t="n">
-        <v>6615684</v>
+        <v>6615860</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4972,10 +4972,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122842479</v>
+        <v>122840392</v>
       </c>
       <c r="B43" t="n">
-        <v>8430</v>
+        <v>57497</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4984,43 +4984,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>676756</v>
+        <v>676983</v>
       </c>
       <c r="R43" t="n">
-        <v>6615927</v>
+        <v>6615701</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5079,10 +5079,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122845880</v>
+        <v>122841097</v>
       </c>
       <c r="B44" t="n">
-        <v>90970</v>
+        <v>5173</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5091,38 +5091,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>100526</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>677085</v>
+        <v>676861</v>
       </c>
       <c r="R44" t="n">
-        <v>6615732</v>
+        <v>6615758</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5181,10 +5186,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122842206</v>
+        <v>122842273</v>
       </c>
       <c r="B45" t="n">
-        <v>100631</v>
+        <v>100634</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5221,10 +5226,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>676816</v>
+        <v>676787</v>
       </c>
       <c r="R45" t="n">
-        <v>6615981</v>
+        <v>6615980</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5283,10 +5288,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122842434</v>
+        <v>122845736</v>
       </c>
       <c r="B46" t="n">
-        <v>57494</v>
+        <v>8441</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5295,43 +5300,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>676739</v>
+        <v>677104</v>
       </c>
       <c r="R46" t="n">
-        <v>6615944</v>
+        <v>6615675</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5390,10 +5395,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122845245</v>
+        <v>122841986</v>
       </c>
       <c r="B47" t="n">
-        <v>8441</v>
+        <v>105474</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5406,39 +5411,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106545</v>
+        <v>221144</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>677001</v>
+        <v>676779</v>
       </c>
       <c r="R47" t="n">
-        <v>6615675</v>
+        <v>6615963</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5500,7 +5500,7 @@
         <v>122845093</v>
       </c>
       <c r="B48" t="n">
-        <v>90917</v>
+        <v>90920</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5599,10 +5599,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122842832</v>
+        <v>122841332</v>
       </c>
       <c r="B49" t="n">
-        <v>57631</v>
+        <v>57497</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5615,42 +5615,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>676682</v>
+        <v>676864</v>
       </c>
       <c r="R49" t="n">
-        <v>6615846</v>
+        <v>6615776</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>

--- a/artfynd/A 9000-2025 artfynd.xlsx
+++ b/artfynd/A 9000-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122840804</v>
+        <v>122842832</v>
       </c>
       <c r="B2" t="n">
-        <v>5358</v>
+        <v>57634</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101728</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>676921</v>
+        <v>676682</v>
       </c>
       <c r="R2" t="n">
-        <v>6615744</v>
+        <v>6615846</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122841077</v>
+        <v>122840930</v>
       </c>
       <c r="B3" t="n">
-        <v>5193</v>
+        <v>57497</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,20 +794,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -816,25 +816,21 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>676870</v>
+        <v>676913</v>
       </c>
       <c r="R3" t="n">
-        <v>6615757</v>
+        <v>6615763</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,7 +871,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -894,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122842819</v>
+        <v>122842401</v>
       </c>
       <c r="B4" t="n">
-        <v>105474</v>
+        <v>57497</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -906,38 +901,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>676682</v>
+        <v>676742</v>
       </c>
       <c r="R4" t="n">
-        <v>6615846</v>
+        <v>6615954</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122840495</v>
+        <v>122845245</v>
       </c>
       <c r="B5" t="n">
-        <v>5193</v>
+        <v>8441</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105930</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>676936</v>
+        <v>677001</v>
       </c>
       <c r="R5" t="n">
-        <v>6615736</v>
+        <v>6615675</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122842748</v>
+        <v>122842479</v>
       </c>
       <c r="B6" t="n">
-        <v>5193</v>
+        <v>8430</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105930</v>
+        <v>106554</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1144,14 +1144,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>676684</v>
+        <v>676756</v>
       </c>
       <c r="R6" t="n">
-        <v>6615835</v>
+        <v>6615927</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122843696</v>
+        <v>122845288</v>
       </c>
       <c r="B7" t="n">
-        <v>90973</v>
+        <v>8430</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,38 +1222,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>106554</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>676651</v>
+        <v>677007</v>
       </c>
       <c r="R7" t="n">
-        <v>6615875</v>
+        <v>6615684</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122845880</v>
+        <v>122840495</v>
       </c>
       <c r="B8" t="n">
-        <v>90973</v>
+        <v>5193</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1324,38 +1329,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>105930</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>677085</v>
+        <v>676936</v>
       </c>
       <c r="R8" t="n">
-        <v>6615732</v>
+        <v>6615736</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122840623</v>
+        <v>122843664</v>
       </c>
       <c r="B9" t="n">
-        <v>57497</v>
+        <v>100636</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1426,43 +1436,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>676932</v>
+        <v>676656</v>
       </c>
       <c r="R9" t="n">
-        <v>6615725</v>
+        <v>6615859</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122842642</v>
+        <v>122841986</v>
       </c>
       <c r="B10" t="n">
-        <v>100634</v>
+        <v>105476</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>676714</v>
+        <v>676779</v>
       </c>
       <c r="R10" t="n">
-        <v>6615824</v>
+        <v>6615963</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1623,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122842950</v>
+        <v>122845880</v>
       </c>
       <c r="B11" t="n">
-        <v>105474</v>
+        <v>90975</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1635,38 +1640,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>676690</v>
+        <v>677085</v>
       </c>
       <c r="R11" t="n">
-        <v>6615799</v>
+        <v>6615732</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1725,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122840930</v>
+        <v>122842133</v>
       </c>
       <c r="B12" t="n">
-        <v>57497</v>
+        <v>100636</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1737,43 +1742,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>676913</v>
+        <v>676838</v>
       </c>
       <c r="R12" t="n">
-        <v>6615763</v>
+        <v>6615977</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1832,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122845245</v>
+        <v>122843861</v>
       </c>
       <c r="B13" t="n">
-        <v>8441</v>
+        <v>57497</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1844,43 +1844,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>677001</v>
+        <v>676804</v>
       </c>
       <c r="R13" t="n">
-        <v>6615675</v>
+        <v>6615893</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1939,10 +1939,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122840712</v>
+        <v>122842434</v>
       </c>
       <c r="B14" t="n">
-        <v>4867</v>
+        <v>57497</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1951,46 +1951,46 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>101675</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>676921</v>
+        <v>676739</v>
       </c>
       <c r="R14" t="n">
-        <v>6615744</v>
+        <v>6615944</v>
       </c>
       <c r="S14" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2153,10 +2153,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122842680</v>
+        <v>122840712</v>
       </c>
       <c r="B16" t="n">
-        <v>57851</v>
+        <v>4867</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2169,42 +2169,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103015</v>
+        <v>101675</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>676711</v>
+        <v>676921</v>
       </c>
       <c r="R16" t="n">
-        <v>6615822</v>
+        <v>6615744</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2260,10 +2260,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122842479</v>
+        <v>122841068</v>
       </c>
       <c r="B17" t="n">
-        <v>8430</v>
+        <v>4867</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2276,21 +2276,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106554</v>
+        <v>101675</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2301,14 +2301,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>676756</v>
+        <v>676872</v>
       </c>
       <c r="R17" t="n">
-        <v>6615927</v>
+        <v>6615746</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2367,10 +2367,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122843664</v>
+        <v>122842557</v>
       </c>
       <c r="B18" t="n">
-        <v>100634</v>
+        <v>90957</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2379,38 +2379,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>676656</v>
+        <v>676745</v>
       </c>
       <c r="R18" t="n">
-        <v>6615859</v>
+        <v>6615878</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2469,10 +2469,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122843607</v>
+        <v>122842748</v>
       </c>
       <c r="B19" t="n">
-        <v>100634</v>
+        <v>5193</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2485,34 +2485,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>676666</v>
+        <v>676684</v>
       </c>
       <c r="R19" t="n">
-        <v>6615819</v>
+        <v>6615835</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2571,10 +2576,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122842185</v>
+        <v>122842206</v>
       </c>
       <c r="B20" t="n">
-        <v>100634</v>
+        <v>100636</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2611,10 +2616,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>676831</v>
+        <v>676816</v>
       </c>
       <c r="R20" t="n">
-        <v>6615990</v>
+        <v>6615981</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2673,10 +2678,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122840989</v>
+        <v>122841077</v>
       </c>
       <c r="B21" t="n">
-        <v>5173</v>
+        <v>5193</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2689,39 +2694,43 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>676899</v>
+        <v>676870</v>
       </c>
       <c r="R21" t="n">
-        <v>6615760</v>
+        <v>6615757</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2762,6 +2771,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2780,10 +2790,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122840972</v>
+        <v>122842792</v>
       </c>
       <c r="B22" t="n">
-        <v>90955</v>
+        <v>90922</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2792,38 +2802,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>676898</v>
+        <v>676683</v>
       </c>
       <c r="R22" t="n">
-        <v>6615759</v>
+        <v>6615843</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2882,10 +2892,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122845448</v>
+        <v>122840922</v>
       </c>
       <c r="B23" t="n">
-        <v>105474</v>
+        <v>105476</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2922,10 +2932,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>676972</v>
+        <v>676912</v>
       </c>
       <c r="R23" t="n">
-        <v>6615705</v>
+        <v>6615761</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2984,10 +2994,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122842434</v>
+        <v>122842950</v>
       </c>
       <c r="B24" t="n">
-        <v>57497</v>
+        <v>105476</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2996,43 +3006,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>676739</v>
+        <v>676690</v>
       </c>
       <c r="R24" t="n">
-        <v>6615944</v>
+        <v>6615799</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3091,10 +3096,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122842133</v>
+        <v>122840804</v>
       </c>
       <c r="B25" t="n">
-        <v>100634</v>
+        <v>5358</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3103,38 +3108,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>101728</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>676838</v>
+        <v>676921</v>
       </c>
       <c r="R25" t="n">
-        <v>6615977</v>
+        <v>6615744</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3193,10 +3203,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122842144</v>
+        <v>122841097</v>
       </c>
       <c r="B26" t="n">
-        <v>100634</v>
+        <v>5173</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3209,34 +3219,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>676841</v>
+        <v>676861</v>
       </c>
       <c r="R26" t="n">
-        <v>6615983</v>
+        <v>6615758</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3295,10 +3310,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122845926</v>
+        <v>122840378</v>
       </c>
       <c r="B27" t="n">
-        <v>90920</v>
+        <v>57851</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3311,34 +3326,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>103015</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>677084</v>
+        <v>676985</v>
       </c>
       <c r="R27" t="n">
-        <v>6615718</v>
+        <v>6615696</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3397,10 +3417,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122843861</v>
+        <v>122840992</v>
       </c>
       <c r="B28" t="n">
-        <v>57497</v>
+        <v>90957</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3413,39 +3433,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>676804</v>
+        <v>676900</v>
       </c>
       <c r="R28" t="n">
-        <v>6615893</v>
+        <v>6615757</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3504,10 +3519,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122840896</v>
+        <v>122845926</v>
       </c>
       <c r="B29" t="n">
-        <v>5358</v>
+        <v>90922</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3516,43 +3531,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>101728</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>676913</v>
+        <v>677084</v>
       </c>
       <c r="R29" t="n">
-        <v>6615766</v>
+        <v>6615718</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3611,10 +3621,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122840922</v>
+        <v>122843607</v>
       </c>
       <c r="B30" t="n">
-        <v>105474</v>
+        <v>100636</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3627,34 +3637,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>676912</v>
+        <v>676666</v>
       </c>
       <c r="R30" t="n">
-        <v>6615761</v>
+        <v>6615819</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3713,10 +3723,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122842792</v>
+        <v>122842273</v>
       </c>
       <c r="B31" t="n">
-        <v>90920</v>
+        <v>100636</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3729,34 +3739,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>676683</v>
+        <v>676787</v>
       </c>
       <c r="R31" t="n">
-        <v>6615843</v>
+        <v>6615980</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3815,10 +3825,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122840378</v>
+        <v>122842819</v>
       </c>
       <c r="B32" t="n">
-        <v>57851</v>
+        <v>105476</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3831,39 +3841,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103015</v>
+        <v>221144</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>676985</v>
+        <v>676682</v>
       </c>
       <c r="R32" t="n">
-        <v>6615696</v>
+        <v>6615846</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3922,10 +3927,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122840992</v>
+        <v>122845736</v>
       </c>
       <c r="B33" t="n">
-        <v>90955</v>
+        <v>8441</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3934,38 +3939,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>676900</v>
+        <v>677104</v>
       </c>
       <c r="R33" t="n">
-        <v>6615757</v>
+        <v>6615675</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4024,10 +4034,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122842832</v>
+        <v>122840392</v>
       </c>
       <c r="B34" t="n">
-        <v>57634</v>
+        <v>57497</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4040,42 +4050,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>676682</v>
+        <v>676983</v>
       </c>
       <c r="R34" t="n">
-        <v>6615846</v>
+        <v>6615701</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4131,10 +4141,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122845288</v>
+        <v>122840623</v>
       </c>
       <c r="B35" t="n">
-        <v>8430</v>
+        <v>57497</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4143,31 +4153,31 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4176,10 +4186,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>677007</v>
+        <v>676932</v>
       </c>
       <c r="R35" t="n">
-        <v>6615684</v>
+        <v>6615725</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4238,10 +4248,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122843888</v>
+        <v>122840972</v>
       </c>
       <c r="B36" t="n">
-        <v>8430</v>
+        <v>90957</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4250,47 +4260,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106554</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>676813</v>
+        <v>676898</v>
       </c>
       <c r="R36" t="n">
-        <v>6615903</v>
+        <v>6615759</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4331,7 +4332,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4350,10 +4350,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122841068</v>
+        <v>122842088</v>
       </c>
       <c r="B37" t="n">
-        <v>4867</v>
+        <v>100636</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4366,39 +4366,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>101675</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>676872</v>
+        <v>676779</v>
       </c>
       <c r="R37" t="n">
-        <v>6615746</v>
+        <v>6615963</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4457,10 +4452,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122842206</v>
+        <v>122843888</v>
       </c>
       <c r="B38" t="n">
-        <v>100634</v>
+        <v>8430</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4473,34 +4468,43 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>676816</v>
+        <v>676813</v>
       </c>
       <c r="R38" t="n">
-        <v>6615981</v>
+        <v>6615903</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4541,6 +4545,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4559,10 +4564,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122842557</v>
+        <v>122842642</v>
       </c>
       <c r="B39" t="n">
-        <v>90955</v>
+        <v>100636</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4571,25 +4576,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4599,10 +4604,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>676745</v>
+        <v>676714</v>
       </c>
       <c r="R39" t="n">
-        <v>6615878</v>
+        <v>6615824</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4661,10 +4666,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122842401</v>
+        <v>122845448</v>
       </c>
       <c r="B40" t="n">
-        <v>57497</v>
+        <v>105476</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4673,43 +4678,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>676742</v>
+        <v>676972</v>
       </c>
       <c r="R40" t="n">
-        <v>6615954</v>
+        <v>6615705</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4768,10 +4768,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122842088</v>
+        <v>122840896</v>
       </c>
       <c r="B41" t="n">
-        <v>100634</v>
+        <v>5358</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4780,38 +4780,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222498</v>
+        <v>101728</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>676779</v>
+        <v>676913</v>
       </c>
       <c r="R41" t="n">
-        <v>6615963</v>
+        <v>6615766</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4870,10 +4875,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122840652</v>
+        <v>122841332</v>
       </c>
       <c r="B42" t="n">
-        <v>90920</v>
+        <v>57497</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4882,38 +4887,43 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>676670</v>
+        <v>676864</v>
       </c>
       <c r="R42" t="n">
-        <v>6615860</v>
+        <v>6615776</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4972,10 +4982,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122840392</v>
+        <v>122845093</v>
       </c>
       <c r="B43" t="n">
-        <v>57497</v>
+        <v>90922</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4984,43 +4994,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>676983</v>
+        <v>676956</v>
       </c>
       <c r="R43" t="n">
-        <v>6615701</v>
+        <v>6615718</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5079,10 +5084,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122841097</v>
+        <v>122842144</v>
       </c>
       <c r="B44" t="n">
-        <v>5173</v>
+        <v>100636</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5095,39 +5100,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>676861</v>
+        <v>676841</v>
       </c>
       <c r="R44" t="n">
-        <v>6615758</v>
+        <v>6615983</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5186,10 +5186,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122842273</v>
+        <v>122843696</v>
       </c>
       <c r="B45" t="n">
-        <v>100634</v>
+        <v>90975</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5198,38 +5198,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>676787</v>
+        <v>676651</v>
       </c>
       <c r="R45" t="n">
-        <v>6615980</v>
+        <v>6615875</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5288,10 +5288,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122845736</v>
+        <v>122842680</v>
       </c>
       <c r="B46" t="n">
-        <v>8441</v>
+        <v>57851</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5304,39 +5304,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>103015</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>677104</v>
+        <v>676711</v>
       </c>
       <c r="R46" t="n">
-        <v>6615675</v>
+        <v>6615822</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5395,10 +5395,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122841986</v>
+        <v>122840652</v>
       </c>
       <c r="B47" t="n">
-        <v>105474</v>
+        <v>90922</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5411,34 +5411,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221144</v>
+        <v>5447</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>676779</v>
+        <v>676670</v>
       </c>
       <c r="R47" t="n">
-        <v>6615963</v>
+        <v>6615860</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5497,10 +5497,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122845093</v>
+        <v>122840989</v>
       </c>
       <c r="B48" t="n">
-        <v>90920</v>
+        <v>5173</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5513,34 +5513,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>676956</v>
+        <v>676899</v>
       </c>
       <c r="R48" t="n">
-        <v>6615718</v>
+        <v>6615760</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5599,10 +5604,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122841332</v>
+        <v>122842185</v>
       </c>
       <c r="B49" t="n">
-        <v>57497</v>
+        <v>100636</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5611,43 +5616,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>676864</v>
+        <v>676831</v>
       </c>
       <c r="R49" t="n">
-        <v>6615776</v>
+        <v>6615990</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>

--- a/artfynd/A 9000-2025 artfynd.xlsx
+++ b/artfynd/A 9000-2025 artfynd.xlsx
@@ -3203,10 +3203,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122841097</v>
+        <v>122843607</v>
       </c>
       <c r="B26" t="n">
-        <v>5173</v>
+        <v>100636</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3219,39 +3219,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>676861</v>
+        <v>676666</v>
       </c>
       <c r="R26" t="n">
-        <v>6615758</v>
+        <v>6615819</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3310,10 +3305,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122840378</v>
+        <v>122842819</v>
       </c>
       <c r="B27" t="n">
-        <v>57851</v>
+        <v>105476</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3326,39 +3321,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103015</v>
+        <v>221144</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>676985</v>
+        <v>676682</v>
       </c>
       <c r="R27" t="n">
-        <v>6615696</v>
+        <v>6615846</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3417,10 +3407,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122840992</v>
+        <v>122840378</v>
       </c>
       <c r="B28" t="n">
-        <v>90957</v>
+        <v>57851</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3429,38 +3419,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>103015</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>676900</v>
+        <v>676985</v>
       </c>
       <c r="R28" t="n">
-        <v>6615757</v>
+        <v>6615696</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3519,10 +3514,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122845926</v>
+        <v>122842273</v>
       </c>
       <c r="B29" t="n">
-        <v>90922</v>
+        <v>100636</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3535,34 +3530,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>677084</v>
+        <v>676787</v>
       </c>
       <c r="R29" t="n">
-        <v>6615718</v>
+        <v>6615980</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3621,10 +3616,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122843607</v>
+        <v>122841097</v>
       </c>
       <c r="B30" t="n">
-        <v>100636</v>
+        <v>5173</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3637,34 +3632,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>676666</v>
+        <v>676861</v>
       </c>
       <c r="R30" t="n">
-        <v>6615819</v>
+        <v>6615758</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3723,10 +3723,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122842273</v>
+        <v>122840992</v>
       </c>
       <c r="B31" t="n">
-        <v>100636</v>
+        <v>90957</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3735,38 +3735,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>676787</v>
+        <v>676900</v>
       </c>
       <c r="R31" t="n">
-        <v>6615980</v>
+        <v>6615757</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3825,10 +3825,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122842819</v>
+        <v>122845926</v>
       </c>
       <c r="B32" t="n">
-        <v>105476</v>
+        <v>90922</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3841,34 +3841,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221144</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>676682</v>
+        <v>677084</v>
       </c>
       <c r="R32" t="n">
-        <v>6615846</v>
+        <v>6615718</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4350,10 +4350,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122842088</v>
+        <v>122843888</v>
       </c>
       <c r="B37" t="n">
-        <v>100636</v>
+        <v>8430</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4366,34 +4366,43 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>676779</v>
+        <v>676813</v>
       </c>
       <c r="R37" t="n">
-        <v>6615963</v>
+        <v>6615903</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4434,6 +4443,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4452,10 +4462,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122843888</v>
+        <v>122842088</v>
       </c>
       <c r="B38" t="n">
-        <v>8430</v>
+        <v>100636</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4468,43 +4478,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>676813</v>
+        <v>676779</v>
       </c>
       <c r="R38" t="n">
-        <v>6615903</v>
+        <v>6615963</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4545,7 +4546,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 9000-2025 artfynd.xlsx
+++ b/artfynd/A 9000-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122842832</v>
+        <v>122840392</v>
       </c>
       <c r="B2" t="n">
-        <v>57634</v>
+        <v>57497</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>676682</v>
+        <v>676983</v>
       </c>
       <c r="R2" t="n">
-        <v>6615846</v>
+        <v>6615701</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122840930</v>
+        <v>122842792</v>
       </c>
       <c r="B3" t="n">
-        <v>57497</v>
+        <v>90928</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,43 +794,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>676913</v>
+        <v>676683</v>
       </c>
       <c r="R3" t="n">
-        <v>6615763</v>
+        <v>6615843</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122842401</v>
+        <v>122842088</v>
       </c>
       <c r="B4" t="n">
-        <v>57497</v>
+        <v>100642</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,43 +896,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>676742</v>
+        <v>676779</v>
       </c>
       <c r="R4" t="n">
-        <v>6615954</v>
+        <v>6615963</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122845245</v>
+        <v>122843888</v>
       </c>
       <c r="B5" t="n">
-        <v>8441</v>
+        <v>8430</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,39 +1002,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>677001</v>
+        <v>676813</v>
       </c>
       <c r="R5" t="n">
-        <v>6615675</v>
+        <v>6615903</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,6 +1079,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1103,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122842479</v>
+        <v>122842401</v>
       </c>
       <c r="B6" t="n">
-        <v>8430</v>
+        <v>57497</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,31 +1110,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1148,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>676756</v>
+        <v>676742</v>
       </c>
       <c r="R6" t="n">
-        <v>6615927</v>
+        <v>6615954</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122845288</v>
+        <v>122842557</v>
       </c>
       <c r="B7" t="n">
-        <v>8430</v>
+        <v>90963</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,43 +1217,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106554</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>677007</v>
+        <v>676745</v>
       </c>
       <c r="R7" t="n">
-        <v>6615684</v>
+        <v>6615878</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122840495</v>
+        <v>122843607</v>
       </c>
       <c r="B8" t="n">
-        <v>5193</v>
+        <v>100642</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,39 +1323,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>676936</v>
+        <v>676666</v>
       </c>
       <c r="R8" t="n">
-        <v>6615736</v>
+        <v>6615819</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122843664</v>
+        <v>122841077</v>
       </c>
       <c r="B9" t="n">
-        <v>100636</v>
+        <v>5193</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1440,34 +1425,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>676656</v>
+        <v>676870</v>
       </c>
       <c r="R9" t="n">
-        <v>6615859</v>
+        <v>6615757</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1508,6 +1502,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1529,7 +1524,7 @@
         <v>122841986</v>
       </c>
       <c r="B10" t="n">
-        <v>105476</v>
+        <v>105482</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1628,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122845880</v>
+        <v>122840804</v>
       </c>
       <c r="B11" t="n">
-        <v>90975</v>
+        <v>5358</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1644,34 +1639,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>101728</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>677085</v>
+        <v>676921</v>
       </c>
       <c r="R11" t="n">
-        <v>6615732</v>
+        <v>6615744</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1730,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122842133</v>
+        <v>122843696</v>
       </c>
       <c r="B12" t="n">
-        <v>100636</v>
+        <v>90981</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1742,38 +1742,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>676838</v>
+        <v>676651</v>
       </c>
       <c r="R12" t="n">
-        <v>6615977</v>
+        <v>6615875</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1832,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122843861</v>
+        <v>122842144</v>
       </c>
       <c r="B13" t="n">
-        <v>57497</v>
+        <v>100642</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1844,43 +1844,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>676804</v>
+        <v>676841</v>
       </c>
       <c r="R13" t="n">
-        <v>6615893</v>
+        <v>6615983</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1939,10 +1934,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122842434</v>
+        <v>122845448</v>
       </c>
       <c r="B14" t="n">
-        <v>57497</v>
+        <v>105482</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1951,43 +1946,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>676739</v>
+        <v>676972</v>
       </c>
       <c r="R14" t="n">
-        <v>6615944</v>
+        <v>6615705</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2046,10 +2036,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122841301</v>
+        <v>122842680</v>
       </c>
       <c r="B15" t="n">
-        <v>8430</v>
+        <v>57851</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2062,39 +2052,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106554</v>
+        <v>103015</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>676893</v>
+        <v>676711</v>
       </c>
       <c r="R15" t="n">
-        <v>6615790</v>
+        <v>6615822</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2153,10 +2143,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122840712</v>
+        <v>122841301</v>
       </c>
       <c r="B16" t="n">
-        <v>4867</v>
+        <v>8430</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2169,21 +2159,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>101675</v>
+        <v>106554</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2198,13 +2188,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>676921</v>
+        <v>676893</v>
       </c>
       <c r="R16" t="n">
-        <v>6615744</v>
+        <v>6615790</v>
       </c>
       <c r="S16" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2260,10 +2250,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122841068</v>
+        <v>122845926</v>
       </c>
       <c r="B17" t="n">
-        <v>4867</v>
+        <v>90928</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2276,39 +2266,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>101675</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>676872</v>
+        <v>677084</v>
       </c>
       <c r="R17" t="n">
-        <v>6615746</v>
+        <v>6615718</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2367,10 +2352,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122842557</v>
+        <v>122843861</v>
       </c>
       <c r="B18" t="n">
-        <v>90957</v>
+        <v>57497</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2383,34 +2368,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>676745</v>
+        <v>676804</v>
       </c>
       <c r="R18" t="n">
-        <v>6615878</v>
+        <v>6615893</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2469,10 +2459,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122842748</v>
+        <v>122840989</v>
       </c>
       <c r="B19" t="n">
-        <v>5193</v>
+        <v>5173</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2485,21 +2475,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2510,14 +2500,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>676684</v>
+        <v>676899</v>
       </c>
       <c r="R19" t="n">
-        <v>6615835</v>
+        <v>6615760</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2576,10 +2566,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122842206</v>
+        <v>122842273</v>
       </c>
       <c r="B20" t="n">
-        <v>100636</v>
+        <v>100642</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2616,10 +2606,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>676816</v>
+        <v>676787</v>
       </c>
       <c r="R20" t="n">
-        <v>6615981</v>
+        <v>6615980</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2678,10 +2668,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122841077</v>
+        <v>122842479</v>
       </c>
       <c r="B21" t="n">
-        <v>5193</v>
+        <v>8430</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2694,43 +2684,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>105930</v>
+        <v>106554</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>676870</v>
+        <v>676756</v>
       </c>
       <c r="R21" t="n">
-        <v>6615757</v>
+        <v>6615927</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2771,7 +2757,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2790,10 +2775,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122842792</v>
+        <v>122840623</v>
       </c>
       <c r="B22" t="n">
-        <v>90922</v>
+        <v>57497</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2802,38 +2787,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>676683</v>
+        <v>676932</v>
       </c>
       <c r="R22" t="n">
-        <v>6615843</v>
+        <v>6615725</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2892,10 +2882,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122840922</v>
+        <v>122845288</v>
       </c>
       <c r="B23" t="n">
-        <v>105476</v>
+        <v>8430</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2908,34 +2898,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221144</v>
+        <v>106554</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>676912</v>
+        <v>677007</v>
       </c>
       <c r="R23" t="n">
-        <v>6615761</v>
+        <v>6615684</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2994,10 +2989,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122842950</v>
+        <v>122840972</v>
       </c>
       <c r="B24" t="n">
-        <v>105476</v>
+        <v>90963</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3006,38 +3001,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>676690</v>
+        <v>676898</v>
       </c>
       <c r="R24" t="n">
-        <v>6615799</v>
+        <v>6615759</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3096,10 +3091,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122840804</v>
+        <v>122840712</v>
       </c>
       <c r="B25" t="n">
-        <v>5358</v>
+        <v>4867</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3108,25 +3103,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>101728</v>
+        <v>101675</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3147,7 +3142,7 @@
         <v>6615744</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3203,10 +3198,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122843607</v>
+        <v>122842819</v>
       </c>
       <c r="B26" t="n">
-        <v>100636</v>
+        <v>105482</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3219,21 +3214,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3243,10 +3238,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>676666</v>
+        <v>676682</v>
       </c>
       <c r="R26" t="n">
-        <v>6615819</v>
+        <v>6615846</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3305,10 +3300,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122842819</v>
+        <v>122840378</v>
       </c>
       <c r="B27" t="n">
-        <v>105476</v>
+        <v>57851</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3321,34 +3316,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221144</v>
+        <v>103015</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>676682</v>
+        <v>676985</v>
       </c>
       <c r="R27" t="n">
-        <v>6615846</v>
+        <v>6615696</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3407,10 +3407,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122840378</v>
+        <v>122842748</v>
       </c>
       <c r="B28" t="n">
-        <v>57851</v>
+        <v>5193</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3423,16 +3423,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103015</v>
+        <v>105930</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3443,19 +3443,19 @@
       <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>676985</v>
+        <v>676684</v>
       </c>
       <c r="R28" t="n">
-        <v>6615696</v>
+        <v>6615835</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3514,10 +3514,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122842273</v>
+        <v>122845093</v>
       </c>
       <c r="B29" t="n">
-        <v>100636</v>
+        <v>90928</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3530,34 +3530,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>676787</v>
+        <v>676956</v>
       </c>
       <c r="R29" t="n">
-        <v>6615980</v>
+        <v>6615718</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3616,10 +3616,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122841097</v>
+        <v>122845736</v>
       </c>
       <c r="B30" t="n">
-        <v>5173</v>
+        <v>8441</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3632,21 +3632,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3661,10 +3661,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>676861</v>
+        <v>677104</v>
       </c>
       <c r="R30" t="n">
-        <v>6615758</v>
+        <v>6615675</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3723,10 +3723,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122840992</v>
+        <v>122842133</v>
       </c>
       <c r="B31" t="n">
-        <v>90957</v>
+        <v>100642</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3735,38 +3735,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>676900</v>
+        <v>676838</v>
       </c>
       <c r="R31" t="n">
-        <v>6615757</v>
+        <v>6615977</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3825,10 +3825,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122845926</v>
+        <v>122840930</v>
       </c>
       <c r="B32" t="n">
-        <v>90922</v>
+        <v>57497</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3837,38 +3837,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>677084</v>
+        <v>676913</v>
       </c>
       <c r="R32" t="n">
-        <v>6615718</v>
+        <v>6615763</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3927,10 +3932,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122845736</v>
+        <v>122841068</v>
       </c>
       <c r="B33" t="n">
-        <v>8441</v>
+        <v>4867</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3943,21 +3948,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>101675</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3972,10 +3977,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>677104</v>
+        <v>676872</v>
       </c>
       <c r="R33" t="n">
-        <v>6615675</v>
+        <v>6615746</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4034,10 +4039,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122840392</v>
+        <v>122840922</v>
       </c>
       <c r="B34" t="n">
-        <v>57497</v>
+        <v>105482</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4046,43 +4051,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>676983</v>
+        <v>676912</v>
       </c>
       <c r="R34" t="n">
-        <v>6615701</v>
+        <v>6615761</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4141,10 +4141,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122840623</v>
+        <v>122842642</v>
       </c>
       <c r="B35" t="n">
-        <v>57497</v>
+        <v>100642</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4153,43 +4153,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>676932</v>
+        <v>676714</v>
       </c>
       <c r="R35" t="n">
-        <v>6615725</v>
+        <v>6615824</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4248,10 +4243,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122840972</v>
+        <v>122845880</v>
       </c>
       <c r="B36" t="n">
-        <v>90957</v>
+        <v>90981</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4264,21 +4259,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4288,10 +4283,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>676898</v>
+        <v>677085</v>
       </c>
       <c r="R36" t="n">
-        <v>6615759</v>
+        <v>6615732</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4350,10 +4345,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122843888</v>
+        <v>122840495</v>
       </c>
       <c r="B37" t="n">
-        <v>8430</v>
+        <v>5193</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4366,43 +4361,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>676813</v>
+        <v>676936</v>
       </c>
       <c r="R37" t="n">
-        <v>6615903</v>
+        <v>6615736</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4443,7 +4434,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4462,10 +4452,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122842088</v>
+        <v>122840896</v>
       </c>
       <c r="B38" t="n">
-        <v>100636</v>
+        <v>5358</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4474,38 +4464,43 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>101728</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>676779</v>
+        <v>676913</v>
       </c>
       <c r="R38" t="n">
-        <v>6615963</v>
+        <v>6615766</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4564,10 +4559,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122842642</v>
+        <v>122841332</v>
       </c>
       <c r="B39" t="n">
-        <v>100636</v>
+        <v>57497</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4576,38 +4571,43 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>676714</v>
+        <v>676864</v>
       </c>
       <c r="R39" t="n">
-        <v>6615824</v>
+        <v>6615776</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4666,10 +4666,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122845448</v>
+        <v>122840652</v>
       </c>
       <c r="B40" t="n">
-        <v>105476</v>
+        <v>90928</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4682,34 +4682,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221144</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>676972</v>
+        <v>676670</v>
       </c>
       <c r="R40" t="n">
-        <v>6615705</v>
+        <v>6615860</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4768,10 +4768,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122840896</v>
+        <v>122841097</v>
       </c>
       <c r="B41" t="n">
-        <v>5358</v>
+        <v>5173</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4780,25 +4780,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>101728</v>
+        <v>100526</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4813,10 +4813,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>676913</v>
+        <v>676861</v>
       </c>
       <c r="R41" t="n">
-        <v>6615766</v>
+        <v>6615758</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4875,10 +4875,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122841332</v>
+        <v>122842206</v>
       </c>
       <c r="B42" t="n">
-        <v>57497</v>
+        <v>100642</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4887,43 +4887,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>676864</v>
+        <v>676816</v>
       </c>
       <c r="R42" t="n">
-        <v>6615776</v>
+        <v>6615981</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4982,10 +4977,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122845093</v>
+        <v>122842185</v>
       </c>
       <c r="B43" t="n">
-        <v>90922</v>
+        <v>100642</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4998,34 +4993,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>676956</v>
+        <v>676831</v>
       </c>
       <c r="R43" t="n">
-        <v>6615718</v>
+        <v>6615990</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5084,10 +5079,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122842144</v>
+        <v>122842832</v>
       </c>
       <c r="B44" t="n">
-        <v>100636</v>
+        <v>57634</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5096,41 +5091,46 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>676841</v>
+        <v>676682</v>
       </c>
       <c r="R44" t="n">
-        <v>6615983</v>
+        <v>6615846</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5186,10 +5186,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122843696</v>
+        <v>122842434</v>
       </c>
       <c r="B45" t="n">
-        <v>90975</v>
+        <v>57497</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5202,34 +5202,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Dammvreten, Dammvreten, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>676651</v>
+        <v>676739</v>
       </c>
       <c r="R45" t="n">
-        <v>6615875</v>
+        <v>6615944</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5288,10 +5293,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122842680</v>
+        <v>122842950</v>
       </c>
       <c r="B46" t="n">
-        <v>57851</v>
+        <v>105482</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5304,39 +5309,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103015</v>
+        <v>221144</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>676711</v>
+        <v>676690</v>
       </c>
       <c r="R46" t="n">
-        <v>6615822</v>
+        <v>6615799</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5395,10 +5395,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122840652</v>
+        <v>122840992</v>
       </c>
       <c r="B47" t="n">
-        <v>90922</v>
+        <v>90963</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5407,38 +5407,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Hästkärret, Hästkärret, Upl</t>
+          <t>Lugnet, Lugnet, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>676670</v>
+        <v>676900</v>
       </c>
       <c r="R47" t="n">
-        <v>6615860</v>
+        <v>6615757</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5497,10 +5497,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122840989</v>
+        <v>122845245</v>
       </c>
       <c r="B48" t="n">
-        <v>5173</v>
+        <v>8441</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5513,21 +5513,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5542,10 +5542,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>676899</v>
+        <v>677001</v>
       </c>
       <c r="R48" t="n">
-        <v>6615760</v>
+        <v>6615675</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5604,10 +5604,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122842185</v>
+        <v>122843664</v>
       </c>
       <c r="B49" t="n">
-        <v>100636</v>
+        <v>100642</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5640,14 +5640,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Dammvreten, Dammvreten, Upl</t>
+          <t>Hästkärret, Hästkärret, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>676831</v>
+        <v>676656</v>
       </c>
       <c r="R49" t="n">
-        <v>6615990</v>
+        <v>6615859</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
